--- a/Generic_Requests_filled.xlsx
+++ b/Generic_Requests_filled.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
       <sz val="11"/>
       <u val="single"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -221,7 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,8 +314,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -711,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.42578125" customWidth="1" min="1" max="1"/>
@@ -957,3102 +973,5363 @@
       <c r="O5" s="35" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>HGE Foods</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Lama Albalawi</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Lama@hgefoods.com</t>
         </is>
       </c>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr"/>
+      <c r="G6" s="37" t="inlineStr"/>
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>Food business (buyer)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="36" t="inlineStr">
         <is>
           <t>Bulk freeze-dried fruits</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="27" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="27" t="n"/>
+      <c r="J6" s="36" t="inlineStr"/>
+      <c r="K6" s="38" t="n"/>
+      <c r="L6" s="36" t="inlineStr"/>
+      <c r="M6" s="38" t="n"/>
+      <c r="N6" s="36" t="inlineStr"/>
+      <c r="O6" s="38" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Alvas &amp; ko</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Rolandas Saltupis (Head of Procurement)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>Rolandas.Saltupis@alvas.lt</t>
         </is>
       </c>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr"/>
+      <c r="G7" s="37" t="inlineStr"/>
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>Distributor/wholesaler &amp; snack manufacturer</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Freeze-dried fruits</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="27" t="n"/>
+      <c r="J7" s="36" t="inlineStr"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="36" t="inlineStr"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="36" t="inlineStr"/>
+      <c r="O7" s="38" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Al Safwa Group</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Ali</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>ALi_Hamed3@hotmail.com</t>
         </is>
       </c>
-      <c r="F8" s="36" t="inlineStr">
-        <is>
-          <t>www.al-safwagroup.com</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr"/>
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>01020958645</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H8" s="37" t="inlineStr"/>
+      <c r="I8" s="36" t="inlineStr">
         <is>
           <t>Orange &amp; lemon concentrate (Brix 60-65%)</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="27" t="n"/>
+      <c r="J8" s="36" t="inlineStr"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="36" t="inlineStr"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="36" t="inlineStr"/>
+      <c r="O8" s="38" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Max Mark for Food Investment</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Yasmine Adel</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>yasmine.adel@maxmark-inv.com</t>
         </is>
       </c>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr"/>
+      <c r="G9" s="37" t="inlineStr"/>
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>Supplier/exporter fresh vegetables</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Cooperation - fresh vegetables</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="27" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="27" t="n"/>
+      <c r="J9" s="36" t="inlineStr"/>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="36" t="inlineStr"/>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="36" t="inlineStr"/>
+      <c r="O9" s="38" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Paradise Company for Fruit Drinks</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr"/>
+      <c r="D10" s="37" t="inlineStr"/>
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>paradiseco_import@outlook.com</t>
         </is>
       </c>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr"/>
+      <c r="G10" s="37" t="inlineStr"/>
+      <c r="H10" s="37" t="inlineStr"/>
+      <c r="I10" s="36" t="inlineStr">
         <is>
           <t>Orange juice concentrate (RFQ)</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="27" t="n"/>
+      <c r="J10" s="36" t="inlineStr"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="36" t="inlineStr"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="36" t="inlineStr"/>
+      <c r="O10" s="38" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Diamond Distributions</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>ruby@diamondgrocery.com</t>
         </is>
       </c>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr"/>
+      <c r="G11" s="37" t="inlineStr"/>
+      <c r="H11" s="37" t="inlineStr">
         <is>
           <t>Distributor</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="36" t="inlineStr">
         <is>
           <t>NFC juices (samples + quotation)</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="27" t="n"/>
+      <c r="J11" s="36" t="inlineStr"/>
+      <c r="K11" s="38" t="n"/>
+      <c r="L11" s="36" t="inlineStr"/>
+      <c r="M11" s="38" t="n"/>
+      <c r="N11" s="36" t="inlineStr"/>
+      <c r="O11" s="38" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Sealand</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr"/>
+      <c r="D12" s="37" t="inlineStr"/>
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>welcome.sealand@gmail.com</t>
         </is>
       </c>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr"/>
+      <c r="G12" s="37" t="inlineStr"/>
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t>Importer &amp; distributor</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
         <is>
           <t>Frozen strawberries, mango, puree</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="27" t="n"/>
+      <c r="J12" s="36" t="inlineStr"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="36" t="inlineStr"/>
+      <c r="M12" s="38" t="n"/>
+      <c r="N12" s="36" t="inlineStr"/>
+      <c r="O12" s="38" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Venkatesh Naturals</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr"/>
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>sales.dubai@venkateshnaturals.com</t>
         </is>
       </c>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr"/>
+      <c r="G13" s="37" t="inlineStr"/>
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>Supplier of ingredients</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Non-dairy creamer, fruit &amp; veg powders, natural extracts</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="27" t="n"/>
+      <c r="J13" s="36" t="inlineStr"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="36" t="inlineStr"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="36" t="inlineStr"/>
+      <c r="O13" s="38" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Yayla Agro</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Mert Palta</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>mert.palta@yaylaagro.com</t>
         </is>
       </c>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr"/>
+      <c r="G14" s="37" t="inlineStr"/>
+      <c r="H14" s="37" t="inlineStr"/>
+      <c r="I14" s="36" t="inlineStr">
         <is>
           <t>Freeze-dried strawberries (15-25mm, 5 tons CIF Mersin)</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="27" t="n"/>
+      <c r="J14" s="36" t="inlineStr"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="36" t="inlineStr"/>
+      <c r="M14" s="38" t="n"/>
+      <c r="N14" s="36" t="inlineStr"/>
+      <c r="O14" s="38" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Noble Alliance Trade</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr"/>
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Hojat</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>supply.chain.expert@noblealliancetrade.com</t>
         </is>
       </c>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr"/>
+      <c r="G15" s="37" t="inlineStr"/>
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="36" t="inlineStr">
         <is>
           <t>Fruit juice concentrates &amp; tomato paste</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="27" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="27" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="27" t="n"/>
+      <c r="J15" s="36" t="inlineStr"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="36" t="inlineStr"/>
+      <c r="M15" s="38" t="n"/>
+      <c r="N15" s="36" t="inlineStr"/>
+      <c r="O15" s="38" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>GreenField Sp. z o.o.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Daniel Polak (Sourcing Development Manager)</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>daniel.polak@greenfield.eu.com</t>
         </is>
       </c>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr"/>
+      <c r="G16" s="37" t="inlineStr"/>
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>Manufacturer of natural ingredients</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>Wet strawberry/blackberry/kiwi pomace &amp; seeds (20-200 tons)</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="27" t="n"/>
+      <c r="J16" s="36" t="inlineStr"/>
+      <c r="K16" s="38" t="n"/>
+      <c r="L16" s="36" t="inlineStr"/>
+      <c r="M16" s="38" t="n"/>
+      <c r="N16" s="36" t="inlineStr"/>
+      <c r="O16" s="38" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>EMCO spol. s r.o.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Jakub Fric (Strategic Procurement Specialist)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Jakub.Fric@emco.cz</t>
         </is>
       </c>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr"/>
+      <c r="G17" s="37" t="inlineStr">
         <is>
           <t>+420 771 257 818</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="37" t="inlineStr">
         <is>
           <t>Producer of breakfast cereals &amp; snacks</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
         <is>
           <t>Conventional FD fruits</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="27" t="n"/>
+      <c r="J17" s="36" t="inlineStr"/>
+      <c r="K17" s="38" t="n"/>
+      <c r="L17" s="36" t="inlineStr"/>
+      <c r="M17" s="38" t="n"/>
+      <c r="N17" s="36" t="inlineStr"/>
+      <c r="O17" s="38" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Pelian Lab</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr"/>
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>info@pelianlab.com</t>
         </is>
       </c>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr"/>
+      <c r="G18" s="37" t="inlineStr"/>
+      <c r="H18" s="37" t="inlineStr">
         <is>
           <t>Food company - healthy snacking</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="36" t="inlineStr">
         <is>
           <t>Freeze-dried whole strawberries</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="27" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="27" t="n"/>
+      <c r="J18" s="36" t="inlineStr"/>
+      <c r="K18" s="38" t="n"/>
+      <c r="L18" s="36" t="inlineStr"/>
+      <c r="M18" s="38" t="n"/>
+      <c r="N18" s="36" t="inlineStr"/>
+      <c r="O18" s="38" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Reliance Egypt (Ecole Ducasse Cairo)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>Amina Othman</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>amina.othman@relianceegypt.com</t>
         </is>
       </c>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr"/>
+      <c r="G19" s="37" t="inlineStr"/>
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>Culinary school launching in Egypt</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Supplier inquiry - range of products</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="27" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="27" t="n"/>
+      <c r="J19" s="36" t="inlineStr"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="36" t="inlineStr"/>
+      <c r="M19" s="38" t="n"/>
+      <c r="N19" s="36" t="inlineStr"/>
+      <c r="O19" s="38" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Litsupply</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>Justinas</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>justinas@litsupply.eu</t>
         </is>
       </c>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr"/>
+      <c r="G20" s="37" t="inlineStr"/>
+      <c r="H20" s="37" t="inlineStr">
         <is>
           <t>Supplier of food raw materials</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="36" t="inlineStr">
         <is>
           <t>Freeze-dried strawberries, blueberries, raspberries, cherries</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="27" t="n"/>
+      <c r="J20" s="36" t="inlineStr"/>
+      <c r="K20" s="38" t="n"/>
+      <c r="L20" s="36" t="inlineStr"/>
+      <c r="M20" s="38" t="n"/>
+      <c r="N20" s="36" t="inlineStr"/>
+      <c r="O20" s="38" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Good Food Group</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Mathias Bønløkke Andersen (Category Manager)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>man@goodfoodgroup.com</t>
         </is>
       </c>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr"/>
+      <c r="G21" s="37" t="inlineStr">
         <is>
           <t>+45 53 53 82 25</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="H21" s="37" t="inlineStr"/>
+      <c r="I21" s="36" t="inlineStr">
         <is>
           <t>Polaris meeting (FD/frozen fruit)</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="27" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="27" t="n"/>
+      <c r="J21" s="36" t="inlineStr"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="36" t="inlineStr"/>
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="36" t="inlineStr"/>
+      <c r="O21" s="38" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>CTD Sports</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>peter@ctdsports.com</t>
         </is>
       </c>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr"/>
+      <c r="G22" s="37" t="inlineStr"/>
+      <c r="H22" s="37" t="inlineStr"/>
+      <c r="I22" s="36" t="inlineStr">
         <is>
           <t>Freeze-dried sliced strawberries (100-500kg)</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="27" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="27" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="27" t="n"/>
+      <c r="J22" s="36" t="inlineStr"/>
+      <c r="K22" s="38" t="n"/>
+      <c r="L22" s="36" t="inlineStr"/>
+      <c r="M22" s="38" t="n"/>
+      <c r="N22" s="36" t="inlineStr"/>
+      <c r="O22" s="38" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Ginju</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>Patrick (Sales Manager)</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>patrick@ginju.ca</t>
         </is>
       </c>
-      <c r="F23" s="36" t="inlineStr">
-        <is>
-          <t>www.ginju.ca</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr"/>
+      <c r="G23" s="37" t="inlineStr">
         <is>
           <t>+1 514 299 1111</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="H23" s="37" t="inlineStr"/>
+      <c r="I23" s="36" t="inlineStr">
         <is>
           <t>Freeze-dried fruits / frozen mango</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="27" t="n"/>
+      <c r="J23" s="36" t="inlineStr"/>
+      <c r="K23" s="38" t="n"/>
+      <c r="L23" s="36" t="inlineStr"/>
+      <c r="M23" s="38" t="n"/>
+      <c r="N23" s="36" t="inlineStr"/>
+      <c r="O23" s="38" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Iberfruta Muerza S.A.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>Larami Crespo Dominguez</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>larami.crespo@iberfruta.es</t>
         </is>
       </c>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr"/>
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>+34 948 692 977</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="H24" s="37" t="inlineStr"/>
+      <c r="I24" s="36" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="27" t="n"/>
+      <c r="J24" s="36" t="inlineStr"/>
+      <c r="K24" s="38" t="n"/>
+      <c r="L24" s="36" t="inlineStr"/>
+      <c r="M24" s="38" t="n"/>
+      <c r="N24" s="36" t="inlineStr"/>
+      <c r="O24" s="38" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Alterra SA</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>Nicoletta Tarfali (Export Manager)</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>n.tarfali@alterra.gr</t>
         </is>
       </c>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr"/>
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>+30 23820 81820</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="H25" s="37" t="inlineStr"/>
+      <c r="I25" s="36" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="27" t="n"/>
+      <c r="J25" s="36" t="inlineStr"/>
+      <c r="K25" s="38" t="n"/>
+      <c r="L25" s="36" t="inlineStr"/>
+      <c r="M25" s="38" t="n"/>
+      <c r="N25" s="36" t="inlineStr"/>
+      <c r="O25" s="38" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Nomad Foods</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr"/>
+      <c r="D26" s="37" t="inlineStr">
         <is>
           <t>Emma Whitehouse (Senior Buyer - Vegetables)</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="37" t="inlineStr">
         <is>
           <t>Emma.Whitehouse@nomadfoods.com</t>
         </is>
       </c>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr"/>
+      <c r="G26" s="37" t="inlineStr"/>
+      <c r="H26" s="37" t="inlineStr"/>
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>Polaris meeting (vegetables)</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="27" t="n"/>
+      <c r="J26" s="36" t="inlineStr"/>
+      <c r="K26" s="38" t="n"/>
+      <c r="L26" s="36" t="inlineStr"/>
+      <c r="M26" s="38" t="n"/>
+      <c r="N26" s="36" t="inlineStr"/>
+      <c r="O26" s="38" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Bio Berry Poland Sp. z o.o.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>Marta Ziółkowska (Project Development Manager)</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>marta@bioberry.com.pl</t>
         </is>
       </c>
-      <c r="F27" s="36" t="n"/>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr"/>
+      <c r="G27" s="37" t="inlineStr">
         <is>
           <t>+48 535 330 803</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr"/>
+      <c r="I27" s="36" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="27" t="n"/>
+      <c r="J27" s="36" t="inlineStr"/>
+      <c r="K27" s="38" t="n"/>
+      <c r="L27" s="36" t="inlineStr"/>
+      <c r="M27" s="38" t="n"/>
+      <c r="N27" s="36" t="inlineStr"/>
+      <c r="O27" s="38" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="39" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Mondi Polska</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="40" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="40" t="inlineStr">
         <is>
           <t>Frederik Huyghe (Commercial Director)</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="40" t="inlineStr">
         <is>
           <t>frederik.huyghe@mondipolska.pl</t>
         </is>
       </c>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr"/>
+      <c r="G28" s="40" t="inlineStr">
         <is>
           <t>+32 473 93 20 00</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="H28" s="40" t="inlineStr"/>
+      <c r="I28" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
+      <c r="J28" s="39" t="inlineStr"/>
+      <c r="L28" s="39" t="inlineStr"/>
+      <c r="N28" s="39" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Back-Europ</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="40" t="inlineStr">
         <is>
           <t>Marcel Quack (Senior Trader)</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>Marcel.Quack@back-europ.de</t>
         </is>
       </c>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="F29" s="40" t="inlineStr"/>
+      <c r="G29" s="40" t="inlineStr">
         <is>
           <t>+49 221 888966 49</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="H29" s="40" t="inlineStr"/>
+      <c r="I29" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
+      <c r="J29" s="39" t="inlineStr"/>
+      <c r="L29" s="39" t="inlineStr"/>
+      <c r="N29" s="39" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>Otree Foods Co., Ltd.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="40" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="40" t="inlineStr">
         <is>
           <t>Wontae Ahn (Senior Director, Global Purchasing &amp; Business Development)</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="40" t="inlineStr">
         <is>
           <t>wontaeahn@otreefoods.com</t>
         </is>
       </c>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr"/>
+      <c r="G30" s="40" t="inlineStr"/>
+      <c r="H30" s="40" t="inlineStr"/>
+      <c r="I30" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="J30" s="39" t="inlineStr"/>
+      <c r="L30" s="39" t="inlineStr"/>
+      <c r="N30" s="39" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="39" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>Skogsmat I Uddeholm AB</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="40" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="40" t="inlineStr">
         <is>
           <t>Anton Hoogenraad</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="40" t="inlineStr">
         <is>
           <t>anton.hoogenraad@skogsmat.se</t>
         </is>
       </c>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="F31" s="40" t="inlineStr"/>
+      <c r="G31" s="40" t="inlineStr">
         <is>
           <t>+31 10 282 70 18</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="H31" s="40" t="inlineStr"/>
+      <c r="I31" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="J31" s="39" t="inlineStr"/>
+      <c r="L31" s="39" t="inlineStr"/>
+      <c r="N31" s="39" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="39" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>Bilow</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="40" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="40" t="inlineStr">
         <is>
           <t>Kamil Krzywonos</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="40" t="inlineStr">
         <is>
           <t>kamil.krzywonos@bilow.eu</t>
         </is>
       </c>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr"/>
+      <c r="G32" s="40" t="inlineStr"/>
+      <c r="H32" s="40" t="inlineStr"/>
+      <c r="I32" s="39" t="inlineStr">
         <is>
           <t>Freeze-dried strawberry slices, raspberries (offer request)</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="J32" s="39" t="inlineStr"/>
+      <c r="L32" s="39" t="inlineStr"/>
+      <c r="N32" s="39" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="39" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>Pico/GoodFood (Polaris) JQ International</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="C33" s="40" t="inlineStr"/>
+      <c r="D33" s="40" t="inlineStr">
         <is>
           <t>Nico Decuyper</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="40" t="inlineStr">
         <is>
           <t>ndecuyper@jqinternational.com</t>
         </is>
       </c>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="F33" s="40" t="inlineStr"/>
+      <c r="G33" s="40" t="inlineStr"/>
+      <c r="H33" s="40" t="inlineStr">
         <is>
           <t>Sourcing</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I33" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
+      <c r="J33" s="39" t="inlineStr"/>
+      <c r="L33" s="39" t="inlineStr"/>
+      <c r="N33" s="39" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Franuí España</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="40" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="40" t="inlineStr">
         <is>
           <t>Petar Rajic (Procurement Manager)</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="40" t="inlineStr">
         <is>
           <t>petar.rajic@franui.es</t>
         </is>
       </c>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr"/>
+      <c r="G34" s="40" t="inlineStr"/>
+      <c r="H34" s="40" t="inlineStr"/>
+      <c r="I34" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
+      <c r="J34" s="39" t="inlineStr"/>
+      <c r="L34" s="39" t="inlineStr"/>
+      <c r="N34" s="39" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="39" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>MLB Biotrade</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="40" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="40" t="inlineStr">
         <is>
           <t>Bartłomiej Złotnicki</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="40" t="inlineStr">
         <is>
           <t>b.zlotnicki@mlb-biotrade.com</t>
         </is>
       </c>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="F35" s="40" t="inlineStr"/>
+      <c r="G35" s="40" t="inlineStr"/>
+      <c r="H35" s="40" t="inlineStr"/>
+      <c r="I35" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="J35" s="39" t="inlineStr"/>
+      <c r="L35" s="39" t="inlineStr"/>
+      <c r="N35" s="39" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="39" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Leyuan Health Technology Co., Ltd</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="40" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="40" t="inlineStr">
         <is>
           <t>Alex Gao</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="40" t="inlineStr">
         <is>
           <t>gaoshan@zjleyuan.com</t>
         </is>
       </c>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr"/>
+      <c r="G36" s="40" t="inlineStr"/>
+      <c r="H36" s="40" t="inlineStr"/>
+      <c r="I36" s="39" t="inlineStr">
         <is>
           <t>FC &amp; NFC Orange Juice (quotation)</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
+      <c r="J36" s="39" t="inlineStr"/>
+      <c r="L36" s="39" t="inlineStr"/>
+      <c r="N36" s="39" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="39" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>Döhler GmbH</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="40" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="40" t="inlineStr">
         <is>
           <t>Adriana Szprega</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="40" t="inlineStr">
         <is>
           <t>adriana.szprega@doehler.com</t>
         </is>
       </c>
-      <c r="F37" s="36" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="F37" s="40" t="inlineStr"/>
+      <c r="G37" s="40" t="inlineStr"/>
+      <c r="H37" s="40" t="inlineStr"/>
+      <c r="I37" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting (IQF &amp; FD)</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="J37" s="39" t="inlineStr"/>
+      <c r="L37" s="39" t="inlineStr"/>
+      <c r="N37" s="39" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="39" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Baum Hospitality</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="C38" s="40" t="inlineStr"/>
+      <c r="D38" s="40" t="inlineStr">
         <is>
           <t>Jaroslav Sedlacek</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="40" t="inlineStr">
         <is>
           <t>info@baum-hospitality.com</t>
         </is>
       </c>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr"/>
+      <c r="G38" s="40" t="inlineStr"/>
+      <c r="H38" s="40" t="inlineStr"/>
+      <c r="I38" s="39" t="inlineStr">
         <is>
           <t>FD strawberries (slices, ~3 tonnes/yr)</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="J38" s="39" t="inlineStr"/>
+      <c r="L38" s="39" t="inlineStr"/>
+      <c r="N38" s="39" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="39" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>Alfa Trans Group</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="40" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="40" t="inlineStr">
         <is>
           <t>Mohamed Fathy Helal (Business Operations Manager)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="40" t="inlineStr">
         <is>
           <t>mohamed.helal@alfatrans.org</t>
         </is>
       </c>
-      <c r="F39" s="36" t="n"/>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr"/>
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>01005622232</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="H39" s="40" t="inlineStr"/>
+      <c r="I39" s="39" t="inlineStr">
         <is>
           <t>Private label dried strawberries &amp; fruit purees</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n"/>
-      <c r="L39" s="4" t="n"/>
-      <c r="N39" s="4" t="n"/>
+      <c r="J39" s="39" t="inlineStr"/>
+      <c r="L39" s="39" t="inlineStr"/>
+      <c r="N39" s="39" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="39" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr"/>
+      <c r="C40" s="40" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="40" t="inlineStr">
         <is>
           <t>Muhammed Uwaiz Tutla</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="40" t="inlineStr">
         <is>
           <t>muwaiztutla@gmail.com</t>
         </is>
       </c>
-      <c r="F40" s="36" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr"/>
+      <c r="G40" s="40" t="inlineStr"/>
+      <c r="H40" s="40" t="inlineStr"/>
+      <c r="I40" s="39" t="inlineStr">
         <is>
           <t>Private label juice (import to Malawi)</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
+      <c r="J40" s="39" t="inlineStr"/>
+      <c r="L40" s="39" t="inlineStr"/>
+      <c r="N40" s="39" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="39" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>Al Malaky Royal</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="40" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="40" t="inlineStr">
         <is>
           <t>Aisha Mondez</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="40" t="inlineStr">
         <is>
           <t>coordinator@almalaky.com</t>
         </is>
       </c>
-      <c r="F41" s="36" t="n"/>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="F41" s="40" t="inlineStr"/>
+      <c r="G41" s="40" t="inlineStr">
         <is>
           <t>0523525206</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="H41" s="40" t="inlineStr"/>
+      <c r="I41" s="39" t="inlineStr">
         <is>
           <t>Product inquiry</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
+      <c r="J41" s="39" t="inlineStr"/>
+      <c r="L41" s="39" t="inlineStr"/>
+      <c r="N41" s="39" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="39" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>DrinkCanva</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="C42" s="40" t="inlineStr"/>
+      <c r="D42" s="40" t="inlineStr">
         <is>
           <t>Abdelrahman Ibrahim</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="40" t="inlineStr">
         <is>
           <t>abdelrahman.ibrahim@drinkcanva.com</t>
         </is>
       </c>
-      <c r="F42" s="36" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr"/>
+      <c r="G42" s="40" t="inlineStr"/>
+      <c r="H42" s="40" t="inlineStr"/>
+      <c r="I42" s="39" t="inlineStr">
         <is>
           <t>Orange juice concentrate supply &amp; EU market collaboration</t>
         </is>
       </c>
-      <c r="J42" s="3" t="n"/>
-      <c r="L42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="J42" s="39" t="inlineStr"/>
+      <c r="L42" s="39" t="inlineStr"/>
+      <c r="N42" s="39" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="39" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>Cybera Capital</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="C43" s="40" t="inlineStr"/>
+      <c r="D43" s="40" t="inlineStr">
         <is>
           <t>A. Kose</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="40" t="inlineStr">
         <is>
           <t>br@cyberacapital.com</t>
         </is>
       </c>
-      <c r="F43" s="36" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="F43" s="40" t="inlineStr"/>
+      <c r="G43" s="40" t="inlineStr"/>
+      <c r="H43" s="40" t="inlineStr"/>
+      <c r="I43" s="39" t="inlineStr">
         <is>
           <t>IFE London meeting - fruits &amp; vegetables</t>
         </is>
       </c>
-      <c r="J43" s="3" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
+      <c r="J43" s="39" t="inlineStr"/>
+      <c r="L43" s="39" t="inlineStr"/>
+      <c r="N43" s="39" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>Entyce</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="40" t="inlineStr">
         <is>
           <t>Gino</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="40" t="inlineStr">
         <is>
           <t>gino@entyce.com.au</t>
         </is>
       </c>
-      <c r="F44" s="36" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr"/>
+      <c r="G44" s="40" t="inlineStr"/>
+      <c r="H44" s="40" t="inlineStr"/>
+      <c r="I44" s="39" t="inlineStr">
         <is>
           <t>Polaris meeting</t>
         </is>
       </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="J44" s="39" t="inlineStr"/>
+      <c r="L44" s="39" t="inlineStr"/>
+      <c r="N44" s="39" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="39" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>HBC Holding (Hamoud Boualem)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="40" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="40" t="inlineStr">
         <is>
           <t>S. Dziri</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="40" t="inlineStr">
         <is>
           <t>s.dziri@hbc-holding.com</t>
         </is>
       </c>
-      <c r="F45" s="36" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="F45" s="40" t="inlineStr"/>
+      <c r="G45" s="40" t="inlineStr"/>
+      <c r="H45" s="40" t="inlineStr"/>
+      <c r="I45" s="39" t="inlineStr">
         <is>
           <t>Concentrates (Gulfood 2026 follow-up)</t>
         </is>
       </c>
-      <c r="J45" s="3" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
+      <c r="J45" s="39" t="inlineStr"/>
+      <c r="L45" s="39" t="inlineStr"/>
+      <c r="N45" s="39" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>(Private label venture - Mr. Alaa)</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="40" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="40" t="inlineStr">
         <is>
           <t>Ghada Abdeen</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="40" t="inlineStr">
         <is>
           <t>ghadaabdeen333@gmail.com</t>
         </is>
       </c>
-      <c r="F46" s="36" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Freeze-dried fruit private label &amp; export to US</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
+      <c r="F46" s="40" t="inlineStr"/>
+      <c r="G46" s="40" t="inlineStr"/>
+      <c r="H46" s="40" t="inlineStr"/>
+      <c r="I46" s="39" t="inlineStr">
+        <is>
+          <t>FD fruit snacks private label/OEM for US Amazon FBA</t>
+        </is>
+      </c>
+      <c r="J46" s="39" t="inlineStr"/>
+      <c r="L46" s="39" t="inlineStr"/>
+      <c r="N46" s="39" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="39" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>Zain Group</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
         <is>
           <t>Jordan/ME</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="40" t="inlineStr">
         <is>
           <t>Ahmad Taha; Abdallah Sweiss; Maryam Abuawad</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="40" t="inlineStr">
         <is>
           <t>ahmad.taha@zaingroup-me.com</t>
         </is>
       </c>
-      <c r="F47" s="36" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="F47" s="40" t="inlineStr"/>
+      <c r="G47" s="40" t="inlineStr"/>
+      <c r="H47" s="40" t="inlineStr"/>
+      <c r="I47" s="39" t="inlineStr">
         <is>
           <t>Orange &amp; strawberry concentrate (specs/pricing)</t>
         </is>
       </c>
-      <c r="J47" s="3" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
+      <c r="J47" s="39" t="inlineStr"/>
+      <c r="L47" s="39" t="inlineStr"/>
+      <c r="N47" s="39" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="39" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>Fresh Dynamic</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="40" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="40" t="inlineStr">
         <is>
           <t>Nina</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="40" t="inlineStr">
         <is>
           <t>nina@freshdynamic.cn</t>
         </is>
       </c>
-      <c r="F48" s="36" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="F48" s="40" t="inlineStr"/>
+      <c r="G48" s="40" t="inlineStr"/>
+      <c r="H48" s="40" t="inlineStr"/>
+      <c r="I48" s="39" t="inlineStr">
         <is>
           <t>QF fruits &amp; vegetables (Gulfood)</t>
         </is>
       </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="J48" s="39" t="inlineStr"/>
+      <c r="L48" s="39" t="inlineStr"/>
+      <c r="N48" s="39" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="39" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>CB Commerce (Crossborders Commerce)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="40" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="40" t="inlineStr">
         <is>
           <t>Mahmoud</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="40" t="inlineStr">
         <is>
           <t>sourcing@crossboarderscommerce.com</t>
         </is>
       </c>
-      <c r="F49" s="36" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="F49" s="40" t="inlineStr"/>
+      <c r="G49" s="40" t="inlineStr"/>
+      <c r="H49" s="40" t="inlineStr"/>
+      <c r="I49" s="39" t="inlineStr">
         <is>
           <t>Strawberry puree 8% &amp; 20% Brix (USA client)</t>
         </is>
       </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="J49" s="39" t="inlineStr"/>
+      <c r="L49" s="39" t="inlineStr"/>
+      <c r="N49" s="39" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="39" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>Nature Foods Company LTD</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="40" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="40" t="inlineStr">
         <is>
           <t>Hang Tran</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="40" t="inlineStr">
         <is>
           <t>hang.tl@naturefoods.com.vn</t>
         </is>
       </c>
-      <c r="F50" s="36" t="n"/>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="F50" s="40" t="inlineStr"/>
+      <c r="G50" s="40" t="inlineStr">
         <is>
           <t>+84903941664</t>
         </is>
       </c>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="H50" s="40" t="inlineStr"/>
+      <c r="I50" s="39" t="inlineStr">
         <is>
           <t>Product inquiry</t>
         </is>
       </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="L50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="J50" s="39" t="inlineStr"/>
+      <c r="L50" s="39" t="inlineStr"/>
+      <c r="N50" s="39" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="39" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>EDEKA Südwest Stiftung &amp; Co. KG</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="40" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="40" t="inlineStr">
         <is>
           <t>Luis Meyer</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="40" t="inlineStr">
         <is>
           <t>luis.meyer@edeka-sudwest.com</t>
         </is>
       </c>
-      <c r="F51" s="36" t="n"/>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="F51" s="40" t="inlineStr"/>
+      <c r="G51" s="40" t="inlineStr">
         <is>
           <t>+49 15214017665</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="H51" s="40" t="inlineStr"/>
+      <c r="I51" s="39" t="inlineStr">
         <is>
           <t>Product inquiry (retailer)</t>
         </is>
       </c>
-      <c r="J51" s="3" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="J51" s="39" t="inlineStr"/>
+      <c r="L51" s="39" t="inlineStr"/>
+      <c r="N51" s="39" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="39" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>P. Barigelli &amp; C srl</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="40" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="40" t="inlineStr">
         <is>
           <t>Simone Soverchia</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="40" t="inlineStr">
         <is>
           <t>sales@pbarigelli.it</t>
         </is>
       </c>
-      <c r="F52" s="36" t="n"/>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr"/>
+      <c r="G52" s="40" t="inlineStr">
         <is>
           <t>0733616257</t>
         </is>
       </c>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="H52" s="40" t="inlineStr"/>
+      <c r="I52" s="39" t="inlineStr">
         <is>
           <t>Company presentation / cooperation</t>
         </is>
       </c>
-      <c r="J52" s="3" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="J52" s="39" t="inlineStr"/>
+      <c r="L52" s="39" t="inlineStr"/>
+      <c r="N52" s="39" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="39" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>MZS-TC</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="C53" s="40" t="inlineStr"/>
+      <c r="D53" s="40" t="inlineStr">
         <is>
           <t>Ahmed Kodus (Business Development)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="40" t="inlineStr">
         <is>
           <t>a.kodus@mzs-tc.com</t>
         </is>
       </c>
-      <c r="F53" s="36" t="n"/>
-      <c r="G53" s="3" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="F53" s="40" t="inlineStr"/>
+      <c r="G53" s="40" t="inlineStr"/>
+      <c r="H53" s="40" t="inlineStr"/>
+      <c r="I53" s="39" t="inlineStr">
         <is>
           <t>Gulfood follow-up - collaboration</t>
         </is>
       </c>
-      <c r="J53" s="3" t="n"/>
-      <c r="L53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
+      <c r="J53" s="39" t="inlineStr"/>
+      <c r="L53" s="39" t="inlineStr"/>
+      <c r="N53" s="39" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>Emirates Flight Catering (EKFC)</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="40" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="40" t="inlineStr">
         <is>
           <t>Chandan P</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="40" t="inlineStr">
         <is>
           <t>chandanp@ekfc.ae</t>
         </is>
       </c>
-      <c r="F54" s="36" t="n"/>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="F54" s="40" t="inlineStr"/>
+      <c r="G54" s="40" t="inlineStr"/>
+      <c r="H54" s="40" t="inlineStr"/>
+      <c r="I54" s="39" t="inlineStr">
         <is>
           <t>Custom-cut frozen vegetables (Gulfood)</t>
         </is>
       </c>
-      <c r="J54" s="3" t="n"/>
-      <c r="L54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
+      <c r="J54" s="39" t="inlineStr"/>
+      <c r="L54" s="39" t="inlineStr"/>
+      <c r="N54" s="39" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="39" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="40" t="inlineStr">
         <is>
           <t>Caila Germany</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="40" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="D55" s="40" t="inlineStr"/>
+      <c r="E55" s="40" t="inlineStr">
         <is>
           <t>hello@caila.eu</t>
         </is>
       </c>
-      <c r="F55" s="36" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="F55" s="40" t="inlineStr"/>
+      <c r="G55" s="40" t="inlineStr"/>
+      <c r="H55" s="40" t="inlineStr"/>
+      <c r="I55" s="39" t="inlineStr">
         <is>
           <t>FD fruits (Strawberry/Mango/Banana, 400-500g, 20ft CIF Rotterdam)</t>
         </is>
       </c>
-      <c r="J55" s="3" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="J55" s="39" t="inlineStr"/>
+      <c r="L55" s="39" t="inlineStr"/>
+      <c r="N55" s="39" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="39" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>Agile Table S.L. / IMB</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="40" t="inlineStr">
         <is>
           <t>Spain/USA</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="40" t="inlineStr">
         <is>
           <t>Pablo Martínez (Buyer &amp; Business Manager)</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="40" t="inlineStr">
         <is>
           <t>pablo@agiletable.es</t>
         </is>
       </c>
-      <c r="F56" s="36" t="n"/>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="F56" s="40" t="inlineStr"/>
+      <c r="G56" s="40" t="inlineStr">
         <is>
           <t>+34 676206892</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="H56" s="40" t="inlineStr"/>
+      <c r="I56" s="39" t="inlineStr">
         <is>
           <t>Tomato concentrate</t>
         </is>
       </c>
-      <c r="J56" s="3" t="n"/>
-      <c r="L56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="J56" s="39" t="inlineStr"/>
+      <c r="L56" s="39" t="inlineStr"/>
+      <c r="N56" s="39" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="39" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>Shafei Ingredients</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="40" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="40" t="inlineStr">
         <is>
           <t>Alaa Shafei (Co-founder)</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="40" t="inlineStr">
         <is>
           <t>Info@shafei-ingredients.com</t>
         </is>
       </c>
-      <c r="F57" s="36" t="n"/>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="F57" s="40" t="inlineStr"/>
+      <c r="G57" s="40" t="inlineStr">
         <is>
           <t>01006569656</t>
         </is>
       </c>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="H57" s="40" t="inlineStr"/>
+      <c r="I57" s="39" t="inlineStr">
         <is>
           <t>Ingredients cooperation</t>
         </is>
       </c>
-      <c r="J57" s="3" t="n"/>
-      <c r="L57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
+      <c r="J57" s="39" t="inlineStr"/>
+      <c r="L57" s="39" t="inlineStr"/>
+      <c r="N57" s="39" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="39" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="40" t="inlineStr">
         <is>
           <t>BridgeMark Export</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="40" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="40" t="inlineStr">
         <is>
           <t>Baher Mohamed</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="40" t="inlineStr">
         <is>
           <t>baher@bridgemarkinternational.com</t>
         </is>
       </c>
-      <c r="F58" s="36" t="n"/>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="F58" s="40" t="inlineStr"/>
+      <c r="G58" s="40" t="inlineStr">
         <is>
           <t>01010009464</t>
         </is>
       </c>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="H58" s="40" t="inlineStr"/>
+      <c r="I58" s="39" t="inlineStr">
         <is>
           <t>Export cooperation</t>
         </is>
       </c>
-      <c r="J58" s="3" t="n"/>
-      <c r="L58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="J58" s="39" t="inlineStr"/>
+      <c r="L58" s="39" t="inlineStr"/>
+      <c r="N58" s="39" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="39" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>(Supplies company / توريدات)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="40" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="40" t="inlineStr">
         <is>
           <t>Ahmed Sabry</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="40" t="inlineStr">
         <is>
           <t>ahmedalrefaey5322@gmail.com</t>
         </is>
       </c>
-      <c r="F59" s="36" t="n"/>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="F59" s="40" t="inlineStr"/>
+      <c r="G59" s="40" t="inlineStr">
         <is>
           <t>01064476303</t>
         </is>
       </c>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="H59" s="40" t="inlineStr"/>
+      <c r="I59" s="39" t="inlineStr">
         <is>
           <t>Supplier of fresh strawberries 2026/2027</t>
         </is>
       </c>
-      <c r="J59" s="3" t="n"/>
-      <c r="L59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
+      <c r="J59" s="39" t="inlineStr"/>
+      <c r="L59" s="39" t="inlineStr"/>
+      <c r="N59" s="39" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="39" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>Nickal</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="40" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="40" t="inlineStr">
         <is>
           <t>Tomasz Karolczak</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="40" t="inlineStr">
         <is>
           <t>t.karolczak@nickal.pl</t>
         </is>
       </c>
-      <c r="F60" s="36" t="n"/>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="F60" s="40" t="inlineStr"/>
+      <c r="G60" s="40" t="inlineStr">
         <is>
           <t>575400582</t>
         </is>
       </c>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="H60" s="40" t="inlineStr"/>
+      <c r="I60" s="39" t="inlineStr">
         <is>
           <t>Distributor - product inquiry</t>
         </is>
       </c>
-      <c r="J60" s="3" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
+      <c r="J60" s="39" t="inlineStr"/>
+      <c r="L60" s="39" t="inlineStr"/>
+      <c r="N60" s="39" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="39" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>Dr. Oetker</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="C61" s="40" t="inlineStr"/>
+      <c r="D61" s="40" t="inlineStr">
         <is>
           <t>Amit Gupta</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="40" t="inlineStr">
         <is>
           <t>Amit.Gupta@oetker.com</t>
         </is>
       </c>
-      <c r="F61" s="36" t="n"/>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="F61" s="40" t="inlineStr"/>
+      <c r="G61" s="40" t="inlineStr">
         <is>
           <t>+91 8470045903</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="H61" s="40" t="inlineStr"/>
+      <c r="I61" s="39" t="inlineStr">
         <is>
           <t>Concentrates requirements (Gulfood)</t>
         </is>
       </c>
-      <c r="J61" s="3" t="n"/>
-      <c r="L61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
+      <c r="J61" s="39" t="inlineStr"/>
+      <c r="L61" s="39" t="inlineStr"/>
+      <c r="N61" s="39" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="39" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>Jamil Sabbagh (juice factory)</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="40" t="inlineStr">
         <is>
           <t>Syria</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="40" t="inlineStr">
         <is>
           <t>Jamil Sabbagh</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="40" t="inlineStr">
         <is>
           <t>sabbaghjamil@gmail.com</t>
         </is>
       </c>
-      <c r="F62" s="36" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="F62" s="40" t="inlineStr"/>
+      <c r="G62" s="40" t="inlineStr"/>
+      <c r="H62" s="40" t="inlineStr"/>
+      <c r="I62" s="39" t="inlineStr">
         <is>
           <t>Strawberry &amp; guava concentrate (1 container mixed)</t>
         </is>
       </c>
-      <c r="J62" s="3" t="n"/>
-      <c r="L62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
+      <c r="J62" s="39" t="inlineStr"/>
+      <c r="L62" s="39" t="inlineStr"/>
+      <c r="N62" s="39" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="39" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>MT Export</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="40" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="D63" s="40" t="inlineStr">
+        <is>
+          <t>Amal Elsaid</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
         <is>
           <t>info@mtexporteg.com</t>
         </is>
       </c>
-      <c r="F63" s="36" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="F63" s="40" t="inlineStr"/>
+      <c r="G63" s="40" t="inlineStr">
+        <is>
+          <t>01060333434</t>
+        </is>
+      </c>
+      <c r="H63" s="40" t="inlineStr"/>
+      <c r="I63" s="39" t="inlineStr">
         <is>
           <t>RFQ freeze-dried strawberries</t>
         </is>
       </c>
-      <c r="J63" s="3" t="n"/>
-      <c r="L63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
+      <c r="J63" s="39" t="inlineStr"/>
+      <c r="L63" s="39" t="inlineStr"/>
+      <c r="N63" s="39" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="39" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>Pronat S.C.</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="40" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="40" t="inlineStr">
         <is>
           <t>J. Sanchez</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="40" t="inlineStr">
         <is>
           <t>jsanchez@pronat.com.es</t>
         </is>
       </c>
-      <c r="F64" s="36" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="F64" s="40" t="inlineStr"/>
+      <c r="G64" s="40" t="inlineStr"/>
+      <c r="H64" s="40" t="inlineStr"/>
+      <c r="I64" s="39" t="inlineStr">
         <is>
           <t>Gulfood contact (food company)</t>
         </is>
       </c>
-      <c r="J64" s="3" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
+      <c r="J64" s="39" t="inlineStr"/>
+      <c r="L64" s="39" t="inlineStr"/>
+      <c r="N64" s="39" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="39" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>Ecoloni</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="C65" s="40" t="inlineStr"/>
+      <c r="D65" s="40" t="inlineStr">
         <is>
           <t>Deniz Tuncay</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="40" t="inlineStr">
         <is>
           <t>deniz.tuncay@ecoloni.com</t>
         </is>
       </c>
-      <c r="F65" s="36" t="n"/>
-      <c r="G65" s="3" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="F65" s="40" t="inlineStr"/>
+      <c r="G65" s="40" t="inlineStr"/>
+      <c r="H65" s="40" t="inlineStr"/>
+      <c r="I65" s="39" t="inlineStr">
         <is>
           <t>Concentrates - organic (Gulfood)</t>
         </is>
       </c>
-      <c r="J65" s="3" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
+      <c r="J65" s="39" t="inlineStr"/>
+      <c r="L65" s="39" t="inlineStr"/>
+      <c r="N65" s="39" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>Helio S.A.</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="40" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="40" t="inlineStr">
         <is>
           <t>Małgorzata Jankiewicz</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="40" t="inlineStr">
         <is>
           <t>m.jankiewicz@helio.pl</t>
         </is>
       </c>
-      <c r="F66" s="36" t="n"/>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="F66" s="40" t="inlineStr"/>
+      <c r="G66" s="40" t="inlineStr">
         <is>
           <t>506558283</t>
         </is>
       </c>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="H66" s="40" t="inlineStr"/>
+      <c r="I66" s="39" t="inlineStr">
         <is>
           <t>Freeze-dried fruits</t>
         </is>
       </c>
-      <c r="J66" s="3" t="n"/>
-      <c r="L66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
+      <c r="J66" s="39" t="inlineStr"/>
+      <c r="L66" s="39" t="inlineStr"/>
+      <c r="N66" s="39" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="39" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="40" t="inlineStr">
         <is>
           <t>Iberfoods</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="40" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="40" t="inlineStr">
         <is>
           <t>A. Canovas</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="40" t="inlineStr">
         <is>
           <t>export@iberfoods.com</t>
         </is>
       </c>
-      <c r="F67" s="36" t="n"/>
-      <c r="G67" s="3" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="F67" s="40" t="inlineStr"/>
+      <c r="G67" s="40" t="inlineStr"/>
+      <c r="H67" s="40" t="inlineStr"/>
+      <c r="I67" s="39" t="inlineStr">
         <is>
           <t>IQF strawberry for France (offer request)</t>
         </is>
       </c>
-      <c r="J67" s="3" t="n"/>
-      <c r="L67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
+      <c r="J67" s="39" t="inlineStr"/>
+      <c r="L67" s="39" t="inlineStr"/>
+      <c r="N67" s="39" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="39" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>Longhai Juli Food Co., Ltd</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="40" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="40" t="inlineStr">
         <is>
           <t>Trixy</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="40" t="inlineStr">
         <is>
           <t>115514922@qq.com</t>
         </is>
       </c>
-      <c r="F68" s="36" t="n"/>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="F68" s="40" t="inlineStr"/>
+      <c r="G68" s="40" t="inlineStr">
         <is>
           <t>+86 596-6719777</t>
         </is>
       </c>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="H68" s="40" t="inlineStr"/>
+      <c r="I68" s="39" t="inlineStr">
         <is>
           <t>IQF strawberry</t>
         </is>
       </c>
-      <c r="J68" s="3" t="n"/>
-      <c r="L68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
+      <c r="J68" s="39" t="inlineStr"/>
+      <c r="L68" s="39" t="inlineStr"/>
+      <c r="N68" s="39" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="39" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>Gulf Processing (Sharaf Group)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="40" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="40" t="inlineStr">
         <is>
           <t>Nisheeth Sanwal (COO); Anirudha</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="40" t="inlineStr">
         <is>
           <t>nisheeth@gulfpro.ae</t>
         </is>
       </c>
-      <c r="F69" s="36" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="F69" s="40" t="inlineStr"/>
+      <c r="G69" s="40" t="inlineStr"/>
+      <c r="H69" s="40" t="inlineStr"/>
+      <c r="I69" s="39" t="inlineStr">
         <is>
           <t>Tomato concentrate (Gulfood)</t>
         </is>
       </c>
-      <c r="J69" s="3" t="n"/>
-      <c r="L69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
+      <c r="J69" s="39" t="inlineStr"/>
+      <c r="L69" s="39" t="inlineStr"/>
+      <c r="N69" s="39" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="39" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t>Della Peruta Vincenzo / San Marzano</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="40" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="40" t="inlineStr">
         <is>
           <t>Enzo</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="40" t="inlineStr">
         <is>
           <t>enzo@dellaperutavincenzo.it</t>
         </is>
       </c>
-      <c r="F70" s="36" t="n"/>
-      <c r="G70" s="3" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="F70" s="40" t="inlineStr"/>
+      <c r="G70" s="40" t="inlineStr"/>
+      <c r="H70" s="40" t="inlineStr"/>
+      <c r="I70" s="39" t="inlineStr">
         <is>
           <t>Tomato concentrate (Gulfood)</t>
         </is>
       </c>
-      <c r="J70" s="3" t="n"/>
-      <c r="L70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
+      <c r="J70" s="39" t="inlineStr"/>
+      <c r="L70" s="39" t="inlineStr"/>
+      <c r="N70" s="39" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="39" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>O&amp;3 Polska Sp. z o.o</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="40" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="40" t="inlineStr">
         <is>
           <t>Hubert Miklinski</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="40" t="inlineStr">
         <is>
           <t>hubertmiklinski@oand3.com</t>
         </is>
       </c>
-      <c r="F71" s="36" t="n"/>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="F71" s="40" t="inlineStr"/>
+      <c r="G71" s="40" t="inlineStr">
         <is>
           <t>506680754</t>
         </is>
       </c>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="H71" s="40" t="inlineStr"/>
+      <c r="I71" s="39" t="inlineStr">
         <is>
           <t>Strawberry seed 24 MT</t>
         </is>
       </c>
-      <c r="J71" s="3" t="n"/>
-      <c r="L71" s="4" t="n"/>
-      <c r="N71" s="4" t="n"/>
+      <c r="J71" s="39" t="inlineStr"/>
+      <c r="L71" s="39" t="inlineStr"/>
+      <c r="N71" s="39" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="39" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>DonMatcha</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="D72" s="40" t="inlineStr">
+        <is>
+          <t>Martin Veleba (CEO)</t>
+        </is>
+      </c>
+      <c r="E72" s="40" t="inlineStr">
         <is>
           <t>martin@donmatcha.com</t>
         </is>
       </c>
-      <c r="F72" s="36" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>IQF co-manufacturing order</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="n"/>
-      <c r="L72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="F72" s="40" t="inlineStr"/>
+      <c r="G72" s="40" t="inlineStr">
+        <is>
+          <t>773046154</t>
+        </is>
+      </c>
+      <c r="H72" s="40" t="inlineStr"/>
+      <c r="I72" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries (20-30 tons; whole/slices/powder)</t>
+        </is>
+      </c>
+      <c r="J72" s="39" t="inlineStr"/>
+      <c r="L72" s="39" t="inlineStr"/>
+      <c r="N72" s="39" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="39" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="40" t="inlineStr">
         <is>
           <t>Prodalim</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Jose Garcia / Francesca Blasi</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D73" s="40" t="inlineStr">
+        <is>
+          <t>Jose Antonio García (Global Sales Manager)</t>
+        </is>
+      </c>
+      <c r="E73" s="40" t="inlineStr">
         <is>
           <t>jose.garcia@prodalim.com</t>
         </is>
       </c>
-      <c r="F73" s="36" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>Citrus concentrates &amp; oils (Gulfood)</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="F73" s="40" t="inlineStr"/>
+      <c r="G73" s="40" t="inlineStr"/>
+      <c r="H73" s="40" t="inlineStr"/>
+      <c r="I73" s="39" t="inlineStr">
+        <is>
+          <t>Citrus concentrates (Gulfood meeting)</t>
+        </is>
+      </c>
+      <c r="J73" s="39" t="inlineStr"/>
+      <c r="L73" s="39" t="inlineStr"/>
+      <c r="N73" s="39" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="39" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>PROWTC</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="C74" s="40" t="inlineStr"/>
+      <c r="D74" s="40" t="inlineStr">
         <is>
           <t>Antonina Pozhilova / Maria Ducheva</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="40" t="inlineStr">
         <is>
           <t>antonina.pozhilova@prowtc.com</t>
         </is>
       </c>
-      <c r="F74" s="36" t="n"/>
-      <c r="G74" s="3" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="F74" s="40" t="inlineStr"/>
+      <c r="G74" s="40" t="inlineStr"/>
+      <c r="H74" s="40" t="inlineStr"/>
+      <c r="I74" s="39" t="inlineStr">
         <is>
           <t>IQF fruits &amp; vegetables (Gulfood)</t>
         </is>
       </c>
-      <c r="J74" s="3" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
+      <c r="J74" s="39" t="inlineStr"/>
+      <c r="L74" s="39" t="inlineStr"/>
+      <c r="N74" s="39" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="39" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="40" t="inlineStr">
         <is>
           <t>GreenLix</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="40" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="40" t="inlineStr">
         <is>
           <t>Edvardas Margelis</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="40" t="inlineStr">
         <is>
           <t>edvardas@greenlix.com</t>
         </is>
       </c>
-      <c r="F75" s="36" t="n"/>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="F75" s="40" t="inlineStr"/>
+      <c r="G75" s="40" t="inlineStr">
         <is>
           <t>+4571447106</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="H75" s="40" t="inlineStr"/>
+      <c r="I75" s="39" t="inlineStr">
         <is>
           <t>Product inquiry</t>
         </is>
       </c>
-      <c r="J75" s="3" t="n"/>
-      <c r="L75" s="4" t="n"/>
-      <c r="N75" s="4" t="n"/>
+      <c r="J75" s="39" t="inlineStr"/>
+      <c r="L75" s="39" t="inlineStr"/>
+      <c r="N75" s="39" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="39" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t>Newberry International</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="40" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="40" t="inlineStr">
         <is>
           <t>Connor Sparrow</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="40" t="inlineStr">
         <is>
           <t>ConnorS@newberryint.co.uk</t>
         </is>
       </c>
-      <c r="F76" s="36" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="F76" s="40" t="inlineStr"/>
+      <c r="G76" s="40" t="inlineStr"/>
+      <c r="H76" s="40" t="inlineStr"/>
+      <c r="I76" s="39" t="inlineStr">
         <is>
           <t>Aseptic strawberry puree (drums, CFR UK)</t>
         </is>
       </c>
-      <c r="J76" s="3" t="n"/>
-      <c r="L76" s="4" t="n"/>
-      <c r="N76" s="4" t="n"/>
+      <c r="J76" s="39" t="inlineStr"/>
+      <c r="L76" s="39" t="inlineStr"/>
+      <c r="N76" s="39" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="40" t="inlineStr">
         <is>
           <t>Endülüs Krom GmbH</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="40" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="40" t="inlineStr">
         <is>
           <t>Ahmad Hummeid</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="40" t="inlineStr">
         <is>
           <t>ahmad@enduluskromgmbh.com</t>
         </is>
       </c>
-      <c r="F77" s="36" t="n"/>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="F77" s="40" t="inlineStr"/>
+      <c r="G77" s="40" t="inlineStr">
         <is>
           <t>+4917667503821</t>
         </is>
       </c>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="H77" s="40" t="inlineStr"/>
+      <c r="I77" s="39" t="inlineStr">
         <is>
           <t>Product inquiry</t>
         </is>
       </c>
-      <c r="J77" s="3" t="n"/>
-      <c r="L77" s="4" t="n"/>
-      <c r="N77" s="4" t="n"/>
+      <c r="J77" s="39" t="inlineStr"/>
+      <c r="L77" s="39" t="inlineStr"/>
+      <c r="N77" s="39" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="39" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="40" t="inlineStr">
         <is>
           <t>Chane GmbH</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="40" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="40" t="inlineStr">
         <is>
           <t>Ali Imran Terzi</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="40" t="inlineStr">
         <is>
           <t>ali.terzi42@icloud.com</t>
         </is>
       </c>
-      <c r="F78" s="36" t="n"/>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="F78" s="40" t="inlineStr"/>
+      <c r="G78" s="40" t="inlineStr">
         <is>
           <t>1787811247</t>
         </is>
       </c>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="H78" s="40" t="inlineStr"/>
+      <c r="I78" s="39" t="inlineStr">
         <is>
           <t>FD strawberry slices (price/MOQ)</t>
         </is>
       </c>
-      <c r="J78" s="3" t="n"/>
-      <c r="L78" s="4" t="n"/>
-      <c r="N78" s="4" t="n"/>
+      <c r="J78" s="39" t="inlineStr"/>
+      <c r="L78" s="39" t="inlineStr"/>
+      <c r="N78" s="39" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="39" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="40" t="inlineStr">
         <is>
           <t>Dafanatürel / Global Supply Point Gida</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="40" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="40" t="inlineStr">
         <is>
           <t>Mesut Şişman (GM)</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E79" s="40" t="inlineStr">
         <is>
           <t>mesutsisman@dafanaturel.com.tr</t>
         </is>
       </c>
-      <c r="F79" s="36" t="n"/>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="F79" s="40" t="inlineStr"/>
+      <c r="G79" s="40" t="inlineStr">
         <is>
           <t>+90 507 077 6453</t>
         </is>
       </c>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="H79" s="40" t="inlineStr"/>
+      <c r="I79" s="39" t="inlineStr">
         <is>
           <t>Orange/lemon/pomegranate concentrate (FOJC Brix 65, 5 containers, Mersin)</t>
         </is>
       </c>
-      <c r="J79" s="3" t="n"/>
-      <c r="L79" s="4" t="n"/>
-      <c r="N79" s="4" t="n"/>
+      <c r="J79" s="39" t="inlineStr"/>
+      <c r="L79" s="39" t="inlineStr"/>
+      <c r="N79" s="39" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="39" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>Kern Export</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="C80" s="40" t="inlineStr"/>
+      <c r="D80" s="40" t="inlineStr">
         <is>
           <t>Hossam Soliman</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E80" s="40" t="inlineStr">
         <is>
           <t>Hossam.Soliman@kern-export.com</t>
         </is>
       </c>
-      <c r="F80" s="36" t="n"/>
-      <c r="G80" s="3" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="F80" s="40" t="inlineStr"/>
+      <c r="G80" s="40" t="inlineStr"/>
+      <c r="H80" s="40" t="inlineStr"/>
+      <c r="I80" s="39" t="inlineStr">
         <is>
           <t>CMO / co-manufacturing availability</t>
         </is>
       </c>
-      <c r="J80" s="3" t="n"/>
-      <c r="L80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
+      <c r="J80" s="39" t="inlineStr"/>
+      <c r="L80" s="39" t="inlineStr"/>
+      <c r="N80" s="39" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="39" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="40" t="inlineStr">
+        <is>
+          <t>Fergana Exim Agro</t>
+        </is>
+      </c>
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="D81" s="40" t="inlineStr">
+        <is>
+          <t>Orifjon Sultonov</t>
+        </is>
+      </c>
+      <c r="E81" s="40" t="inlineStr">
+        <is>
+          <t>info@eximagro.uz</t>
+        </is>
+      </c>
+      <c r="F81" s="40" t="inlineStr"/>
+      <c r="G81" s="40" t="inlineStr">
+        <is>
+          <t>+998331017330</t>
+        </is>
+      </c>
+      <c r="H81" s="40" t="inlineStr"/>
+      <c r="I81" s="39" t="inlineStr">
+        <is>
+          <t>IQF whole strawberries (1 container, Poti/FOB)</t>
+        </is>
+      </c>
+      <c r="J81" s="39" t="inlineStr"/>
+      <c r="L81" s="39" t="inlineStr"/>
+      <c r="N81" s="39" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="40" t="inlineStr">
+        <is>
+          <t>World's Garden / Freshzilla</t>
+        </is>
+      </c>
+      <c r="C82" s="40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D82" s="40" t="inlineStr">
+        <is>
+          <t>Rebecca Perez</t>
+        </is>
+      </c>
+      <c r="E82" s="40" t="inlineStr">
+        <is>
+          <t>avo@worldsgarden.eu</t>
+        </is>
+      </c>
+      <c r="F82" s="40" t="inlineStr"/>
+      <c r="G82" s="40" t="inlineStr">
+        <is>
+          <t>4434828798</t>
+        </is>
+      </c>
+      <c r="H82" s="40" t="inlineStr"/>
+      <c r="I82" s="39" t="inlineStr">
+        <is>
+          <t>FD slices (mango/banana/peach), strawberry powder/pieces (50kg)</t>
+        </is>
+      </c>
+      <c r="J82" s="39" t="inlineStr"/>
+      <c r="L82" s="39" t="inlineStr"/>
+      <c r="N82" s="39" t="inlineStr"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="39" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="40" t="inlineStr">
+        <is>
+          <t>Genba Food</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="D83" s="40" t="inlineStr">
+        <is>
+          <t>Dominykas Jasaitis</t>
+        </is>
+      </c>
+      <c r="E83" s="40" t="inlineStr">
+        <is>
+          <t>d.jasaitis@genbafood.lt</t>
+        </is>
+      </c>
+      <c r="F83" s="40" t="inlineStr"/>
+      <c r="G83" s="40" t="inlineStr"/>
+      <c r="H83" s="40" t="inlineStr"/>
+      <c r="I83" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried berries (Baltics wholesaler)</t>
+        </is>
+      </c>
+      <c r="J83" s="39" t="inlineStr"/>
+      <c r="L83" s="39" t="inlineStr"/>
+      <c r="N83" s="39" t="inlineStr"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="40" t="inlineStr">
+        <is>
+          <t>Vitmark</t>
+        </is>
+      </c>
+      <c r="C84" s="40" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="D84" s="40" t="inlineStr">
+        <is>
+          <t>Oksana Diachkova</t>
+        </is>
+      </c>
+      <c r="E84" s="40" t="inlineStr">
+        <is>
+          <t>o.diachkova@vitmark.com</t>
+        </is>
+      </c>
+      <c r="F84" s="40" t="inlineStr"/>
+      <c r="G84" s="40" t="inlineStr"/>
+      <c r="H84" s="40" t="inlineStr"/>
+      <c r="I84" s="39" t="inlineStr">
+        <is>
+          <t>Strawberry puree, mandarin JC, lemon JC</t>
+        </is>
+      </c>
+      <c r="J84" s="39" t="inlineStr"/>
+      <c r="L84" s="39" t="inlineStr"/>
+      <c r="N84" s="39" t="inlineStr"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="39" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="40" t="inlineStr">
+        <is>
+          <t>JV Chortoq Mineral Water LLC</t>
+        </is>
+      </c>
+      <c r="C85" s="40" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="D85" s="40" t="inlineStr">
+        <is>
+          <t>Natalya Kupriyanova</t>
+        </is>
+      </c>
+      <c r="E85" s="40" t="inlineStr">
+        <is>
+          <t>kupriyanova.natalya@chortoq.com</t>
+        </is>
+      </c>
+      <c r="F85" s="40" t="inlineStr"/>
+      <c r="G85" s="40" t="inlineStr">
+        <is>
+          <t>+998947111984</t>
+        </is>
+      </c>
+      <c r="H85" s="40" t="inlineStr"/>
+      <c r="I85" s="39" t="inlineStr">
+        <is>
+          <t>Samples / product match</t>
+        </is>
+      </c>
+      <c r="J85" s="39" t="inlineStr"/>
+      <c r="L85" s="39" t="inlineStr"/>
+      <c r="N85" s="39" t="inlineStr"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="39" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="40" t="inlineStr">
+        <is>
+          <t>MTB</t>
+        </is>
+      </c>
+      <c r="C86" s="40" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D86" s="40" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="E86" s="40" t="inlineStr">
+        <is>
+          <t>guilherme@mtb.net.br</t>
+        </is>
+      </c>
+      <c r="F86" s="40" t="inlineStr"/>
+      <c r="G86" s="40" t="inlineStr"/>
+      <c r="H86" s="40" t="inlineStr"/>
+      <c r="I86" s="39" t="inlineStr">
+        <is>
+          <t>Fruit juices (sales inquiry)</t>
+        </is>
+      </c>
+      <c r="J86" s="39" t="inlineStr"/>
+      <c r="L86" s="39" t="inlineStr"/>
+      <c r="N86" s="39" t="inlineStr"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="39" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="40" t="inlineStr">
+        <is>
+          <t>K.B. Innovation Group</t>
+        </is>
+      </c>
+      <c r="C87" s="40" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D87" s="40" t="inlineStr">
+        <is>
+          <t>Matej Tornyai</t>
+        </is>
+      </c>
+      <c r="E87" s="40" t="inlineStr">
+        <is>
+          <t>matej@lipty.sk</t>
+        </is>
+      </c>
+      <c r="F87" s="40" t="inlineStr"/>
+      <c r="G87" s="40" t="inlineStr">
+        <is>
+          <t>+421903752228</t>
+        </is>
+      </c>
+      <c r="H87" s="40" t="inlineStr"/>
+      <c r="I87" s="39" t="inlineStr">
+        <is>
+          <t>Cooperation</t>
+        </is>
+      </c>
+      <c r="J87" s="39" t="inlineStr"/>
+      <c r="L87" s="39" t="inlineStr"/>
+      <c r="N87" s="39" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="39" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="40" t="inlineStr"/>
+      <c r="C88" s="40" t="inlineStr"/>
+      <c r="D88" s="40" t="inlineStr"/>
+      <c r="E88" s="40" t="inlineStr">
+        <is>
+          <t>zsygdkmt1999@gmail.com</t>
+        </is>
+      </c>
+      <c r="F88" s="40" t="inlineStr"/>
+      <c r="G88" s="40" t="inlineStr"/>
+      <c r="H88" s="40" t="inlineStr"/>
+      <c r="I88" s="39" t="inlineStr">
+        <is>
+          <t>Fruit concentrates (guava, mango, strawberry, orange) - prices/Brix</t>
+        </is>
+      </c>
+      <c r="J88" s="39" t="inlineStr"/>
+      <c r="L88" s="39" t="inlineStr"/>
+      <c r="N88" s="39" t="inlineStr"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="39" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="40" t="inlineStr">
+        <is>
+          <t>Markable General Trading</t>
+        </is>
+      </c>
+      <c r="C89" s="40" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D89" s="40" t="inlineStr">
+        <is>
+          <t>Habib Habib</t>
+        </is>
+      </c>
+      <c r="E89" s="40" t="inlineStr">
+        <is>
+          <t>habib@markableuae.com</t>
+        </is>
+      </c>
+      <c r="F89" s="40" t="inlineStr"/>
+      <c r="G89" s="40" t="inlineStr">
+        <is>
+          <t>00971523925791</t>
+        </is>
+      </c>
+      <c r="H89" s="40" t="inlineStr"/>
+      <c r="I89" s="39" t="inlineStr">
+        <is>
+          <t>Gulfood meeting follow-up</t>
+        </is>
+      </c>
+      <c r="J89" s="39" t="inlineStr"/>
+      <c r="L89" s="39" t="inlineStr"/>
+      <c r="N89" s="39" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="39" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="40" t="inlineStr">
+        <is>
+          <t>Kirlioglu</t>
+        </is>
+      </c>
+      <c r="C90" s="40" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D90" s="40" t="inlineStr">
+        <is>
+          <t>Yasemin Kalay</t>
+        </is>
+      </c>
+      <c r="E90" s="40" t="inlineStr">
+        <is>
+          <t>yasemin.kalay@kirlioglu.com</t>
+        </is>
+      </c>
+      <c r="F90" s="40" t="inlineStr"/>
+      <c r="G90" s="40" t="inlineStr"/>
+      <c r="H90" s="40" t="inlineStr"/>
+      <c r="I90" s="39" t="inlineStr">
+        <is>
+          <t>Purchasing FD fruits (20ft/40ft, FOB/CIF)</t>
+        </is>
+      </c>
+      <c r="J90" s="39" t="inlineStr"/>
+      <c r="L90" s="39" t="inlineStr"/>
+      <c r="N90" s="39" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="39" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="40" t="inlineStr">
+        <is>
+          <t>Bureau Veritas</t>
+        </is>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D91" s="40" t="inlineStr">
+        <is>
+          <t>Miguel Gomez</t>
+        </is>
+      </c>
+      <c r="E91" s="40" t="inlineStr">
+        <is>
+          <t>miguel.gomez@bureouveritas.com</t>
+        </is>
+      </c>
+      <c r="F91" s="40" t="inlineStr"/>
+      <c r="G91" s="40" t="inlineStr">
+        <is>
+          <t>990354287</t>
+        </is>
+      </c>
+      <c r="H91" s="40" t="inlineStr"/>
+      <c r="I91" s="39" t="inlineStr">
+        <is>
+          <t>Sourcing products in bulk</t>
+        </is>
+      </c>
+      <c r="J91" s="39" t="inlineStr"/>
+      <c r="L91" s="39" t="inlineStr"/>
+      <c r="N91" s="39" t="inlineStr"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="39" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="40" t="inlineStr">
+        <is>
+          <t>P. Gkotzaridis and Co</t>
+        </is>
+      </c>
+      <c r="C92" s="40" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="D92" s="40" t="inlineStr">
+        <is>
+          <t>Stella Gkotzaridis (Procurement Manager)</t>
+        </is>
+      </c>
+      <c r="E92" s="40" t="inlineStr">
+        <is>
+          <t>pgkotzaridisandco@gmail.com</t>
+        </is>
+      </c>
+      <c r="F92" s="40" t="inlineStr"/>
+      <c r="G92" s="40" t="inlineStr">
+        <is>
+          <t>2399051416</t>
+        </is>
+      </c>
+      <c r="H92" s="40" t="inlineStr"/>
+      <c r="I92" s="39" t="inlineStr">
+        <is>
+          <t>Procurement inquiry</t>
+        </is>
+      </c>
+      <c r="J92" s="39" t="inlineStr"/>
+      <c r="L92" s="39" t="inlineStr"/>
+      <c r="N92" s="39" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="39" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="40" t="inlineStr">
+        <is>
+          <t>Lemonera / Uj Group</t>
+        </is>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D93" s="40" t="inlineStr">
+        <is>
+          <t>Orhan Dursun</t>
+        </is>
+      </c>
+      <c r="E93" s="40" t="inlineStr">
+        <is>
+          <t>orhan@ujgrp.com</t>
+        </is>
+      </c>
+      <c r="F93" s="40" t="inlineStr"/>
+      <c r="G93" s="40" t="inlineStr">
+        <is>
+          <t>00905325972721</t>
+        </is>
+      </c>
+      <c r="H93" s="40" t="inlineStr"/>
+      <c r="I93" s="39" t="inlineStr">
+        <is>
+          <t>Frozen lemon juice</t>
+        </is>
+      </c>
+      <c r="J93" s="39" t="inlineStr"/>
+      <c r="L93" s="39" t="inlineStr"/>
+      <c r="N93" s="39" t="inlineStr"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="39" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="40" t="inlineStr">
+        <is>
+          <t>Pilmifresh</t>
+        </is>
+      </c>
+      <c r="C94" s="40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D94" s="40" t="inlineStr">
+        <is>
+          <t>C. Guillem</t>
+        </is>
+      </c>
+      <c r="E94" s="40" t="inlineStr">
+        <is>
+          <t>cguillem@pilmifresh.com</t>
+        </is>
+      </c>
+      <c r="F94" s="40" t="inlineStr"/>
+      <c r="G94" s="40" t="inlineStr"/>
+      <c r="H94" s="40" t="inlineStr"/>
+      <c r="I94" s="39" t="inlineStr">
+        <is>
+          <t>Lemon juice concentrate cloudy/clear 400-500 gpl (2026 demand)</t>
+        </is>
+      </c>
+      <c r="J94" s="39" t="inlineStr"/>
+      <c r="L94" s="39" t="inlineStr"/>
+      <c r="N94" s="39" t="inlineStr"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="39" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="40" t="inlineStr">
+        <is>
+          <t>Gemma Natural</t>
+        </is>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D95" s="40" t="inlineStr">
+        <is>
+          <t>Eymen Hamitoglu</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="inlineStr">
+        <is>
+          <t>eymen.hamitoglu@gemmanatural.com</t>
+        </is>
+      </c>
+      <c r="F95" s="40" t="inlineStr"/>
+      <c r="G95" s="40" t="inlineStr"/>
+      <c r="H95" s="40" t="inlineStr"/>
+      <c r="I95" s="39" t="inlineStr">
+        <is>
+          <t>Natural food colors/flavours - cooperation</t>
+        </is>
+      </c>
+      <c r="J95" s="39" t="inlineStr"/>
+      <c r="L95" s="39" t="inlineStr"/>
+      <c r="N95" s="39" t="inlineStr"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="39" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="40" t="inlineStr">
+        <is>
+          <t>Elreefy Trading Co.</t>
+        </is>
+      </c>
+      <c r="C96" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D96" s="40" t="inlineStr">
+        <is>
+          <t>Islam Elamry</t>
+        </is>
+      </c>
+      <c r="E96" s="40" t="inlineStr">
+        <is>
+          <t>islam.elamry94@gmail.com</t>
+        </is>
+      </c>
+      <c r="F96" s="40" t="inlineStr"/>
+      <c r="G96" s="40" t="inlineStr">
+        <is>
+          <t>01061498589</t>
+        </is>
+      </c>
+      <c r="H96" s="40" t="inlineStr"/>
+      <c r="I96" s="39" t="inlineStr">
+        <is>
+          <t>Sales inquiry</t>
+        </is>
+      </c>
+      <c r="J96" s="39" t="inlineStr"/>
+      <c r="L96" s="39" t="inlineStr"/>
+      <c r="N96" s="39" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="39" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="40" t="inlineStr">
+        <is>
+          <t>(N/A)</t>
+        </is>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D97" s="40" t="inlineStr">
+        <is>
+          <t>Ali Ryad</t>
+        </is>
+      </c>
+      <c r="E97" s="40" t="inlineStr">
+        <is>
+          <t>aliryad614@gmail.com</t>
+        </is>
+      </c>
+      <c r="F97" s="40" t="inlineStr"/>
+      <c r="G97" s="40" t="inlineStr">
+        <is>
+          <t>+971503409475</t>
+        </is>
+      </c>
+      <c r="H97" s="40" t="inlineStr"/>
+      <c r="I97" s="39" t="inlineStr">
+        <is>
+          <t>Brochure + quotation request</t>
+        </is>
+      </c>
+      <c r="J97" s="39" t="inlineStr"/>
+      <c r="L97" s="39" t="inlineStr"/>
+      <c r="N97" s="39" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="39" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="40" t="inlineStr">
+        <is>
+          <t>Andros</t>
+        </is>
+      </c>
+      <c r="C98" s="40" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D98" s="40" t="inlineStr">
+        <is>
+          <t>Herve Bassat</t>
+        </is>
+      </c>
+      <c r="E98" s="40" t="inlineStr">
+        <is>
+          <t>herve.bassat@andros.fr</t>
+        </is>
+      </c>
+      <c r="F98" s="40" t="inlineStr"/>
+      <c r="G98" s="40" t="inlineStr">
+        <is>
+          <t>0033620730939</t>
+        </is>
+      </c>
+      <c r="H98" s="40" t="inlineStr"/>
+      <c r="I98" s="39" t="inlineStr">
+        <is>
+          <t>NFC orange juice</t>
+        </is>
+      </c>
+      <c r="J98" s="39" t="inlineStr"/>
+      <c r="L98" s="39" t="inlineStr"/>
+      <c r="N98" s="39" t="inlineStr"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="39" t="n">
+        <v>95</v>
+      </c>
+      <c r="B99" s="40" t="inlineStr">
+        <is>
+          <t>PROGRESS (АО ПРОГРЕСС)</t>
+        </is>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D99" s="40" t="inlineStr">
+        <is>
+          <t>Zhanna Kazak</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="inlineStr">
+        <is>
+          <t>ZKAZAK@PROGRESSFOOD.COM</t>
+        </is>
+      </c>
+      <c r="F99" s="40" t="inlineStr"/>
+      <c r="G99" s="40" t="inlineStr">
+        <is>
+          <t>+79264121460</t>
+        </is>
+      </c>
+      <c r="H99" s="40" t="inlineStr"/>
+      <c r="I99" s="39" t="inlineStr">
+        <is>
+          <t>Product inquiry</t>
+        </is>
+      </c>
+      <c r="J99" s="39" t="inlineStr"/>
+      <c r="L99" s="39" t="inlineStr"/>
+      <c r="N99" s="39" t="inlineStr"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="39" t="n">
+        <v>96</v>
+      </c>
+      <c r="B100" s="40" t="inlineStr">
+        <is>
+          <t>Uniya Chile SpA</t>
+        </is>
+      </c>
+      <c r="C100" s="40" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D100" s="40" t="inlineStr">
+        <is>
+          <t>Najib Ismail</t>
+        </is>
+      </c>
+      <c r="E100" s="40" t="inlineStr">
+        <is>
+          <t>najib@uniya.cl</t>
+        </is>
+      </c>
+      <c r="F100" s="40" t="inlineStr"/>
+      <c r="G100" s="40" t="inlineStr">
+        <is>
+          <t>+56934143633</t>
+        </is>
+      </c>
+      <c r="H100" s="40" t="inlineStr"/>
+      <c r="I100" s="39" t="inlineStr">
+        <is>
+          <t>Sweet potato varieties / EU export &amp; chips line</t>
+        </is>
+      </c>
+      <c r="J100" s="39" t="inlineStr"/>
+      <c r="L100" s="39" t="inlineStr"/>
+      <c r="N100" s="39" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="39" t="n">
+        <v>97</v>
+      </c>
+      <c r="B101" s="40" t="inlineStr">
+        <is>
+          <t>El Motaheda Ltd</t>
+        </is>
+      </c>
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D101" s="40" t="inlineStr">
+        <is>
+          <t>Hany Mahrous</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
+        <is>
+          <t>hany@elmotaheda-agri.com</t>
+        </is>
+      </c>
+      <c r="F101" s="40" t="inlineStr"/>
+      <c r="G101" s="40" t="inlineStr">
+        <is>
+          <t>00447588448739</t>
+        </is>
+      </c>
+      <c r="H101" s="40" t="inlineStr"/>
+      <c r="I101" s="39" t="inlineStr">
+        <is>
+          <t>Cooperation inquiry</t>
+        </is>
+      </c>
+      <c r="J101" s="39" t="inlineStr"/>
+      <c r="L101" s="39" t="inlineStr"/>
+      <c r="N101" s="39" t="inlineStr"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="39" t="n">
+        <v>98</v>
+      </c>
+      <c r="B102" s="40" t="inlineStr">
+        <is>
+          <t>MABNO LLC</t>
+        </is>
+      </c>
+      <c r="C102" s="40" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="D102" s="40" t="inlineStr">
+        <is>
+          <t>Sadulloi Ismat</t>
+        </is>
+      </c>
+      <c r="E102" s="40" t="inlineStr">
+        <is>
+          <t>sadulloismat2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="F102" s="40" t="inlineStr"/>
+      <c r="G102" s="40" t="inlineStr">
+        <is>
+          <t>+992987901998</t>
+        </is>
+      </c>
+      <c r="H102" s="40" t="inlineStr"/>
+      <c r="I102" s="39" t="inlineStr">
+        <is>
+          <t>Cooperation inquiry</t>
+        </is>
+      </c>
+      <c r="J102" s="39" t="inlineStr"/>
+      <c r="L102" s="39" t="inlineStr"/>
+      <c r="N102" s="39" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="39" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="40" t="inlineStr">
+        <is>
+          <t>HR Broker Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="C103" s="40" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D103" s="40" t="inlineStr">
+        <is>
+          <t>Padmini Bharati</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="inlineStr">
+        <is>
+          <t>padmini@hrbroker.com.br</t>
+        </is>
+      </c>
+      <c r="F103" s="40" t="inlineStr"/>
+      <c r="G103" s="40" t="inlineStr">
+        <is>
+          <t>9373399905</t>
+        </is>
+      </c>
+      <c r="H103" s="40" t="inlineStr"/>
+      <c r="I103" s="39" t="inlineStr">
+        <is>
+          <t>Import inquiry</t>
+        </is>
+      </c>
+      <c r="J103" s="39" t="inlineStr"/>
+      <c r="L103" s="39" t="inlineStr"/>
+      <c r="N103" s="39" t="inlineStr"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="40" t="inlineStr">
+        <is>
+          <t>SAMCA</t>
+        </is>
+      </c>
+      <c r="C104" s="40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D104" s="40" t="inlineStr">
+        <is>
+          <t>A. Arnal</t>
+        </is>
+      </c>
+      <c r="E104" s="40" t="inlineStr">
+        <is>
+          <t>aarnal@samca.com</t>
+        </is>
+      </c>
+      <c r="F104" s="40" t="inlineStr"/>
+      <c r="G104" s="40" t="inlineStr"/>
+      <c r="H104" s="40" t="inlineStr"/>
+      <c r="I104" s="39" t="inlineStr">
+        <is>
+          <t>Rehydrated prunes (industrial use - supplier offer)</t>
+        </is>
+      </c>
+      <c r="J104" s="39" t="inlineStr"/>
+      <c r="L104" s="39" t="inlineStr"/>
+      <c r="N104" s="39" t="inlineStr"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="39" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="40" t="inlineStr">
+        <is>
+          <t>Olayan Agricultural Crops (عليان)</t>
+        </is>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D105" s="40" t="inlineStr">
+        <is>
+          <t>Ahmed Atef</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="inlineStr">
+        <is>
+          <t>ahmedatef.4698@gmail.com</t>
+        </is>
+      </c>
+      <c r="F105" s="40" t="inlineStr"/>
+      <c r="G105" s="40" t="inlineStr">
+        <is>
+          <t>01007075225</t>
+        </is>
+      </c>
+      <c r="H105" s="40" t="inlineStr"/>
+      <c r="I105" s="39" t="inlineStr">
+        <is>
+          <t>Supply fresh/IQF strawberries (300 tons, FDA)</t>
+        </is>
+      </c>
+      <c r="J105" s="39" t="inlineStr"/>
+      <c r="L105" s="39" t="inlineStr"/>
+      <c r="N105" s="39" t="inlineStr"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="39" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="40" t="inlineStr">
+        <is>
+          <t>El Daabas Farm (مزرعة الدعباس)</t>
+        </is>
+      </c>
+      <c r="C106" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D106" s="40" t="inlineStr">
+        <is>
+          <t>Ahmed Ali Elsaied</t>
+        </is>
+      </c>
+      <c r="E106" s="40" t="inlineStr">
+        <is>
+          <t>ahmedalielsaied492005@gmail.com</t>
+        </is>
+      </c>
+      <c r="F106" s="40" t="inlineStr"/>
+      <c r="G106" s="40" t="inlineStr"/>
+      <c r="H106" s="40" t="inlineStr"/>
+      <c r="I106" s="39" t="inlineStr">
+        <is>
+          <t>Supply fresh strawberries</t>
+        </is>
+      </c>
+      <c r="J106" s="39" t="inlineStr"/>
+      <c r="L106" s="39" t="inlineStr"/>
+      <c r="N106" s="39" t="inlineStr"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="39" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="40" t="inlineStr">
+        <is>
+          <t>Morocco SAULÉ</t>
+        </is>
+      </c>
+      <c r="C107" s="40" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>Leila Khedji</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
+        <is>
+          <t>leilakhedji@gmail.com</t>
+        </is>
+      </c>
+      <c r="F107" s="40" t="inlineStr"/>
+      <c r="G107" s="40" t="inlineStr"/>
+      <c r="H107" s="40" t="inlineStr"/>
+      <c r="I107" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried products (export to Morocco)</t>
+        </is>
+      </c>
+      <c r="J107" s="39" t="inlineStr"/>
+      <c r="L107" s="39" t="inlineStr"/>
+      <c r="N107" s="39" t="inlineStr"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="39" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="40" t="inlineStr">
+        <is>
+          <t>Pure and Natural Holland by Ksy B.V.</t>
+        </is>
+      </c>
+      <c r="C108" s="40" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D108" s="40" t="inlineStr">
+        <is>
+          <t>Stefan Classens</t>
+        </is>
+      </c>
+      <c r="E108" s="40" t="inlineStr">
+        <is>
+          <t>s.classens@pureandnaturalksy.nl</t>
+        </is>
+      </c>
+      <c r="F108" s="40" t="inlineStr"/>
+      <c r="G108" s="40" t="inlineStr"/>
+      <c r="H108" s="40" t="inlineStr"/>
+      <c r="I108" s="39" t="inlineStr">
+        <is>
+          <t>Citrus / orange juice blends (Gulfood meeting)</t>
+        </is>
+      </c>
+      <c r="J108" s="39" t="inlineStr"/>
+      <c r="L108" s="39" t="inlineStr"/>
+      <c r="N108" s="39" t="inlineStr"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="39" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="40" t="inlineStr">
+        <is>
+          <t>Oleador</t>
+        </is>
+      </c>
+      <c r="C109" s="40" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>Katja Skalda</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
+        <is>
+          <t>katja.skalda@oleador.com</t>
+        </is>
+      </c>
+      <c r="F109" s="40" t="inlineStr"/>
+      <c r="G109" s="40" t="inlineStr"/>
+      <c r="H109" s="40" t="inlineStr"/>
+      <c r="I109" s="39" t="inlineStr">
+        <is>
+          <t>Organic fruit seeds (strawberry/raspberry/blackcurrant) for oil</t>
+        </is>
+      </c>
+      <c r="J109" s="39" t="inlineStr"/>
+      <c r="L109" s="39" t="inlineStr"/>
+      <c r="N109" s="39" t="inlineStr"/>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="39" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="40" t="inlineStr">
+        <is>
+          <t>Garden Guru</t>
+        </is>
+      </c>
+      <c r="C110" s="40" t="inlineStr"/>
+      <c r="D110" s="40" t="inlineStr">
+        <is>
+          <t>Nesrine Hammady (Business Manager)</t>
+        </is>
+      </c>
+      <c r="E110" s="40" t="inlineStr">
+        <is>
+          <t>nesrinehammady@gmail.com</t>
+        </is>
+      </c>
+      <c r="F110" s="40" t="inlineStr"/>
+      <c r="G110" s="40" t="inlineStr"/>
+      <c r="H110" s="40" t="inlineStr"/>
+      <c r="I110" s="39" t="inlineStr">
+        <is>
+          <t>FD strawberries (granules) 7 tons - export to China</t>
+        </is>
+      </c>
+      <c r="J110" s="39" t="inlineStr"/>
+      <c r="L110" s="39" t="inlineStr"/>
+      <c r="N110" s="39" t="inlineStr"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="39" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="40" t="inlineStr">
+        <is>
+          <t>Agricole General Trading S.L</t>
+        </is>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="D111" s="40" t="inlineStr">
+        <is>
+          <t>Leith Bassatina</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="inlineStr">
+        <is>
+          <t>leith.bassatne6@gmail.com</t>
+        </is>
+      </c>
+      <c r="F111" s="40" t="inlineStr"/>
+      <c r="G111" s="40" t="inlineStr">
+        <is>
+          <t>+5358761275</t>
+        </is>
+      </c>
+      <c r="H111" s="40" t="inlineStr"/>
+      <c r="I111" s="39" t="inlineStr">
+        <is>
+          <t>Meeting request / cooperation</t>
+        </is>
+      </c>
+      <c r="J111" s="39" t="inlineStr"/>
+      <c r="L111" s="39" t="inlineStr"/>
+      <c r="N111" s="39" t="inlineStr"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="39" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="40" t="inlineStr">
+        <is>
+          <t>ETS. Enupanco W/A Agency</t>
+        </is>
+      </c>
+      <c r="C112" s="40" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="D112" s="40" t="inlineStr">
+        <is>
+          <t>David U Kalu</t>
+        </is>
+      </c>
+      <c r="E112" s="40" t="inlineStr">
+        <is>
+          <t>ets.enupancowest@gmail.com</t>
+        </is>
+      </c>
+      <c r="F112" s="40" t="inlineStr"/>
+      <c r="G112" s="40" t="inlineStr">
+        <is>
+          <t>+22898471050</t>
+        </is>
+      </c>
+      <c r="H112" s="40" t="inlineStr"/>
+      <c r="I112" s="39" t="inlineStr">
+        <is>
+          <t>Cooperation introduction</t>
+        </is>
+      </c>
+      <c r="J112" s="39" t="inlineStr"/>
+      <c r="L112" s="39" t="inlineStr"/>
+      <c r="N112" s="39" t="inlineStr"/>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="39" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="40" t="inlineStr">
+        <is>
+          <t>ABC Fruits</t>
+        </is>
+      </c>
+      <c r="C113" s="40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>Sharmila Banu (Export Sales)</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
+        <is>
+          <t>sharmila.banu@abcfruits.com</t>
+        </is>
+      </c>
+      <c r="F113" s="40" t="inlineStr"/>
+      <c r="G113" s="40" t="inlineStr"/>
+      <c r="H113" s="40" t="inlineStr"/>
+      <c r="I113" s="39" t="inlineStr">
+        <is>
+          <t>Gulfood meeting</t>
+        </is>
+      </c>
+      <c r="J113" s="39" t="inlineStr"/>
+      <c r="L113" s="39" t="inlineStr"/>
+      <c r="N113" s="39" t="inlineStr"/>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="39" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="40" t="inlineStr">
+        <is>
+          <t>REWE Far East Limited</t>
+        </is>
+      </c>
+      <c r="C114" s="40" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D114" s="40" t="inlineStr">
+        <is>
+          <t>Özlem Yarar</t>
+        </is>
+      </c>
+      <c r="E114" s="40" t="inlineStr">
+        <is>
+          <t>ozlem.yarar@rewe-fareast.com</t>
+        </is>
+      </c>
+      <c r="F114" s="40" t="inlineStr"/>
+      <c r="G114" s="40" t="inlineStr">
+        <is>
+          <t>00905423193883</t>
+        </is>
+      </c>
+      <c r="H114" s="40" t="inlineStr"/>
+      <c r="I114" s="39" t="inlineStr">
+        <is>
+          <t>Retailer sourcing inquiry</t>
+        </is>
+      </c>
+      <c r="J114" s="39" t="inlineStr"/>
+      <c r="L114" s="39" t="inlineStr"/>
+      <c r="N114" s="39" t="inlineStr"/>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="39" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="40" t="inlineStr">
+        <is>
+          <t>Ovorider</t>
+        </is>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>UAE/Jordan</t>
+        </is>
+      </c>
+      <c r="D115" s="40" t="inlineStr">
+        <is>
+          <t>Mohammed Al-Skooti</t>
+        </is>
+      </c>
+      <c r="E115" s="40" t="inlineStr">
+        <is>
+          <t>msk@ovorider.com</t>
+        </is>
+      </c>
+      <c r="F115" s="40" t="inlineStr"/>
+      <c r="G115" s="40" t="inlineStr">
+        <is>
+          <t>00962790389890</t>
+        </is>
+      </c>
+      <c r="H115" s="40" t="inlineStr"/>
+      <c r="I115" s="39" t="inlineStr">
+        <is>
+          <t>Product inquiry</t>
+        </is>
+      </c>
+      <c r="J115" s="39" t="inlineStr"/>
+      <c r="L115" s="39" t="inlineStr"/>
+      <c r="N115" s="39" t="inlineStr"/>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="39" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="40" t="inlineStr">
+        <is>
+          <t>Frutas do Mundo</t>
+        </is>
+      </c>
+      <c r="C116" s="40" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D116" s="40" t="inlineStr">
+        <is>
+          <t>Ricardo Pascal</t>
+        </is>
+      </c>
+      <c r="E116" s="40" t="inlineStr">
+        <is>
+          <t>comercial@frutasdomundo.com.br</t>
+        </is>
+      </c>
+      <c r="F116" s="40" t="inlineStr"/>
+      <c r="G116" s="40" t="inlineStr"/>
+      <c r="H116" s="40" t="inlineStr"/>
+      <c r="I116" s="39" t="inlineStr">
+        <is>
+          <t>Representation &amp; sales for Brazil</t>
+        </is>
+      </c>
+      <c r="J116" s="39" t="inlineStr"/>
+      <c r="L116" s="39" t="inlineStr"/>
+      <c r="N116" s="39" t="inlineStr"/>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="39" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="40" t="inlineStr">
+        <is>
+          <t>MJC co</t>
+        </is>
+      </c>
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="inlineStr">
+        <is>
+          <t>Maria Litvinova</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="inlineStr">
+        <is>
+          <t>mlitvinova.afc@gmail.com</t>
+        </is>
+      </c>
+      <c r="F117" s="40" t="inlineStr"/>
+      <c r="G117" s="40" t="inlineStr">
+        <is>
+          <t>+79817146772</t>
+        </is>
+      </c>
+      <c r="H117" s="40" t="inlineStr"/>
+      <c r="I117" s="39" t="inlineStr">
+        <is>
+          <t>Processing company - sourcing inquiry</t>
+        </is>
+      </c>
+      <c r="J117" s="39" t="inlineStr"/>
+      <c r="L117" s="39" t="inlineStr"/>
+      <c r="N117" s="39" t="inlineStr"/>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="39" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="40" t="inlineStr">
+        <is>
+          <t>Badger Ingredients / Ingredient Logistics</t>
+        </is>
+      </c>
+      <c r="C118" s="40" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D118" s="40" t="inlineStr">
+        <is>
+          <t>Maya Holling</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="inlineStr">
+        <is>
+          <t>maya@badgeringredients.com</t>
+        </is>
+      </c>
+      <c r="F118" s="40" t="inlineStr"/>
+      <c r="G118" s="40" t="inlineStr">
+        <is>
+          <t>(480) 404-9539 / (480) 639-8982</t>
+        </is>
+      </c>
+      <c r="H118" s="40" t="inlineStr"/>
+      <c r="I118" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries</t>
+        </is>
+      </c>
+      <c r="J118" s="39" t="inlineStr"/>
+      <c r="L118" s="39" t="inlineStr"/>
+      <c r="N118" s="39" t="inlineStr"/>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="39" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="40" t="inlineStr">
+        <is>
+          <t>City Run Group</t>
+        </is>
+      </c>
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="inlineStr"/>
+      <c r="E119" s="40" t="inlineStr">
+        <is>
+          <t>info@cityrungroup.com</t>
+        </is>
+      </c>
+      <c r="F119" s="40" t="inlineStr"/>
+      <c r="G119" s="40" t="inlineStr"/>
+      <c r="H119" s="40" t="inlineStr"/>
+      <c r="I119" s="39" t="inlineStr">
+        <is>
+          <t>Whole FD strawberries (Turkish client)</t>
+        </is>
+      </c>
+      <c r="J119" s="39" t="inlineStr"/>
+      <c r="L119" s="39" t="inlineStr"/>
+      <c r="N119" s="39" t="inlineStr"/>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="39" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="40" t="inlineStr">
+        <is>
+          <t>(US-based private label startup, ops UAE)</t>
+        </is>
+      </c>
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>USA/UAE</t>
+        </is>
+      </c>
+      <c r="D120" s="40" t="inlineStr">
+        <is>
+          <t>Alaa Mohamed Fouad</t>
+        </is>
+      </c>
+      <c r="E120" s="40" t="inlineStr">
+        <is>
+          <t>alaa.fouad@live.com</t>
+        </is>
+      </c>
+      <c r="F120" s="40" t="inlineStr"/>
+      <c r="G120" s="40" t="inlineStr"/>
+      <c r="H120" s="40" t="inlineStr"/>
+      <c r="I120" s="39" t="inlineStr">
+        <is>
+          <t>FD fruit private label/OEM export to US</t>
+        </is>
+      </c>
+      <c r="J120" s="39" t="inlineStr"/>
+      <c r="L120" s="39" t="inlineStr"/>
+      <c r="N120" s="39" t="inlineStr"/>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="39" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="40" t="inlineStr">
+        <is>
+          <t>Al Haraki Trading &amp; Commission</t>
+        </is>
+      </c>
+      <c r="C121" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D121" s="40" t="inlineStr">
+        <is>
+          <t>Raed Abutaim</t>
+        </is>
+      </c>
+      <c r="E121" s="40" t="inlineStr">
+        <is>
+          <t>abwtymrayd7@gmail.com</t>
+        </is>
+      </c>
+      <c r="F121" s="40" t="inlineStr"/>
+      <c r="G121" s="40" t="inlineStr"/>
+      <c r="H121" s="40" t="inlineStr"/>
+      <c r="I121" s="39" t="inlineStr">
+        <is>
+          <t>Strategic partnership offer</t>
+        </is>
+      </c>
+      <c r="J121" s="39" t="inlineStr"/>
+      <c r="L121" s="39" t="inlineStr"/>
+      <c r="N121" s="39" t="inlineStr"/>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="39" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="40" t="inlineStr">
+        <is>
+          <t>Vitachem</t>
+        </is>
+      </c>
+      <c r="C122" s="40" t="inlineStr"/>
+      <c r="D122" s="40" t="inlineStr">
+        <is>
+          <t>Eva Kreutzova</t>
+        </is>
+      </c>
+      <c r="E122" s="40" t="inlineStr">
+        <is>
+          <t>Kreutzova@vitachem.eu</t>
+        </is>
+      </c>
+      <c r="F122" s="40" t="inlineStr"/>
+      <c r="G122" s="40" t="inlineStr"/>
+      <c r="H122" s="40" t="inlineStr"/>
+      <c r="I122" s="39" t="inlineStr">
+        <is>
+          <t>Egypt visit / cooperation</t>
+        </is>
+      </c>
+      <c r="J122" s="39" t="inlineStr"/>
+      <c r="L122" s="39" t="inlineStr"/>
+      <c r="N122" s="39" t="inlineStr"/>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="39" t="n">
+        <v>119</v>
+      </c>
+      <c r="B123" s="40" t="inlineStr">
+        <is>
+          <t>(Buyer - Lagos)</t>
+        </is>
+      </c>
+      <c r="C123" s="40" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D123" s="40" t="inlineStr">
+        <is>
+          <t>Mohamad Khalil</t>
+        </is>
+      </c>
+      <c r="E123" s="40" t="inlineStr">
+        <is>
+          <t>mohamadkhalil970@gmail.com</t>
+        </is>
+      </c>
+      <c r="F123" s="40" t="inlineStr"/>
+      <c r="G123" s="40" t="inlineStr"/>
+      <c r="H123" s="40" t="inlineStr"/>
+      <c r="I123" s="39" t="inlineStr">
+        <is>
+          <t>Product info, prices, packaging</t>
+        </is>
+      </c>
+      <c r="J123" s="39" t="inlineStr"/>
+      <c r="L123" s="39" t="inlineStr"/>
+      <c r="N123" s="39" t="inlineStr"/>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="39" t="n">
+        <v>120</v>
+      </c>
+      <c r="B124" s="40" t="inlineStr">
+        <is>
+          <t>Garden Guru</t>
+        </is>
+      </c>
+      <c r="C124" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D124" s="40" t="inlineStr">
+        <is>
+          <t>Taha Azouz; Nesrine Hammady</t>
+        </is>
+      </c>
+      <c r="E124" s="40" t="inlineStr">
+        <is>
+          <t>taha.azouz@gardenguru-eg.com</t>
+        </is>
+      </c>
+      <c r="F124" s="40" t="inlineStr"/>
+      <c r="G124" s="40" t="inlineStr"/>
+      <c r="H124" s="40" t="inlineStr"/>
+      <c r="I124" s="39" t="inlineStr">
+        <is>
+          <t>FD strawberries 50 MT export to China (CIF Shanghai)</t>
+        </is>
+      </c>
+      <c r="J124" s="39" t="inlineStr"/>
+      <c r="L124" s="39" t="inlineStr"/>
+      <c r="N124" s="39" t="inlineStr"/>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="39" t="n">
+        <v>121</v>
+      </c>
+      <c r="B125" s="40" t="inlineStr">
+        <is>
+          <t>(US East Coast distributor)</t>
+        </is>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D125" s="40" t="inlineStr">
+        <is>
+          <t>Ayman Abdelaal</t>
+        </is>
+      </c>
+      <c r="E125" s="40" t="inlineStr">
+        <is>
+          <t>ayman.rashad@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F125" s="40" t="inlineStr"/>
+      <c r="G125" s="40" t="inlineStr"/>
+      <c r="H125" s="40" t="inlineStr"/>
+      <c r="I125" s="39" t="inlineStr">
+        <is>
+          <t>US East Coast distribution partnership</t>
+        </is>
+      </c>
+      <c r="J125" s="39" t="inlineStr"/>
+      <c r="L125" s="39" t="inlineStr"/>
+      <c r="N125" s="39" t="inlineStr"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="39" t="n">
+        <v>122</v>
+      </c>
+      <c r="B126" s="40" t="inlineStr">
+        <is>
+          <t>Fruzbi</t>
+        </is>
+      </c>
+      <c r="C126" s="40" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="D126" s="40" t="inlineStr">
+        <is>
+          <t>Anatolii Kondratenko</t>
+        </is>
+      </c>
+      <c r="E126" s="40" t="inlineStr">
+        <is>
+          <t>sales@fruzbi.com</t>
+        </is>
+      </c>
+      <c r="F126" s="40" t="inlineStr"/>
+      <c r="G126" s="40" t="inlineStr"/>
+      <c r="H126" s="40" t="inlineStr"/>
+      <c r="I126" s="39" t="inlineStr">
+        <is>
+          <t>FD strawberries whole 15-25mm (EU partner)</t>
+        </is>
+      </c>
+      <c r="J126" s="39" t="inlineStr"/>
+      <c r="L126" s="39" t="inlineStr"/>
+      <c r="N126" s="39" t="inlineStr"/>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="39" t="n">
+        <v>123</v>
+      </c>
+      <c r="B127" s="40" t="inlineStr">
+        <is>
+          <t>Anwar Moussa Almaliki (supplier)</t>
+        </is>
+      </c>
+      <c r="C127" s="40" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D127" s="40" t="inlineStr">
+        <is>
+          <t>Anwar Moussa Almaliki</t>
+        </is>
+      </c>
+      <c r="E127" s="40" t="inlineStr">
+        <is>
+          <t>anwarmuosa36@gmail.com</t>
+        </is>
+      </c>
+      <c r="F127" s="40" t="inlineStr"/>
+      <c r="G127" s="40" t="inlineStr">
+        <is>
+          <t>01014147590 / 01555087590</t>
+        </is>
+      </c>
+      <c r="H127" s="40" t="inlineStr"/>
+      <c r="I127" s="39" t="inlineStr">
+        <is>
+          <t>Supplier of fresh/frozen veg &amp; citrus to concentrate plants</t>
+        </is>
+      </c>
+      <c r="J127" s="39" t="inlineStr"/>
+      <c r="L127" s="39" t="inlineStr"/>
+      <c r="N127" s="39" t="inlineStr"/>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="39" t="n">
+        <v>124</v>
+      </c>
+      <c r="B128" s="40" t="inlineStr">
+        <is>
+          <t>Nutripur</t>
+        </is>
+      </c>
+      <c r="C128" s="40" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D128" s="40" t="inlineStr">
+        <is>
+          <t>T. Janson</t>
+        </is>
+      </c>
+      <c r="E128" s="40" t="inlineStr">
+        <is>
+          <t>TJanson@nutripur.eu</t>
+        </is>
+      </c>
+      <c r="F128" s="40" t="inlineStr"/>
+      <c r="G128" s="40" t="inlineStr"/>
+      <c r="H128" s="40" t="inlineStr"/>
+      <c r="I128" s="39" t="inlineStr">
+        <is>
+          <t>FD strawberries sliced 10,000 kg (offer request)</t>
+        </is>
+      </c>
+      <c r="J128" s="39" t="inlineStr"/>
+      <c r="L128" s="39" t="inlineStr"/>
+      <c r="N128" s="39" t="inlineStr"/>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="39" t="n">
+        <v>125</v>
+      </c>
+      <c r="B129" s="40" t="inlineStr">
+        <is>
+          <t>GreenField Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="C129" s="40" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="D129" s="40" t="inlineStr">
+        <is>
+          <t>Pawel Gucajtis; Daniel Polak</t>
+        </is>
+      </c>
+      <c r="E129" s="40" t="inlineStr">
+        <is>
+          <t>pawel.gucajtis@greenfield.waw.pl</t>
+        </is>
+      </c>
+      <c r="F129" s="40" t="inlineStr"/>
+      <c r="G129" s="40" t="inlineStr"/>
+      <c r="H129" s="40" t="inlineStr"/>
+      <c r="I129" s="39" t="inlineStr">
+        <is>
+          <t>Fruit waste/seeds after puree production (2026-28)</t>
+        </is>
+      </c>
+      <c r="J129" s="39" t="inlineStr"/>
+      <c r="L129" s="39" t="inlineStr"/>
+      <c r="N129" s="39" t="inlineStr"/>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="39" t="n">
+        <v>126</v>
+      </c>
+      <c r="B130" s="40" t="inlineStr">
+        <is>
+          <t>FAR WAY AGRO</t>
+        </is>
+      </c>
+      <c r="C130" s="40" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D130" s="40" t="inlineStr"/>
+      <c r="E130" s="40" t="inlineStr">
+        <is>
+          <t>import@farwayfresh.cn</t>
+        </is>
+      </c>
+      <c r="F130" s="40" t="inlineStr"/>
+      <c r="G130" s="40" t="inlineStr"/>
+      <c r="H130" s="40" t="inlineStr">
+        <is>
+          <t>Importer / distributor</t>
+        </is>
+      </c>
+      <c r="I130" s="39" t="inlineStr">
+        <is>
+          <t>Orange Juice Concentrate (demand 200MT/month; wants to be Chinese representative)</t>
+        </is>
+      </c>
+      <c r="J130" s="39" t="inlineStr"/>
+      <c r="L130" s="39" t="inlineStr"/>
+      <c r="N130" s="39" t="inlineStr"/>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="39" t="n">
+        <v>127</v>
+      </c>
+      <c r="B131" s="40" t="inlineStr">
+        <is>
+          <t>TRAWOSA AG</t>
+        </is>
+      </c>
+      <c r="C131" s="40" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D131" s="40" t="inlineStr">
+        <is>
+          <t>Michael Lang (Product Manager)</t>
+        </is>
+      </c>
+      <c r="E131" s="40" t="inlineStr">
+        <is>
+          <t>lang@trawosa.ch</t>
+        </is>
+      </c>
+      <c r="F131" s="40" t="inlineStr"/>
+      <c r="G131" s="40" t="inlineStr"/>
+      <c r="H131" s="40" t="inlineStr">
+        <is>
+          <t>Importer / trader</t>
+        </is>
+      </c>
+      <c r="I131" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries</t>
+        </is>
+      </c>
+      <c r="J131" s="39" t="inlineStr"/>
+      <c r="L131" s="39" t="inlineStr"/>
+      <c r="N131" s="39" t="inlineStr"/>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="39" t="n">
+        <v>128</v>
+      </c>
+      <c r="B132" s="40" t="inlineStr">
+        <is>
+          <t>Freeze-Dry-Foods GmbH</t>
+        </is>
+      </c>
+      <c r="C132" s="40" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D132" s="40" t="inlineStr">
+        <is>
+          <t>Claas Poessiger (Sales Director MEA)</t>
+        </is>
+      </c>
+      <c r="E132" s="40" t="inlineStr">
+        <is>
+          <t>cpoessiger@freeze-dry-foods.com</t>
+        </is>
+      </c>
+      <c r="F132" s="40" t="inlineStr"/>
+      <c r="G132" s="40" t="inlineStr"/>
+      <c r="H132" s="40" t="inlineStr">
+        <is>
+          <t>Manufacturer / trade-show contact (German Pavilion Hall 4 B4-57)</t>
+        </is>
+      </c>
+      <c r="I132" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried products</t>
+        </is>
+      </c>
+      <c r="J132" s="39" t="inlineStr"/>
+      <c r="L132" s="39" t="inlineStr"/>
+      <c r="N132" s="39" t="inlineStr"/>
+    </row>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="39" t="n">
+        <v>129</v>
+      </c>
+      <c r="B133" s="40" t="inlineStr">
+        <is>
+          <t>SunLeaf Foods</t>
+        </is>
+      </c>
+      <c r="C133" s="40" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D133" s="40" t="inlineStr">
+        <is>
+          <t>Angela Perez (Quality Assurance Manager)</t>
+        </is>
+      </c>
+      <c r="E133" s="40" t="inlineStr">
+        <is>
+          <t>aperez@sunleaffoods.com</t>
+        </is>
+      </c>
+      <c r="F133" s="40" t="inlineStr"/>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>+1 949</t>
+        </is>
+      </c>
+      <c r="H133" s="40" t="inlineStr">
+        <is>
+          <t>Importer / buyer</t>
+        </is>
+      </c>
+      <c r="I133" s="39" t="inlineStr">
+        <is>
+          <t>Collaboration / IQF &amp; fruit products (meeting scheduled)</t>
+        </is>
+      </c>
+      <c r="J133" s="39" t="inlineStr"/>
+      <c r="L133" s="39" t="inlineStr"/>
+      <c r="N133" s="39" t="inlineStr"/>
+    </row>
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="39" t="n">
+        <v>130</v>
+      </c>
+      <c r="B134" s="40" t="inlineStr">
+        <is>
+          <t>Fresh Apple Turkey</t>
+        </is>
+      </c>
+      <c r="C134" s="40" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D134" s="40" t="inlineStr">
+        <is>
+          <t>Furkan Col (Manager)</t>
+        </is>
+      </c>
+      <c r="E134" s="40" t="inlineStr">
+        <is>
+          <t>furkancol@freshappleturkey.com</t>
+        </is>
+      </c>
+      <c r="F134" s="40" t="inlineStr"/>
+      <c r="G134" s="40" t="inlineStr">
+        <is>
+          <t>+90 537 223 3</t>
+        </is>
+      </c>
+      <c r="H134" s="40" t="inlineStr">
+        <is>
+          <t>Importer / trader</t>
+        </is>
+      </c>
+      <c r="I134" s="39" t="inlineStr">
+        <is>
+          <t>IQF mango 20x20 chunks (zebdya variety), 1x24t container</t>
+        </is>
+      </c>
+      <c r="J134" s="39" t="inlineStr"/>
+      <c r="L134" s="39" t="inlineStr"/>
+      <c r="N134" s="39" t="inlineStr"/>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="39" t="n">
+        <v>131</v>
+      </c>
+      <c r="B135" s="40" t="inlineStr">
+        <is>
+          <t>Hellenic Juice Industry C. Dedes ASPIS S.A.</t>
+        </is>
+      </c>
+      <c r="C135" s="40" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="D135" s="40" t="inlineStr">
+        <is>
+          <t>Mario Chronis (General Manager)</t>
+        </is>
+      </c>
+      <c r="E135" s="40" t="inlineStr">
+        <is>
+          <t>m.chronis@aspis.gr</t>
+        </is>
+      </c>
+      <c r="F135" s="40" t="inlineStr"/>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>+30 2751028004</t>
+        </is>
+      </c>
+      <c r="H135" s="40" t="inlineStr">
+        <is>
+          <t>Juice manufacturer / buyer</t>
+        </is>
+      </c>
+      <c r="I135" s="39" t="inlineStr">
+        <is>
+          <t>IQF strawberry</t>
+        </is>
+      </c>
+      <c r="J135" s="39" t="inlineStr"/>
+      <c r="L135" s="39" t="inlineStr"/>
+      <c r="N135" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="245">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L17:M17"/>
+  <mergeCells count="410">
+    <mergeCell ref="N101:O101"/>
     <mergeCell ref="N2:O5"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N11:O11"/>
     <mergeCell ref="N76:O76"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="N113:O113"/>
+    <mergeCell ref="N100:O100"/>
+    <mergeCell ref="N94:O94"/>
     <mergeCell ref="J59:K59"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="L75:M75"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N68:O68"/>
     <mergeCell ref="N77:O77"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="L102:M102"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L29:M29"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N29:O29"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="N89:O89"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="J120:K120"/>
+    <mergeCell ref="L120:M120"/>
+    <mergeCell ref="L107:M107"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="L121:M121"/>
+    <mergeCell ref="N121:O121"/>
+    <mergeCell ref="N115:O115"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="N102:O102"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="N116:O116"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L103:M103"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="L134:M134"/>
+    <mergeCell ref="N134:O134"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="N96:O96"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L129:M129"/>
+    <mergeCell ref="L123:M123"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="N123:O123"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L124:M124"/>
+    <mergeCell ref="N124:O124"/>
+    <mergeCell ref="N118:O118"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="N126:O126"/>
+    <mergeCell ref="N109:O109"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="J112:K112"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="J127:K127"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="L119:M119"/>
+    <mergeCell ref="N119:O119"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="N114:O114"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="L130:M130"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="N130:O130"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="N117:O117"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L132:M132"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L81:M81"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J110:K110"/>
+    <mergeCell ref="L110:M110"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N122:O122"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="L94:M94"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="J125:K125"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N133:O133"/>
+    <mergeCell ref="N135:O135"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J131:K131"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L88:M88"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L126:M126"/>
+    <mergeCell ref="N82:O82"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="J113:K113"/>
+    <mergeCell ref="L113:M113"/>
+    <mergeCell ref="L100:M100"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J121:K121"/>
+    <mergeCell ref="J115:K115"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="N108:O108"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="L95:M95"/>
+    <mergeCell ref="N95:O95"/>
+    <mergeCell ref="L131:M131"/>
+    <mergeCell ref="J116:K116"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L97:M97"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N97:O97"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="N88:O88"/>
+    <mergeCell ref="J124:K124"/>
+    <mergeCell ref="J109:K109"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="L96:M96"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="N90:O90"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N83:O83"/>
+    <mergeCell ref="L91:M91"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N91:O91"/>
+    <mergeCell ref="N85:O85"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="L116:M116"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L118:M118"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="N111:O111"/>
     <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L109:M109"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="N38:O38"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="E2:E5"/>
-    <mergeCell ref="L79:M79"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="L122:M122"/>
     <mergeCell ref="L40:M40"/>
     <mergeCell ref="N40:O40"/>
-    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J134:K134"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="N79:O79"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="L98:M98"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L106:M106"/>
+    <mergeCell ref="L93:M93"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L111:M111"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N104:O104"/>
+    <mergeCell ref="L125:M125"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="L112:M112"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N112:O112"/>
+    <mergeCell ref="N106:O106"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="N105:O105"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="N107:O107"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="L114:M114"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="N132:O132"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="J118:K118"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="N110:O110"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="N125:O125"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="L87:M87"/>
+    <mergeCell ref="J123:K123"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L133:M133"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="N127:O127"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="N120:O120"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L128:M128"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="N128:O128"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J126:K126"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="L82:M82"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="J108:K108"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="N103:O103"/>
     <mergeCell ref="L72:M72"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="J71:K71"/>
     <mergeCell ref="L65:M65"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J58:K58"/>
     <mergeCell ref="N65:O65"/>
-    <mergeCell ref="N79:O79"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="J64:K64"/>
-    <mergeCell ref="N35:O35"/>
     <mergeCell ref="L7:M7"/>
-    <mergeCell ref="J73:K73"/>
     <mergeCell ref="N7:O7"/>
-    <mergeCell ref="L16:M16"/>
     <mergeCell ref="N63:O63"/>
-    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N129:O129"/>
     <mergeCell ref="N50:O50"/>
     <mergeCell ref="N25:O25"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="N131:O131"/>
+    <mergeCell ref="J117:K117"/>
     <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J132:K132"/>
+    <mergeCell ref="L83:M83"/>
+    <mergeCell ref="J119:K119"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="N44:O44"/>
     <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N67:O67"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="L85:M85"/>
     <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="L84:M84"/>
     <mergeCell ref="N13:O13"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="N84:O84"/>
     <mergeCell ref="N78:O78"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="J114:K114"/>
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="L80:M80"/>
     <mergeCell ref="N80:O80"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="L61:M61"/>
     <mergeCell ref="N55:O55"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J111:K111"/>
     <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="L47:M47"/>
     <mergeCell ref="J40:K40"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L18:M18"/>
     <mergeCell ref="L33:M33"/>
-    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N58:O58"/>
     <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="J65:K65"/>
     <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J74:K74"/>
     <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="L26:M26"/>
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="J16:K16"/>
     <mergeCell ref="L10:M10"/>
-    <mergeCell ref="J25:K25"/>
     <mergeCell ref="N10:O10"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="J91:K91"/>
     <mergeCell ref="J66:K66"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="J133:K133"/>
+    <mergeCell ref="J130:K130"/>
+    <mergeCell ref="J135:K135"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="L135:M135"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="J122:K122"/>
     <mergeCell ref="J72:K72"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="L101:M101"/>
     <mergeCell ref="J30:K30"/>
-    <mergeCell ref="N72:O72"/>
     <mergeCell ref="N21:O21"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="N81:O81"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="N23:O23"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="J104:K104"/>
+    <mergeCell ref="L104:M104"/>
     <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J7:K7"/>
     <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L1:M1"/>
     <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="L63:M63"/>
     <mergeCell ref="L41:M41"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="J47:K47"/>
     <mergeCell ref="J56:K56"/>
     <mergeCell ref="L56:M56"/>
+    <mergeCell ref="J105:K105"/>
     <mergeCell ref="L34:M34"/>
     <mergeCell ref="J43:K43"/>
+    <mergeCell ref="L105:M105"/>
     <mergeCell ref="N34:O34"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L99:M99"/>
+    <mergeCell ref="N99:O99"/>
     <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="N74:O74"/>
     <mergeCell ref="N49:O49"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="N27:O27"/>
     <mergeCell ref="L36:M36"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="J8:K8"/>
     <mergeCell ref="N36:O36"/>
-    <mergeCell ref="J17:K17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>

--- a/Generic_Requests_filled.xlsx
+++ b/Generic_Requests_filled.xlsx
@@ -972,7 +972,7 @@
       <c r="N5" s="34" t="n"/>
       <c r="O5" s="35" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="36" t="n">
         <v>2</v>
       </c>
@@ -1008,14 +1008,26 @@
           <t>Bulk freeze-dried fruits</t>
         </is>
       </c>
-      <c r="J6" s="36" t="inlineStr"/>
+      <c r="J6" s="36" t="inlineStr">
+        <is>
+          <t>Tiered per SKU: 100-250 kg trial / 500-1,000 kg / 1,500-2,500 kg / 8,000+ kg full container</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="n"/>
-      <c r="L6" s="36" t="inlineStr"/>
+      <c r="L6" s="36" t="inlineStr">
+        <is>
+          <t>Bulk FD fruits, all varieties (berries, tropical, stone, dates, exotic), whole &amp; sliced; moisture &lt;5%; bulk aluminium-foil laminate w/ nitrogen flush, OEM/retail-ready option</t>
+        </is>
+      </c>
       <c r="M6" s="38" t="n"/>
-      <c r="N6" s="36" t="inlineStr"/>
+      <c r="N6" s="36" t="inlineStr">
+        <is>
+          <t>FOB &amp; CIF Jeddah pricing; SFDA compliance; certs ISO22000/HACCP/FSSC22000, Halal, CoA, heavy-metals, pesticide &amp; micro reports; terms 30% deposit/70% vs B/L copy; M +966 547330506</t>
+        </is>
+      </c>
       <c r="O6" s="38" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="36" t="n">
         <v>3</v>
       </c>
@@ -1051,14 +1063,26 @@
           <t>Freeze-dried fruits</t>
         </is>
       </c>
-      <c r="J7" s="36" t="inlineStr"/>
+      <c r="J7" s="36" t="inlineStr">
+        <is>
+          <t>MOQ requested (not stated)</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="n"/>
-      <c r="L7" s="36" t="inlineStr"/>
+      <c r="L7" s="36" t="inlineStr">
+        <is>
+          <t>FD strawberry (whole/pieces/slices/powder), blueberry, raspberry, cherry, black/red currant, pineapple, fig, peach, dragon fruit, kiwi, peas, corn; EU-compliant</t>
+        </is>
+      </c>
       <c r="M7" s="38" t="n"/>
-      <c r="N7" s="36" t="inlineStr"/>
+      <c r="N7" s="36" t="inlineStr">
+        <is>
+          <t>Wants catalogue + wholesale price list, MOQ, packaging options; long-term; Mob +370 687 32276</t>
+        </is>
+      </c>
       <c r="O7" s="38" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="36" t="n">
         <v>4</v>
       </c>
@@ -1096,12 +1120,20 @@
       </c>
       <c r="J8" s="36" t="inlineStr"/>
       <c r="K8" s="38" t="n"/>
-      <c r="L8" s="36" t="inlineStr"/>
+      <c r="L8" s="36" t="inlineStr">
+        <is>
+          <t>Orange &amp; lemon juice concentrate, Brix 60-65%</t>
+        </is>
+      </c>
       <c r="M8" s="38" t="n"/>
-      <c r="N8" s="36" t="inlineStr"/>
+      <c r="N8" s="36" t="inlineStr">
+        <is>
+          <t>Best offer requested; Al Safwa Group; tel 01020958645; al-safwagroup.com</t>
+        </is>
+      </c>
       <c r="O8" s="38" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="36" t="n">
         <v>5</v>
       </c>
@@ -1144,7 +1176,7 @@
       <c r="N9" s="36" t="inlineStr"/>
       <c r="O9" s="38" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" s="36" t="n">
         <v>6</v>
       </c>
@@ -1168,14 +1200,26 @@
           <t>Orange juice concentrate (RFQ)</t>
         </is>
       </c>
-      <c r="J10" s="36" t="inlineStr"/>
+      <c r="J10" s="36" t="inlineStr">
+        <is>
+          <t>25 MT</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="n"/>
-      <c r="L10" s="36" t="inlineStr"/>
+      <c r="L10" s="36" t="inlineStr">
+        <is>
+          <t>FCOJ Brix 65 +/-1, acid/sugar ratio 12-15, pulp &lt;6%, high aroma &amp; cloud stability, Valencia oranges; 200-250 L steel drums w/ aseptic liner</t>
+        </is>
+      </c>
       <c r="M10" s="38" t="n"/>
-      <c r="N10" s="36" t="inlineStr"/>
+      <c r="N10" s="36" t="inlineStr">
+        <is>
+          <t>CIF Aden Port (Yemen); SGF + ISO22000/HACCP; L/C at sight; offer valid 15 days; deadline 15 May 2026; pre-shipment sample; +967 775289989</t>
+        </is>
+      </c>
       <c r="O10" s="38" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="46" customHeight="1">
       <c r="A11" s="36" t="n">
         <v>7</v>
       </c>
@@ -1211,14 +1255,26 @@
           <t>NFC juices (samples + quotation)</t>
         </is>
       </c>
-      <c r="J11" s="36" t="inlineStr"/>
+      <c r="J11" s="36" t="inlineStr">
+        <is>
+          <t>40 ft container (initial/annual)</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="n"/>
-      <c r="L11" s="36" t="inlineStr"/>
+      <c r="L11" s="36" t="inlineStr">
+        <is>
+          <t>NFC juices in ready-to-sell 495 ml bottles / Tetra / aluminium cans, all flavours; samples for R&amp;D/private label</t>
+        </is>
+      </c>
       <c r="M11" s="38" t="n"/>
-      <c r="N11" s="36" t="inlineStr"/>
+      <c r="N11" s="36" t="inlineStr">
+        <is>
+          <t>FOB Alexandria; destination Port of Los Angeles; FDA compliance; +1 626 230 3697</t>
+        </is>
+      </c>
       <c r="O11" s="38" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="46" customHeight="1">
       <c r="A12" s="36" t="n">
         <v>8</v>
       </c>
@@ -1246,14 +1302,26 @@
           <t>Frozen strawberries, mango, puree</t>
         </is>
       </c>
-      <c r="J12" s="36" t="inlineStr"/>
+      <c r="J12" s="36" t="inlineStr">
+        <is>
+          <t>Open to volume commitment after offer (RFQ, FOB $/MT)</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="n"/>
-      <c r="L12" s="36" t="inlineStr"/>
+      <c r="L12" s="36" t="inlineStr">
+        <is>
+          <t>IQF strawberries 1 kg/pack (Fortuna/Festival/Sensation, Grade A/B/BC, calibrated 15-25 &amp; 25-35); frozen mango slices/cubes (Zebdya/Kent) 1 kg; mango puree 1 kg; strawberry puree 1 kg</t>
+        </is>
+      </c>
       <c r="M12" s="38" t="n"/>
-      <c r="N12" s="36" t="inlineStr"/>
+      <c r="N12" s="36" t="inlineStr">
+        <is>
+          <t>FOB price/MT; certs ISO22000/GLOBALG.A.P./HACCP/Halal/BRC; COA &amp; MRLs; Italian shareholding; plans New Cairo office visit; +216 53531335</t>
+        </is>
+      </c>
       <c r="O12" s="38" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="36" t="n">
         <v>9</v>
       </c>
@@ -1287,12 +1355,20 @@
       </c>
       <c r="J13" s="36" t="inlineStr"/>
       <c r="K13" s="38" t="n"/>
-      <c r="L13" s="36" t="inlineStr"/>
+      <c r="L13" s="36" t="inlineStr">
+        <is>
+          <t>Supplier-side offer (not a buyer RFQ): Non-Dairy Creamer/fat-filled powder; Fruit &amp; Vegetable powders (mango, banana, beetroot, spinach); natural extracts &amp; colors; coconut/dairy ingredients; maltodextrin</t>
+        </is>
+      </c>
       <c r="M13" s="38" t="n"/>
-      <c r="N13" s="36" t="inlineStr"/>
+      <c r="N13" s="36" t="inlineStr">
+        <is>
+          <t>Met at Gulfood Dubai 2026; product catalogue attached; offers samples &amp; custom formulations; asks for MAFI's requirements; from Harshit Shukla, Venkatesh, India</t>
+        </is>
+      </c>
       <c r="O13" s="38" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="46" customHeight="1">
       <c r="A14" s="36" t="n">
         <v>10</v>
       </c>
@@ -1324,14 +1400,26 @@
           <t>Freeze-dried strawberries (15-25mm, 5 tons CIF Mersin)</t>
         </is>
       </c>
-      <c r="J14" s="36" t="inlineStr"/>
+      <c r="J14" s="36" t="inlineStr">
+        <is>
+          <t>5 tons</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="n"/>
-      <c r="L14" s="36" t="inlineStr"/>
+      <c r="L14" s="36" t="inlineStr">
+        <is>
+          <t>FD strawberries, 15-25 mm festival calibrated</t>
+        </is>
+      </c>
       <c r="M14" s="38" t="n"/>
-      <c r="N14" s="36" t="inlineStr"/>
+      <c r="N14" s="36" t="inlineStr">
+        <is>
+          <t>CIF Mersin; also exploring IQF (Gulfood 2026 follow-up) &amp; market availability; M +90 542 761 5459</t>
+        </is>
+      </c>
       <c r="O14" s="38" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="46" customHeight="1">
       <c r="A15" s="36" t="n">
         <v>11</v>
       </c>
@@ -1363,14 +1451,26 @@
           <t>Fruit juice concentrates &amp; tomato paste</t>
         </is>
       </c>
-      <c r="J15" s="36" t="inlineStr"/>
+      <c r="J15" s="36" t="inlineStr">
+        <is>
+          <t>20ft container = 86 drums x 270 kg</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="n"/>
-      <c r="L15" s="36" t="inlineStr"/>
+      <c r="L15" s="36" t="inlineStr">
+        <is>
+          <t>Supplier-side offer (not a buyer RFQ): pomegranate, apple, sour cherry, date juice concentrates &amp; tomato paste; aseptic bags in drums</t>
+        </is>
+      </c>
       <c r="M15" s="38" t="n"/>
-      <c r="N15" s="36" t="inlineStr"/>
+      <c r="N15" s="36" t="inlineStr">
+        <is>
+          <t>CFR Alexandria/Damietta; ETD 7-10 days after order, ETA Egypt ~32-35 days; met Mr. Amr Medany at Gulfood; Hojat Abdolahi, Dubai, +971569736002</t>
+        </is>
+      </c>
       <c r="O15" s="38" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="46" customHeight="1">
       <c r="A16" s="36" t="n">
         <v>12</v>
       </c>
@@ -1406,14 +1506,26 @@
           <t>Wet strawberry/blackberry/kiwi pomace &amp; seeds (20-200 tons)</t>
         </is>
       </c>
-      <c r="J16" s="36" t="inlineStr"/>
+      <c r="J16" s="36" t="inlineStr">
+        <is>
+          <t>20 to 200 tons of each by-product</t>
+        </is>
+      </c>
       <c r="K16" s="38" t="n"/>
-      <c r="L16" s="36" t="inlineStr"/>
+      <c r="L16" s="36" t="inlineStr">
+        <is>
+          <t>Wet strawberry pomace/seeds (from puree production), wet blackberry pomace, wet kiwi pomace (from puree/NFC/concentrate); packed frozen in used drums</t>
+        </is>
+      </c>
       <c r="M16" s="38" t="n"/>
-      <c r="N16" s="36" t="inlineStr"/>
+      <c r="N16" s="36" t="inlineStr">
+        <is>
+          <t>Requests price offer, available qty, photos, lead time; buying strawberry now as season started; upcycling/circular economy; Daniel Polak, GreenField Poland, WhatsApp +48 510 410 180</t>
+        </is>
+      </c>
       <c r="O16" s="38" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="46" customHeight="1">
       <c r="A17" s="36" t="n">
         <v>13</v>
       </c>
@@ -1453,14 +1565,26 @@
           <t>Conventional FD fruits</t>
         </is>
       </c>
-      <c r="J17" s="36" t="inlineStr"/>
+      <c r="J17" s="36" t="inlineStr">
+        <is>
+          <t>~50 tons/year; orders by full 40ft FCL container</t>
+        </is>
+      </c>
       <c r="K17" s="38" t="n"/>
-      <c r="L17" s="36" t="inlineStr"/>
+      <c r="L17" s="36" t="inlineStr">
+        <is>
+          <t>Conventional FD strawberry slices 5-7mm (also dices 5-10mm or mix); max 5-7% moisture, max 5% dust; no sugar/additives, 100% fruit, no pesticide residue; requests current price offer</t>
+        </is>
+      </c>
       <c r="M17" s="38" t="n"/>
-      <c r="N17" s="36" t="inlineStr"/>
+      <c r="N17" s="36" t="inlineStr">
+        <is>
+          <t>Kosher certified, gluten up to 10ppm; DAP Czech Republic, Hrdly 412 01; long-term cooperation; Jakub Fric, Emco, +420 771 257 818</t>
+        </is>
+      </c>
       <c r="O17" s="38" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="46" customHeight="1">
       <c r="A18" s="36" t="n">
         <v>14</v>
       </c>
@@ -1494,12 +1618,20 @@
       </c>
       <c r="J18" s="36" t="inlineStr"/>
       <c r="K18" s="38" t="n"/>
-      <c r="L18" s="36" t="inlineStr"/>
+      <c r="L18" s="36" t="inlineStr">
+        <is>
+          <t>Freeze-dried whole strawberries; requests product catalog and pricing</t>
+        </is>
+      </c>
       <c r="M18" s="38" t="n"/>
-      <c r="N18" s="36" t="inlineStr"/>
+      <c r="N18" s="36" t="inlineStr">
+        <is>
+          <t>EU food law compliance and delivery details requested; Pelian Lab Greece (healthy snacking); Nasos Drakopoulos</t>
+        </is>
+      </c>
       <c r="O18" s="38" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="46" customHeight="1">
       <c r="A19" s="36" t="n">
         <v>15</v>
       </c>
@@ -1542,7 +1674,7 @@
       <c r="N19" s="36" t="inlineStr"/>
       <c r="O19" s="38" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="46" customHeight="1">
       <c r="A20" s="36" t="n">
         <v>16</v>
       </c>
@@ -1580,12 +1712,20 @@
       </c>
       <c r="J20" s="36" t="inlineStr"/>
       <c r="K20" s="38" t="n"/>
-      <c r="L20" s="36" t="inlineStr"/>
+      <c r="L20" s="36" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries, blueberries, raspberries, cherries; particularly interested in whole raspberries; requests product range details</t>
+        </is>
+      </c>
       <c r="M20" s="38" t="n"/>
-      <c r="N20" s="36" t="inlineStr"/>
+      <c r="N20" s="36" t="inlineStr">
+        <is>
+          <t>Met at SIAL Paris 2024; has several customers interested; LitSupply (food raw materials supplier); Justinas Grazelis</t>
+        </is>
+      </c>
       <c r="O20" s="38" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="46" customHeight="1">
       <c r="A21" s="36" t="n">
         <v>17</v>
       </c>
@@ -1628,7 +1768,7 @@
       <c r="N21" s="36" t="inlineStr"/>
       <c r="O21" s="38" t="n"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="46" customHeight="1">
       <c r="A22" s="36" t="n">
         <v>18</v>
       </c>
@@ -1660,14 +1800,26 @@
           <t>Freeze-dried sliced strawberries (100-500kg)</t>
         </is>
       </c>
-      <c r="J22" s="36" t="inlineStr"/>
+      <c r="J22" s="36" t="inlineStr">
+        <is>
+          <t>100-500 kg</t>
+        </is>
+      </c>
       <c r="K22" s="38" t="n"/>
-      <c r="L22" s="36" t="inlineStr"/>
+      <c r="L22" s="36" t="inlineStr">
+        <is>
+          <t>Freeze-dried sliced strawberries, in bulk cartons; requests quote and a sample before buying</t>
+        </is>
+      </c>
       <c r="M22" s="38" t="n"/>
-      <c r="N22" s="36" t="inlineStr"/>
+      <c r="N22" s="36" t="inlineStr">
+        <is>
+          <t>Ship to Texas, likely Port of Houston; samples to CTD Sports, 5784 Sapp Road, Conroe, TX 77304, USA; Peter</t>
+        </is>
+      </c>
       <c r="O22" s="38" t="n"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="46" customHeight="1">
       <c r="A23" s="36" t="n">
         <v>19</v>
       </c>
@@ -1703,14 +1855,26 @@
           <t>Freeze-dried fruits / frozen mango</t>
         </is>
       </c>
-      <c r="J23" s="36" t="inlineStr"/>
+      <c r="J23" s="36" t="inlineStr">
+        <is>
+          <t>100 kg of each fruit ideally to start</t>
+        </is>
+      </c>
       <c r="K23" s="38" t="n"/>
-      <c r="L23" s="36" t="inlineStr"/>
+      <c r="L23" s="36" t="inlineStr">
+        <is>
+          <t>Freeze-dried fruits: strawberries, figs, orange, raspberry, blueberry, mulberry, pineapple, lemon; private labeling; requests prices</t>
+        </is>
+      </c>
       <c r="M23" s="38" t="n"/>
-      <c r="N23" s="36" t="inlineStr"/>
+      <c r="N23" s="36" t="inlineStr">
+        <is>
+          <t>Private label inquiry; prefers WhatsApp; Patrick, Sales Manager, Ginju, +1 (514) 299-1111, www.ginju.ca</t>
+        </is>
+      </c>
       <c r="O23" s="38" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="46" customHeight="1">
       <c r="A24" s="36" t="n">
         <v>20</v>
       </c>
@@ -1753,7 +1917,7 @@
       <c r="N24" s="36" t="inlineStr"/>
       <c r="O24" s="38" t="n"/>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="46" customHeight="1">
       <c r="A25" s="36" t="n">
         <v>21</v>
       </c>
@@ -1796,7 +1960,7 @@
       <c r="N25" s="36" t="inlineStr"/>
       <c r="O25" s="38" t="n"/>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="46" customHeight="1">
       <c r="A26" s="36" t="n">
         <v>22</v>
       </c>
@@ -1831,7 +1995,7 @@
       <c r="N26" s="36" t="inlineStr"/>
       <c r="O26" s="38" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="46" customHeight="1">
       <c r="A27" s="36" t="n">
         <v>23</v>
       </c>
@@ -1874,7 +2038,7 @@
       <c r="N27" s="36" t="inlineStr"/>
       <c r="O27" s="38" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="46" customHeight="1">
       <c r="A28" s="39" t="n">
         <v>24</v>
       </c>
@@ -1914,7 +2078,7 @@
       <c r="L28" s="39" t="inlineStr"/>
       <c r="N28" s="39" t="inlineStr"/>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="46" customHeight="1">
       <c r="A29" s="39" t="n">
         <v>25</v>
       </c>
@@ -1954,7 +2118,7 @@
       <c r="L29" s="39" t="inlineStr"/>
       <c r="N29" s="39" t="inlineStr"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="46" customHeight="1">
       <c r="A30" s="39" t="n">
         <v>26</v>
       </c>
@@ -1990,7 +2154,7 @@
       <c r="L30" s="39" t="inlineStr"/>
       <c r="N30" s="39" t="inlineStr"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="46" customHeight="1">
       <c r="A31" s="39" t="n">
         <v>27</v>
       </c>
@@ -2030,7 +2194,7 @@
       <c r="L31" s="39" t="inlineStr"/>
       <c r="N31" s="39" t="inlineStr"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="46" customHeight="1">
       <c r="A32" s="39" t="n">
         <v>28</v>
       </c>
@@ -2063,10 +2227,18 @@
         </is>
       </c>
       <c r="J32" s="39" t="inlineStr"/>
-      <c r="L32" s="39" t="inlineStr"/>
-      <c r="N32" s="39" t="inlineStr"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+      <c r="L32" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberry slices and freeze-dried raspberries; requests product catalog, price list and MOQs</t>
+        </is>
+      </c>
+      <c r="N32" s="39" t="inlineStr">
+        <is>
+          <t>Terms of cooperation requested; Polish company; Kamil Krzywonos, CEO, BILOW sp. z o.o., Rzeszow, +48 791 523 861</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
       <c r="A33" s="39" t="n">
         <v>29</v>
       </c>
@@ -2102,7 +2274,7 @@
       <c r="L33" s="39" t="inlineStr"/>
       <c r="N33" s="39" t="inlineStr"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="46" customHeight="1">
       <c r="A34" s="39" t="n">
         <v>30</v>
       </c>
@@ -2138,7 +2310,7 @@
       <c r="L34" s="39" t="inlineStr"/>
       <c r="N34" s="39" t="inlineStr"/>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="46" customHeight="1">
       <c r="A35" s="39" t="n">
         <v>31</v>
       </c>
@@ -2174,7 +2346,7 @@
       <c r="L35" s="39" t="inlineStr"/>
       <c r="N35" s="39" t="inlineStr"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="46" customHeight="1">
       <c r="A36" s="39" t="n">
         <v>32</v>
       </c>
@@ -2207,10 +2379,18 @@
         </is>
       </c>
       <c r="J36" s="39" t="inlineStr"/>
-      <c r="L36" s="39" t="inlineStr"/>
-      <c r="N36" s="39" t="inlineStr"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+      <c r="L36" s="39" t="inlineStr">
+        <is>
+          <t>FC Orange Juice (66 Brix) and NFC orange juice; also other FC/NFC fruit juices with supply-chain advantages; requests quotation, MOQ, product info</t>
+        </is>
+      </c>
+      <c r="N36" s="39" t="inlineStr">
+        <is>
+          <t>FOB/CIF Main Chinese Ports; requests delivery time and payment terms; Alex Gao, Leyuan Health Technology, Hangzhou China; company intro PDF attached</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="46" customHeight="1">
       <c r="A37" s="39" t="n">
         <v>33</v>
       </c>
@@ -2246,7 +2426,7 @@
       <c r="L37" s="39" t="inlineStr"/>
       <c r="N37" s="39" t="inlineStr"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="46" customHeight="1">
       <c r="A38" s="39" t="n">
         <v>34</v>
       </c>
@@ -2274,11 +2454,23 @@
           <t>FD strawberries (slices, ~3 tonnes/yr)</t>
         </is>
       </c>
-      <c r="J38" s="39" t="inlineStr"/>
-      <c r="L38" s="39" t="inlineStr"/>
-      <c r="N38" s="39" t="inlineStr"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+      <c r="J38" s="39" t="inlineStr">
+        <is>
+          <t>~3 tonnes per annum (sliced strawberries)</t>
+        </is>
+      </c>
+      <c r="L38" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried fruit; sliced strawberries; asks whether other fruits beyond strawberries are freeze-dried; requests price</t>
+        </is>
+      </c>
+      <c r="N38" s="39" t="inlineStr">
+        <is>
+          <t>Czech Republic food importer/distributor to ~400 stores; wants to start importing freeze-dried fruit; received brochure; Jaroslav</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="46" customHeight="1">
       <c r="A39" s="39" t="n">
         <v>35</v>
       </c>
@@ -2315,10 +2507,18 @@
         </is>
       </c>
       <c r="J39" s="39" t="inlineStr"/>
-      <c r="L39" s="39" t="inlineStr"/>
-      <c r="N39" s="39" t="inlineStr"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+      <c r="L39" s="39" t="inlineStr">
+        <is>
+          <t>Private label/OEM dried strawberries &amp; bananas and fruit purees; requests MOQs, pricing structure (tiered + setup fees), packaging/custom branding capabilities</t>
+        </is>
+      </c>
+      <c r="N39" s="39" t="inlineStr">
+        <is>
+          <t>Lead times &amp; export compliance certs (ISO, HACCP, FDA, BRC) for EU &amp; Gulf/GCC markets; two-phase local-then-export rollout; Mohamed Fathy Helal, Alfa Trans, Cairo, +20227515755 / +201005622232; requests intro call</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="46" customHeight="1">
       <c r="A40" s="39" t="n">
         <v>36</v>
       </c>
@@ -2347,10 +2547,18 @@
         </is>
       </c>
       <c r="J40" s="39" t="inlineStr"/>
-      <c r="L40" s="39" t="inlineStr"/>
-      <c r="N40" s="39" t="inlineStr"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
+      <c r="L40" s="39" t="inlineStr">
+        <is>
+          <t>Private label juice (own brand)</t>
+        </is>
+      </c>
+      <c r="N40" s="39" t="inlineStr">
+        <is>
+          <t>Wants to import to Malawi; requests WhatsApp contact; Muhammed from Malawi (+265...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="46" customHeight="1">
       <c r="A41" s="39" t="n">
         <v>37</v>
       </c>
@@ -2386,11 +2594,23 @@
           <t>Product inquiry</t>
         </is>
       </c>
-      <c r="J41" s="39" t="inlineStr"/>
-      <c r="L41" s="39" t="inlineStr"/>
-      <c r="N41" s="39" t="inlineStr"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+      <c r="J41" s="39" t="inlineStr">
+        <is>
+          <t>25 MT every 2 months; yearly contract basis with scalable volume</t>
+        </is>
+      </c>
+      <c r="L41" s="39" t="inlineStr">
+        <is>
+          <t>Frozen NFC Lemon Juice (not from concentrate), 100% natural no additives; specs needed Brix, acidity %citric, pH, pulp content, color, shelf life, storage -18C; also Frozen Ginger Juice (NFC/extracted); packaging food-grade HDPE buckets 10-20 L</t>
+        </is>
+      </c>
+      <c r="N41" s="39" t="inlineStr">
+        <is>
+          <t>FOB Alexandria/Damietta/Port Said; CIF Jebel Ali, UAE; immediate shipment; payment advance + balance vs shipping docs (negotiable); docs TDS, COA, ISO/HACCP/Halal; Al Malaky Royal, UAE; Tel 0523525206</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="46" customHeight="1">
       <c r="A42" s="39" t="n">
         <v>38</v>
       </c>
@@ -2422,7 +2642,7 @@
       <c r="L42" s="39" t="inlineStr"/>
       <c r="N42" s="39" t="inlineStr"/>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" ht="46" customHeight="1">
       <c r="A43" s="39" t="n">
         <v>39</v>
       </c>
@@ -2454,7 +2674,7 @@
       <c r="L43" s="39" t="inlineStr"/>
       <c r="N43" s="39" t="inlineStr"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="46" customHeight="1">
       <c r="A44" s="39" t="n">
         <v>40</v>
       </c>
@@ -2490,7 +2710,7 @@
       <c r="L44" s="39" t="inlineStr"/>
       <c r="N44" s="39" t="inlineStr"/>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="46" customHeight="1">
       <c r="A45" s="39" t="n">
         <v>41</v>
       </c>
@@ -2523,10 +2743,18 @@
         </is>
       </c>
       <c r="J45" s="39" t="inlineStr"/>
-      <c r="L45" s="39" t="inlineStr"/>
-      <c r="N45" s="39" t="inlineStr"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
+      <c r="L45" s="39" t="inlineStr">
+        <is>
+          <t>Citrus &amp; fruit concentrates discussed at Gulfood 2026 (no detailed specs given)</t>
+        </is>
+      </c>
+      <c r="N45" s="39" t="inlineStr">
+        <is>
+          <t>Met at Gulfood; copied R&amp;D dept; at this stage not in position to proceed with a purchase order, may revisit later; Samia Dziri, HBC Holding / Hamoud Boualem</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="46" customHeight="1">
       <c r="A46" s="39" t="n">
         <v>42</v>
       </c>
@@ -2559,10 +2787,18 @@
         </is>
       </c>
       <c r="J46" s="39" t="inlineStr"/>
-      <c r="L46" s="39" t="inlineStr"/>
-      <c r="N46" s="39" t="inlineStr"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
+      <c r="L46" s="39" t="inlineStr">
+        <is>
+          <t>Private label/OEM freeze-dried fruit snacks (strawberry, mango, mixed fruits), bulk &amp; private label; requests MOQ and price list</t>
+        </is>
+      </c>
+      <c r="N46" s="39" t="inlineStr">
+        <is>
+          <t>For export to USA / Amazon US FBA; asks re FDA-compliant labeling, UPC/FNSKU barcoding, export docs &amp; customs, shipping to US freight forwarder/FBA, production availability &amp; lead time; Ghada Abdeen (partner Mr. Alaa met at Gulfood)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="46" customHeight="1">
       <c r="A47" s="39" t="n">
         <v>43</v>
       </c>
@@ -2594,11 +2830,23 @@
           <t>Orange &amp; strawberry concentrate (specs/pricing)</t>
         </is>
       </c>
-      <c r="J47" s="39" t="inlineStr"/>
-      <c r="L47" s="39" t="inlineStr"/>
-      <c r="N47" s="39" t="inlineStr"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
+      <c r="J47" s="39" t="inlineStr">
+        <is>
+          <t>Orange concentrate 700 MT/yr; strawberry concentrate (without seeds) 100 MT/yr; strawberry concentrate (with seeds) 100 MT/yr</t>
+        </is>
+      </c>
+      <c r="L47" s="39" t="inlineStr">
+        <is>
+          <t>Orange concentrate; strawberry concentrate with and without seeds; aseptic/drums packaging; spec sheets attached (Orange Concentrate, Strawberry Puree, Strawberry Puree with seeds); requests best pricing</t>
+        </is>
+      </c>
+      <c r="N47" s="39" t="inlineStr">
+        <is>
+          <t>Pricing terms EXW &amp; CIF Aqaba (Jordan); met at Gulfood 2026; Ahmad Taha / Abdallah Sweiss, Zain Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
       <c r="A48" s="39" t="n">
         <v>44</v>
       </c>
@@ -2630,11 +2878,23 @@
           <t>QF fruits &amp; vegetables (Gulfood)</t>
         </is>
       </c>
-      <c r="J48" s="39" t="inlineStr"/>
-      <c r="L48" s="39" t="inlineStr"/>
-      <c r="N48" s="39" t="inlineStr"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
+      <c r="J48" s="39" t="inlineStr">
+        <is>
+          <t>1 container</t>
+        </is>
+      </c>
+      <c r="L48" s="39" t="inlineStr">
+        <is>
+          <t>IQF fruits &amp; vegetables price list requested; bulk 10KG packaging; packaging: double wall corrugated cartons with polyethylene bags</t>
+        </is>
+      </c>
+      <c r="N48" s="39" t="inlineStr">
+        <is>
+          <t>Follow-up from Gulfood; nina (Qingdao Fresh Dynamic) is supplier sharing prices; WhatsApp 86+15066252086</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="46" customHeight="1">
       <c r="A49" s="39" t="n">
         <v>45</v>
       </c>
@@ -2667,10 +2927,18 @@
         </is>
       </c>
       <c r="J49" s="39" t="inlineStr"/>
-      <c r="L49" s="39" t="inlineStr"/>
-      <c r="N49" s="39" t="inlineStr"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
+      <c r="L49" s="39" t="inlineStr">
+        <is>
+          <t>Strawberry Puree Concentrate, 8% Brix and 20% Brix, Egypt origin; price per MT requested for both Brix; packaging options (aseptic drums, frozen bags); technical data sheet requested</t>
+        </is>
+      </c>
+      <c r="N49" s="39" t="inlineStr">
+        <is>
+          <t>End buyer in USA via CB Commerce; FDA registration a must, must meet USA MRLs; certs HACCP/ISO/Halal/Organic/FDA; long-term repeat business</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="46" customHeight="1">
       <c r="A50" s="39" t="n">
         <v>46</v>
       </c>
@@ -2707,10 +2975,18 @@
         </is>
       </c>
       <c r="J50" s="39" t="inlineStr"/>
-      <c r="L50" s="39" t="inlineStr"/>
-      <c r="N50" s="39" t="inlineStr"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
+      <c r="L50" s="39" t="inlineStr">
+        <is>
+          <t>FD (freeze-dried) Strawberry slices and Frozen Strawberry slices; asks if available</t>
+        </is>
+      </c>
+      <c r="N50" s="39" t="inlineStr">
+        <is>
+          <t>Nature Foods Company LTD, Dong Nai, Vietnam; Tel +84903941664</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="46" customHeight="1">
       <c r="A51" s="39" t="n">
         <v>47</v>
       </c>
@@ -2747,10 +3023,18 @@
         </is>
       </c>
       <c r="J51" s="39" t="inlineStr"/>
-      <c r="L51" s="39" t="inlineStr"/>
-      <c r="N51" s="39" t="inlineStr"/>
-    </row>
-    <row r="52" ht="30" customHeight="1">
+      <c r="L51" s="39" t="inlineStr">
+        <is>
+          <t>No specific product/specs; general partnership inquiry for retail/wholesale supply</t>
+        </is>
+      </c>
+      <c r="N51" s="39" t="inlineStr">
+        <is>
+          <t>EDEKA Sudwest Stiftung &amp; Co. KG, Offenburg, Germany; seeking strategic supplier partnership; Tel 015214017665</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="46" customHeight="1">
       <c r="A52" s="39" t="n">
         <v>48</v>
       </c>
@@ -2790,7 +3074,7 @@
       <c r="L52" s="39" t="inlineStr"/>
       <c r="N52" s="39" t="inlineStr"/>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="46" customHeight="1">
       <c r="A53" s="39" t="n">
         <v>49</v>
       </c>
@@ -2822,7 +3106,7 @@
       <c r="L53" s="39" t="inlineStr"/>
       <c r="N53" s="39" t="inlineStr"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="46" customHeight="1">
       <c r="A54" s="39" t="n">
         <v>50</v>
       </c>
@@ -2855,10 +3139,18 @@
         </is>
       </c>
       <c r="J54" s="39" t="inlineStr"/>
-      <c r="L54" s="39" t="inlineStr"/>
-      <c r="N54" s="39" t="inlineStr"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
+      <c r="L54" s="39" t="inlineStr">
+        <is>
+          <t>Custom-cut IQF frozen vegetables (custom cuts); requests available formats, technical specs needed; MOQ and lead times requested</t>
+        </is>
+      </c>
+      <c r="N54" s="39" t="inlineStr">
+        <is>
+          <t>Emirates Flight Catering (Dubai, UAE); flight catering/food service; Tel +971 4 208 6095, Mob +971 56 508 2351; follow-up from Gulfood 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
       <c r="A55" s="39" t="n">
         <v>51</v>
       </c>
@@ -2886,11 +3178,23 @@
           <t>FD fruits (Strawberry/Mango/Banana, 400-500g, 20ft CIF Rotterdam)</t>
         </is>
       </c>
-      <c r="J55" s="39" t="inlineStr"/>
-      <c r="L55" s="39" t="inlineStr"/>
-      <c r="N55" s="39" t="inlineStr"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
+      <c r="J55" s="39" t="inlineStr">
+        <is>
+          <t>1x20ft container (10 pallets), first order</t>
+        </is>
+      </c>
+      <c r="L55" s="39" t="inlineStr">
+        <is>
+          <t>FD Strawberry / Mango / Banana, sliced; 400-500 g buckets (branded sticker), palletised</t>
+        </is>
+      </c>
+      <c r="N55" s="39" t="inlineStr">
+        <is>
+          <t>CIF Rotterdam; German sourcing agency buying for client; product brochure &amp; certificates requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
       <c r="A56" s="39" t="n">
         <v>52</v>
       </c>
@@ -2926,11 +3230,23 @@
           <t>Tomato concentrate</t>
         </is>
       </c>
-      <c r="J56" s="39" t="inlineStr"/>
-      <c r="L56" s="39" t="inlineStr"/>
-      <c r="N56" s="39" t="inlineStr"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+      <c r="J56" s="39" t="inlineStr">
+        <is>
+          <t>At least 12 full containers annually (estimated)</t>
+        </is>
+      </c>
+      <c r="L56" s="39" t="inlineStr">
+        <is>
+          <t>Tomato concentrate 28/30 Brix (hot break) and 30/32 Brix (hot break); prices needed in all sizes incl retail; bulk/aseptic drums/retail packs</t>
+        </is>
+      </c>
+      <c r="N56" s="39" t="inlineStr">
+        <is>
+          <t>Agile Table SL (Spain) &amp; IMB (US); delivery Busan port/Japan; certs BRC/ISO/Halal/Kosher/Organic; contact +34 676206892</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="46" customHeight="1">
       <c r="A57" s="39" t="n">
         <v>53</v>
       </c>
@@ -2970,7 +3286,7 @@
       <c r="L57" s="39" t="inlineStr"/>
       <c r="N57" s="39" t="inlineStr"/>
     </row>
-    <row r="58" ht="30" customHeight="1">
+    <row r="58" ht="46" customHeight="1">
       <c r="A58" s="39" t="n">
         <v>54</v>
       </c>
@@ -3010,7 +3326,7 @@
       <c r="L58" s="39" t="inlineStr"/>
       <c r="N58" s="39" t="inlineStr"/>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" ht="46" customHeight="1">
       <c r="A59" s="39" t="n">
         <v>55</v>
       </c>
@@ -3047,10 +3363,18 @@
         </is>
       </c>
       <c r="J59" s="39" t="inlineStr"/>
-      <c r="L59" s="39" t="inlineStr"/>
-      <c r="N59" s="39" t="inlineStr"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
+      <c r="L59" s="39" t="inlineStr">
+        <is>
+          <t>Fresh strawberries for 2026/2027 season, export/processing grade; ready to coordinate specs, quantities, pricing, delivery</t>
+        </is>
+      </c>
+      <c r="N59" s="39" t="inlineStr">
+        <is>
+          <t>Ahmed Sabry offering to supply (potential supplier); asks for required quality standards/certifications; phone 01064476303</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="46" customHeight="1">
       <c r="A60" s="39" t="n">
         <v>56</v>
       </c>
@@ -3087,10 +3411,18 @@
         </is>
       </c>
       <c r="J60" s="39" t="inlineStr"/>
-      <c r="L60" s="39" t="inlineStr"/>
-      <c r="N60" s="39" t="inlineStr"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
+      <c r="L60" s="39" t="inlineStr">
+        <is>
+          <t>Requests full catalogue and price list; interested in frozen goods, ice cream, chilled and ambient products for distribution</t>
+        </is>
+      </c>
+      <c r="N60" s="39" t="inlineStr">
+        <is>
+          <t>Nickal distributor, Warsaw, Poland; supplies Biedronka, Lidl, Auchan, Intermarche, BP, Shell; wants intro meeting to enter Polish market; Tel 575400582</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="46" customHeight="1">
       <c r="A61" s="39" t="n">
         <v>57</v>
       </c>
@@ -3124,9 +3456,13 @@
       </c>
       <c r="J61" s="39" t="inlineStr"/>
       <c r="L61" s="39" t="inlineStr"/>
-      <c r="N61" s="39" t="inlineStr"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
+      <c r="N61" s="39" t="inlineStr">
+        <is>
+          <t>Only an out-of-office auto-reply received re Concentrates follow-up (Gulfood 2026); no requirement details provided; contact 8470045903</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="46" customHeight="1">
       <c r="A62" s="39" t="n">
         <v>58</v>
       </c>
@@ -3158,11 +3494,23 @@
           <t>Strawberry &amp; guava concentrate (1 container mixed)</t>
         </is>
       </c>
-      <c r="J62" s="39" t="inlineStr"/>
-      <c r="L62" s="39" t="inlineStr"/>
-      <c r="N62" s="39" t="inlineStr"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
+      <c r="J62" s="39" t="inlineStr">
+        <is>
+          <t>1 container, mixed items</t>
+        </is>
+      </c>
+      <c r="L62" s="39" t="inlineStr">
+        <is>
+          <t>Strawberry concentrate and guava; requests specifications and best price</t>
+        </is>
+      </c>
+      <c r="N62" s="39" t="inlineStr">
+        <is>
+          <t>Jamil Sabbagh, juice factory in Syria</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="46" customHeight="1">
       <c r="A63" s="39" t="n">
         <v>59</v>
       </c>
@@ -3198,11 +3546,23 @@
           <t>RFQ freeze-dried strawberries</t>
         </is>
       </c>
-      <c r="J63" s="39" t="inlineStr"/>
-      <c r="L63" s="39" t="inlineStr"/>
-      <c r="N63" s="39" t="inlineStr"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
+      <c r="J63" s="39" t="inlineStr">
+        <is>
+          <t>1 x 20-foot container</t>
+        </is>
+      </c>
+      <c r="L63" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries (whole and powder); packaging in drums; size/spec 15 x 25; unit &amp; total price, technical data sheet, shelf life/storage requested</t>
+        </is>
+      </c>
+      <c r="N63" s="39" t="inlineStr">
+        <is>
+          <t>Incoterms EXW/FOB/CIF Mersin; destination Mersin Port, Turkey; production/delivery lead time and certifications requested; contact Amal Elhakim 01060333434</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="46" customHeight="1">
       <c r="A64" s="39" t="n">
         <v>60</v>
       </c>
@@ -3236,9 +3596,13 @@
       </c>
       <c r="J64" s="39" t="inlineStr"/>
       <c r="L64" s="39" t="inlineStr"/>
-      <c r="N64" s="39" t="inlineStr"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
+      <c r="N64" s="39" t="inlineStr">
+        <is>
+          <t>Only auto-reply re Pronat email address change received; no inquiry details</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="46" customHeight="1">
       <c r="A65" s="39" t="n">
         <v>61</v>
       </c>
@@ -3267,10 +3631,18 @@
         </is>
       </c>
       <c r="J65" s="39" t="inlineStr"/>
-      <c r="L65" s="39" t="inlineStr"/>
-      <c r="N65" s="39" t="inlineStr"/>
-    </row>
-    <row r="66" ht="30" customHeight="1">
+      <c r="L65" s="39" t="inlineStr">
+        <is>
+          <t>Juice/fruit concentrates discussed at Gulfood 2026; asks whether MAFI offers organic products from catalogue</t>
+        </is>
+      </c>
+      <c r="N65" s="39" t="inlineStr">
+        <is>
+          <t>Requires EU, USDA or JAS organic certification; Ecoloni Gida (Sakarya, Turkey); contact +90 535 623 54 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="46" customHeight="1">
       <c r="A66" s="39" t="n">
         <v>62</v>
       </c>
@@ -3307,10 +3679,18 @@
         </is>
       </c>
       <c r="J66" s="39" t="inlineStr"/>
-      <c r="L66" s="39" t="inlineStr"/>
-      <c r="N66" s="39" t="inlineStr"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
+      <c r="L66" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried fruits: FD mango ~2x2 cm pieces, FD pineapple cut into 1/16 pieces, FD strawberries sliced; requests product specifications</t>
+        </is>
+      </c>
+      <c r="N66" s="39" t="inlineStr">
+        <is>
+          <t>Helio S.A., Brochow, Poland; requests delivery terms and offer; Tel 506558283</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="46" customHeight="1">
       <c r="A67" s="39" t="n">
         <v>63</v>
       </c>
@@ -3342,11 +3722,23 @@
           <t>IQF strawberry for France (offer request)</t>
         </is>
       </c>
-      <c r="J67" s="39" t="inlineStr"/>
-      <c r="L67" s="39" t="inlineStr"/>
-      <c r="N67" s="39" t="inlineStr"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
+      <c r="J67" s="39" t="inlineStr">
+        <is>
+          <t>66,000 KG total (min); 22,000 KG min per shipment</t>
+        </is>
+      </c>
+      <c r="L67" s="39" t="inlineStr">
+        <is>
+          <t>IQF Frozen Strawberry; cardboard box packaging, 20 KG per unit; product specs and availability requested</t>
+        </is>
+      </c>
+      <c r="N67" s="39" t="inlineStr">
+        <is>
+          <t>CFR Marseille, France; first delivery 06/04/2026; include 3% Iberfoods fee in price; Iberfoods commercial office for France market</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="46" customHeight="1">
       <c r="A68" s="39" t="n">
         <v>64</v>
       </c>
@@ -3383,10 +3775,18 @@
         </is>
       </c>
       <c r="J68" s="39" t="inlineStr"/>
-      <c r="L68" s="39" t="inlineStr"/>
-      <c r="N68" s="39" t="inlineStr"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
+      <c r="L68" s="39" t="inlineStr">
+        <is>
+          <t>IQF Strawberry (context of discussion); no specific requirements provided</t>
+        </is>
+      </c>
+      <c r="N68" s="39" t="inlineStr">
+        <is>
+          <t>Trixy, Longhai Juli Food Co Ltd, China; will revert when there is a need to import IQF strawberry; Tel +86 596-6719777</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="46" customHeight="1">
       <c r="A69" s="39" t="n">
         <v>65</v>
       </c>
@@ -3419,10 +3819,18 @@
         </is>
       </c>
       <c r="J69" s="39" t="inlineStr"/>
-      <c r="L69" s="39" t="inlineStr"/>
-      <c r="N69" s="39" t="inlineStr"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
+      <c r="L69" s="39" t="inlineStr">
+        <is>
+          <t>Tomato Concentrate (context of discussion); no specific requirements provided yet</t>
+        </is>
+      </c>
+      <c r="N69" s="39" t="inlineStr">
+        <is>
+          <t>Gulf Processing Industries (Sharaf Group), Dubai; forwarded to procurement (Anirudha); their certs HACCP/ISO 22000/FSSC 22000/BRC/Halal/Kosher; M +971 555137949</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="46" customHeight="1">
       <c r="A70" s="39" t="n">
         <v>66</v>
       </c>
@@ -3456,9 +3864,13 @@
       </c>
       <c r="J70" s="39" t="inlineStr"/>
       <c r="L70" s="39" t="inlineStr"/>
-      <c r="N70" s="39" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
+      <c r="N70" s="39" t="inlineStr">
+        <is>
+          <t>No inbound inquiry from this address in folder; only an auto-reply from sanmarzano.com redirecting MAFI's tomato concentrate follow-up to this address</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="46" customHeight="1">
       <c r="A71" s="39" t="n">
         <v>67</v>
       </c>
@@ -3494,11 +3906,23 @@
           <t>Strawberry seed 24 MT</t>
         </is>
       </c>
-      <c r="J71" s="39" t="inlineStr"/>
-      <c r="L71" s="39" t="inlineStr"/>
-      <c r="N71" s="39" t="inlineStr"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
+      <c r="J71" s="39" t="inlineStr">
+        <is>
+          <t>24 MT</t>
+        </is>
+      </c>
+      <c r="L71" s="39" t="inlineStr">
+        <is>
+          <t>Strawberry seeds (for pressing oil) - not standard fruit product</t>
+        </is>
+      </c>
+      <c r="N71" s="39" t="inlineStr">
+        <is>
+          <t>O&amp;3 Polska Sp. z o.o., Warka, Poland; Tel 506680754</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="46" customHeight="1">
       <c r="A72" s="39" t="n">
         <v>68</v>
       </c>
@@ -3534,11 +3958,23 @@
           <t>Freeze-dried strawberries (20-30 tons; whole/slices/powder)</t>
         </is>
       </c>
-      <c r="J72" s="39" t="inlineStr"/>
-      <c r="L72" s="39" t="inlineStr"/>
-      <c r="N72" s="39" t="inlineStr"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
+      <c r="J72" s="39" t="inlineStr">
+        <is>
+          <t>20 tons freeze-dried strawberries; quote based on a full container of each shape</t>
+        </is>
+      </c>
+      <c r="L72" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries: whole, slices, powder; also asks price of IQF strawberries for freeze-drying; requests full quotation</t>
+        </is>
+      </c>
+      <c r="N72" s="39" t="inlineStr">
+        <is>
+          <t>Buyer is CEO of a Czech Republic company; asks for pesticide analyses; notes MAFI starts production Q3 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="46" customHeight="1">
       <c r="A73" s="39" t="n">
         <v>69</v>
       </c>
@@ -3574,7 +4010,7 @@
       <c r="L73" s="39" t="inlineStr"/>
       <c r="N73" s="39" t="inlineStr"/>
     </row>
-    <row r="74" ht="30" customHeight="1">
+    <row r="74" ht="46" customHeight="1">
       <c r="A74" s="39" t="n">
         <v>70</v>
       </c>
@@ -3604,9 +4040,13 @@
       </c>
       <c r="J74" s="39" t="inlineStr"/>
       <c r="L74" s="39" t="inlineStr"/>
-      <c r="N74" s="39" t="inlineStr"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
+      <c r="N74" s="39" t="inlineStr">
+        <is>
+          <t>Only an auto-reply (out of office 16-22.03); re IQF fruits &amp; vegetables discussed at Gulfood 2026; alt contact Maria Ducheva (maria.ducheva@prowtc.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="46" customHeight="1">
       <c r="A75" s="39" t="n">
         <v>71</v>
       </c>
@@ -3643,10 +4083,18 @@
         </is>
       </c>
       <c r="J75" s="39" t="inlineStr"/>
-      <c r="L75" s="39" t="inlineStr"/>
-      <c r="N75" s="39" t="inlineStr"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
+      <c r="L75" s="39" t="inlineStr">
+        <is>
+          <t>Citrus molasses (byproduct of citrus processing, for biogas) - not standard fruit product; asks if facility produces it</t>
+        </is>
+      </c>
+      <c r="N75" s="39" t="inlineStr">
+        <is>
+          <t>GreenLix, Fredericia, Denmark; biomass/industrial byproduct supplier for biogas; Tel +4571447106</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="46" customHeight="1">
       <c r="A76" s="39" t="n">
         <v>72</v>
       </c>
@@ -3678,11 +4126,23 @@
           <t>Aseptic strawberry puree (drums, CFR UK)</t>
         </is>
       </c>
-      <c r="J76" s="39" t="inlineStr"/>
-      <c r="L76" s="39" t="inlineStr"/>
-      <c r="N76" s="39" t="inlineStr"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
+      <c r="J76" s="39" t="inlineStr">
+        <is>
+          <t>300 MT strawberry puree (seedless); full container load shipments; spread deliveries</t>
+        </is>
+      </c>
+      <c r="L76" s="39" t="inlineStr">
+        <is>
+          <t>Aseptic strawberry puree, seedless; 0.5mm sieve filter; minimum Brix 6; aseptic 200kg drums</t>
+        </is>
+      </c>
+      <c r="N76" s="39" t="inlineStr">
+        <is>
+          <t>CFR London Gateway; UK market; meet at IFE Food &amp; Drinks London 30 Mar-1 Apr 2026; asks if storage charges apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="46" customHeight="1">
       <c r="A77" s="39" t="n">
         <v>73</v>
       </c>
@@ -3719,10 +4179,18 @@
         </is>
       </c>
       <c r="J77" s="39" t="inlineStr"/>
-      <c r="L77" s="39" t="inlineStr"/>
-      <c r="N77" s="39" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
+      <c r="L77" s="39" t="inlineStr">
+        <is>
+          <t>No fruit products requested; vendor offering stainless steel tanks, food machinery, pasteurizers, CIP, pumps, filling systems</t>
+        </is>
+      </c>
+      <c r="N77" s="39" t="inlineStr">
+        <is>
+          <t>Endulus Krom GmbH, Duisburg, Germany; equipment supplier pitch (not a buyer); Tel +4917667503821</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="46" customHeight="1">
       <c r="A78" s="39" t="n">
         <v>74</v>
       </c>
@@ -3758,11 +4226,23 @@
           <t>FD strawberry slices (price/MOQ)</t>
         </is>
       </c>
-      <c r="J78" s="39" t="inlineStr"/>
-      <c r="L78" s="39" t="inlineStr"/>
-      <c r="N78" s="39" t="inlineStr"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
+      <c r="J78" s="39" t="inlineStr">
+        <is>
+          <t>Asks MOQ for FD Strawberry slices</t>
+        </is>
+      </c>
+      <c r="L78" s="39" t="inlineStr">
+        <is>
+          <t>FD (freeze-dried) Strawberry slices; asks per-kg price</t>
+        </is>
+      </c>
+      <c r="N78" s="39" t="inlineStr">
+        <is>
+          <t>Chane GmbH, Sandhausen, Germany; Tel 1787811247</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="46" customHeight="1">
       <c r="A79" s="39" t="n">
         <v>75</v>
       </c>
@@ -3798,11 +4278,23 @@
           <t>Orange/lemon/pomegranate concentrate (FOJC Brix 65, 5 containers, Mersin)</t>
         </is>
       </c>
-      <c r="J79" s="39" t="inlineStr"/>
-      <c r="L79" s="39" t="inlineStr"/>
-      <c r="N79" s="39" t="inlineStr"/>
-    </row>
-    <row r="80" ht="30" customHeight="1">
+      <c r="J79" s="39" t="inlineStr">
+        <is>
+          <t>5 containers</t>
+        </is>
+      </c>
+      <c r="L79" s="39" t="inlineStr">
+        <is>
+          <t>Frozen Orange Juice Concentrate (FOJC), Brix 65, aseptic filling in metal drums; also requests orange, lemon &amp; pomegranate concentrate prices and analyses/specs</t>
+        </is>
+      </c>
+      <c r="N79" s="39" t="inlineStr">
+        <is>
+          <t>Delivery port Mersin Seaport, Turkey; WhatsApp/Tel +905070776453; Global Supply Point Gida (Turkey)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="46" customHeight="1">
       <c r="A80" s="39" t="n">
         <v>76</v>
       </c>
@@ -3831,10 +4323,18 @@
         </is>
       </c>
       <c r="J80" s="39" t="inlineStr"/>
-      <c r="L80" s="39" t="inlineStr"/>
-      <c r="N80" s="39" t="inlineStr"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
+      <c r="L80" s="39" t="inlineStr">
+        <is>
+          <t>CMO (contract manufacturing) of frozen brands: strawberries, artichokes, cauliflower, broccoli, green beans; plus orange concentrate</t>
+        </is>
+      </c>
+      <c r="N80" s="39" t="inlineStr">
+        <is>
+          <t>Kern for Export; asks if MAFI has started operation and about production line availability; mobile +201223955440</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="46" customHeight="1">
       <c r="A81" s="39" t="n">
         <v>77</v>
       </c>
@@ -3870,11 +4370,23 @@
           <t>IQF whole strawberries (1 container, Poti/FOB)</t>
         </is>
       </c>
-      <c r="J81" s="39" t="inlineStr"/>
-      <c r="L81" s="39" t="inlineStr"/>
-      <c r="N81" s="39" t="inlineStr"/>
-    </row>
-    <row r="82" ht="30" customHeight="1">
+      <c r="J81" s="39" t="inlineStr">
+        <is>
+          <t>1 full container IQF whole strawberries (bulk)</t>
+        </is>
+      </c>
+      <c r="L81" s="39" t="inlineStr">
+        <is>
+          <t>IQF whole strawberries, calibrated and uncalibrated (size for each requested); 10 kg bags; for freeze-drying production</t>
+        </is>
+      </c>
+      <c r="N81" s="39" t="inlineStr">
+        <is>
+          <t>Poti Port or FOB; Fergana Exim Agro, Uzbekistan; requests crop year &amp; certificates; tel +998331017330, WhatsApp +998909881122</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="46" customHeight="1">
       <c r="A82" s="39" t="n">
         <v>78</v>
       </c>
@@ -3910,11 +4422,23 @@
           <t>FD slices (mango/banana/peach), strawberry powder/pieces (50kg)</t>
         </is>
       </c>
-      <c r="J82" s="39" t="inlineStr"/>
-      <c r="L82" s="39" t="inlineStr"/>
-      <c r="N82" s="39" t="inlineStr"/>
-    </row>
-    <row r="83" ht="30" customHeight="1">
+      <c r="J82" s="39" t="inlineStr">
+        <is>
+          <t>25 kg and/or 50 kg bulk per item; quote for 50 kg per item requested; MOQ requested</t>
+        </is>
+      </c>
+      <c r="L82" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried: slices (kiwi, lime, strawberry, mango, banana, peach, black olives), whole (raspberry, wild blueberry, cranberry, peas), powder (raspberry, strawberry), pieces (pineapple, apple etc.); 25/50kg foil bag + carton</t>
+        </is>
+      </c>
+      <c r="N82" s="39" t="inlineStr">
+        <is>
+          <t>EXW quote, EU market (also USA); asks EU warehouse, lead time, certs (BRCGS/FSSC22000/HACCP/ISO); Worlds Garden/FRESHZILLA Barcelona; tel 4434828798</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="46" customHeight="1">
       <c r="A83" s="39" t="n">
         <v>79</v>
       </c>
@@ -3947,10 +4471,18 @@
         </is>
       </c>
       <c r="J83" s="39" t="inlineStr"/>
-      <c r="L83" s="39" t="inlineStr"/>
-      <c r="N83" s="39" t="inlineStr"/>
-    </row>
-    <row r="84" ht="30" customHeight="1">
+      <c r="L83" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried berries</t>
+        </is>
+      </c>
+      <c r="N83" s="39" t="inlineStr">
+        <is>
+          <t>Genba Food, Lithuania; wholesaler in the Baltics; seeking a trusted partner in Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="46" customHeight="1">
       <c r="A84" s="39" t="n">
         <v>80</v>
       </c>
@@ -3983,10 +4515,18 @@
         </is>
       </c>
       <c r="J84" s="39" t="inlineStr"/>
-      <c r="L84" s="39" t="inlineStr"/>
-      <c r="N84" s="39" t="inlineStr"/>
-    </row>
-    <row r="85" ht="30" customHeight="1">
+      <c r="L84" s="39" t="inlineStr">
+        <is>
+          <t>Requests specifications for Strawberry Puree, Mandarin Juice Concentrate, Lemon Juice Concentrate; MAFI sent specs incl Lemon JC 400 GPL/51.5 Brix and 500 GPL/61.15 Brix</t>
+        </is>
+      </c>
+      <c r="N84" s="39" t="inlineStr">
+        <is>
+          <t>Vitmark-Ukraine, Odesa, Ukraine; Head of Procurement; Tel +380 482 344045 / +380 674485428; cc Alina Khmara</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="46" customHeight="1">
       <c r="A85" s="39" t="n">
         <v>81</v>
       </c>
@@ -4022,11 +4562,23 @@
           <t>Samples / product match</t>
         </is>
       </c>
-      <c r="J85" s="39" t="inlineStr"/>
-      <c r="L85" s="39" t="inlineStr"/>
-      <c r="N85" s="39" t="inlineStr"/>
-    </row>
-    <row r="86" ht="30" customHeight="1">
+      <c r="J85" s="39" t="inlineStr">
+        <is>
+          <t>Samples &gt;=0.5 L for lab/technological testing; MOQ requested</t>
+        </is>
+      </c>
+      <c r="L85" s="39" t="inlineStr">
+        <is>
+          <t>Orange juice concentrate with pulp; Brix &gt;=64.0 (up to ~67.0); titratable acidity 4.5-5.8 g/100g; pH 3.3-4.0</t>
+        </is>
+      </c>
+      <c r="N85" s="39" t="inlineStr">
+        <is>
+          <t>JV Chortoq Mineral Water, Tashkent Uzbekistan; asks price, delivery &amp; payment terms, lead time; tel +998909781925; MAFI offered samples Oct 2026 (starts Q3 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="46" customHeight="1">
       <c r="A86" s="39" t="n">
         <v>82</v>
       </c>
@@ -4059,10 +4611,18 @@
         </is>
       </c>
       <c r="J86" s="39" t="inlineStr"/>
-      <c r="L86" s="39" t="inlineStr"/>
-      <c r="N86" s="39" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
+      <c r="L86" s="39" t="inlineStr">
+        <is>
+          <t>General interest in fruit juice concentrates &amp; purees (also essential/edible oils, terpenes, aroma); no specific product/specs given</t>
+        </is>
+      </c>
+      <c r="N86" s="39" t="inlineStr">
+        <is>
+          <t>Independent procurement rep, MTB - More Than Brokers (Brazil); requests to speak with commercial contact; tel +55 48 99197 1513</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="46" customHeight="1">
       <c r="A87" s="39" t="n">
         <v>83</v>
       </c>
@@ -4102,7 +4662,7 @@
       <c r="L87" s="39" t="inlineStr"/>
       <c r="N87" s="39" t="inlineStr"/>
     </row>
-    <row r="88" ht="30" customHeight="1">
+    <row r="88" ht="46" customHeight="1">
       <c r="A88" s="39" t="n">
         <v>84</v>
       </c>
@@ -4123,10 +4683,18 @@
         </is>
       </c>
       <c r="J88" s="39" t="inlineStr"/>
-      <c r="L88" s="39" t="inlineStr"/>
-      <c r="N88" s="39" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
+      <c r="L88" s="39" t="inlineStr">
+        <is>
+          <t>Fruit juice concentrates: guava, mango, strawberry, orange; asks concentration ratio (Brix) and price of each</t>
+        </is>
+      </c>
+      <c r="N88" s="39" t="inlineStr">
+        <is>
+          <t>Inquiry written in Arabic; requesting prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="46" customHeight="1">
       <c r="A89" s="39" t="n">
         <v>85</v>
       </c>
@@ -4166,7 +4734,7 @@
       <c r="L89" s="39" t="inlineStr"/>
       <c r="N89" s="39" t="inlineStr"/>
     </row>
-    <row r="90" ht="30" customHeight="1">
+    <row r="90" ht="46" customHeight="1">
       <c r="A90" s="39" t="n">
         <v>86</v>
       </c>
@@ -4198,11 +4766,23 @@
           <t>Purchasing FD fruits (20ft/40ft, FOB/CIF)</t>
         </is>
       </c>
-      <c r="J90" s="39" t="inlineStr"/>
-      <c r="L90" s="39" t="inlineStr"/>
-      <c r="N90" s="39" t="inlineStr"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
+      <c r="J90" s="39" t="inlineStr">
+        <is>
+          <t>20ft and 40ft containers</t>
+        </is>
+      </c>
+      <c r="L90" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried fruit: Strawberry (whole), Apple, Peach, Raspberry (whole), Mango; 50 gr retail packages and bulk packages</t>
+        </is>
+      </c>
+      <c r="N90" s="39" t="inlineStr">
+        <is>
+          <t>Quote FOB and CIF prices; buyer in Turkiye (Kirlioglu); contact +905521619909</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="46" customHeight="1">
       <c r="A91" s="39" t="n">
         <v>87</v>
       </c>
@@ -4238,11 +4818,23 @@
           <t>Sourcing products in bulk</t>
         </is>
       </c>
-      <c r="J91" s="39" t="inlineStr"/>
-      <c r="L91" s="39" t="inlineStr"/>
-      <c r="N91" s="39" t="inlineStr"/>
-    </row>
-    <row r="92" ht="30" customHeight="1">
+      <c r="J91" s="39" t="inlineStr">
+        <is>
+          <t>Bulk quantity (unspecified)</t>
+        </is>
+      </c>
+      <c r="L91" s="39" t="inlineStr">
+        <is>
+          <t>Various products in bulk; requests product catalogue, pricing and availability</t>
+        </is>
+      </c>
+      <c r="N91" s="39" t="inlineStr">
+        <is>
+          <t>Partnership opportunity; delivery to Santiago, Chile; Bureauveritas; Tel 990354287</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="46" customHeight="1">
       <c r="A92" s="39" t="n">
         <v>88</v>
       </c>
@@ -4278,11 +4870,23 @@
           <t>Procurement inquiry</t>
         </is>
       </c>
-      <c r="J92" s="39" t="inlineStr"/>
-      <c r="L92" s="39" t="inlineStr"/>
-      <c r="N92" s="39" t="inlineStr"/>
-    </row>
-    <row r="93" ht="30" customHeight="1">
+      <c r="J92" s="39" t="inlineStr">
+        <is>
+          <t>MOQ requested per product/packaging size (not specified)</t>
+        </is>
+      </c>
+      <c r="L92" s="39" t="inlineStr">
+        <is>
+          <t>Purees, concentrates, IQF/bulk frozen fruit (e.g. IQF pomegranate, strawberries) for smoothies/juices/spreads; specs Brix, pH, ingredient declaration, size/grade, sugar, origin, freezing method, packaging; sample + bulk price in EUR/USD</t>
+        </is>
+      </c>
+      <c r="N92" s="39" t="inlineStr">
+        <is>
+          <t>Delivery to Thessaloniki Port, Greece; Incoterm to be defined; payment terms; certs ISO/HACCP/FSSC22000/Organic/Kosher/Halal; lead time; P Gkotzaridis &amp; Co, Greece</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="46" customHeight="1">
       <c r="A93" s="39" t="n">
         <v>89</v>
       </c>
@@ -4319,10 +4923,18 @@
         </is>
       </c>
       <c r="J93" s="39" t="inlineStr"/>
-      <c r="L93" s="39" t="inlineStr"/>
-      <c r="N93" s="39" t="inlineStr"/>
-    </row>
-    <row r="94" ht="30" customHeight="1">
+      <c r="L93" s="39" t="inlineStr">
+        <is>
+          <t>Natural frozen lemon juice (100% freshly squeezed, frozen at -40C then stored -18C); requesting spec, packaging and price info</t>
+        </is>
+      </c>
+      <c r="N93" s="39" t="inlineStr">
+        <is>
+          <t>Buyer Lemonera/UJ Group, Turkey; plans to visit Egypt to meet suppliers, requests office/factory addresses; T +90 212 9860636/+1 713 7771000, M +90 532 5972721</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="46" customHeight="1">
       <c r="A94" s="39" t="n">
         <v>90</v>
       </c>
@@ -4354,11 +4966,23 @@
           <t>Lemon juice concentrate cloudy/clear 400-500 gpl (2026 demand)</t>
         </is>
       </c>
-      <c r="J94" s="39" t="inlineStr"/>
-      <c r="L94" s="39" t="inlineStr"/>
-      <c r="N94" s="39" t="inlineStr"/>
-    </row>
-    <row r="95" ht="30" customHeight="1">
+      <c r="J94" s="39" t="inlineStr">
+        <is>
+          <t>2026 annual demand (securing volumes for 2026)</t>
+        </is>
+      </c>
+      <c r="L94" s="39" t="inlineStr">
+        <is>
+          <t>Lemon juice concentrate cloudy 400/500 gpl; Lemon juice concentrate clear 400/500 gpl</t>
+        </is>
+      </c>
+      <c r="N94" s="39" t="inlineStr">
+        <is>
+          <t>Requests best price FOB basis, specs and estimated lead time; buyer Pilmifresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="46" customHeight="1">
       <c r="A95" s="39" t="n">
         <v>91</v>
       </c>
@@ -4394,7 +5018,7 @@
       <c r="L95" s="39" t="inlineStr"/>
       <c r="N95" s="39" t="inlineStr"/>
     </row>
-    <row r="96" ht="30" customHeight="1">
+    <row r="96" ht="46" customHeight="1">
       <c r="A96" s="39" t="n">
         <v>92</v>
       </c>
@@ -4430,11 +5054,23 @@
           <t>Sales inquiry</t>
         </is>
       </c>
-      <c r="J96" s="39" t="inlineStr"/>
-      <c r="L96" s="39" t="inlineStr"/>
-      <c r="N96" s="39" t="inlineStr"/>
-    </row>
-    <row r="97" ht="30" customHeight="1">
+      <c r="J96" s="39" t="inlineStr">
+        <is>
+          <t>MOQ requested (not specified); samples requested</t>
+        </is>
+      </c>
+      <c r="L96" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried fruits: Mango (chunks/slices), Strawberry (whole/slices), Banana (slices), Kiwi (slices); requests catalog and wholesale price list</t>
+        </is>
+      </c>
+      <c r="N96" s="39" t="inlineStr">
+        <is>
+          <t>Elreefy Trading Co., Giza, Egypt; contact tel 01158300643 / 01061498589</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="46" customHeight="1">
       <c r="A97" s="39" t="n">
         <v>93</v>
       </c>
@@ -4471,10 +5107,18 @@
         </is>
       </c>
       <c r="J97" s="39" t="inlineStr"/>
-      <c r="L97" s="39" t="inlineStr"/>
-      <c r="N97" s="39" t="inlineStr"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
+      <c r="L97" s="39" t="inlineStr">
+        <is>
+          <t>Requests full brochure for all upcoming products and a quotation if possible</t>
+        </is>
+      </c>
+      <c r="N97" s="39" t="inlineStr">
+        <is>
+          <t>Dubai, UAE; Tel +971503409475; MAFI replied with brochure &amp; company profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="46" customHeight="1">
       <c r="A98" s="39" t="n">
         <v>94</v>
       </c>
@@ -4511,10 +5155,18 @@
         </is>
       </c>
       <c r="J98" s="39" t="inlineStr"/>
-      <c r="L98" s="39" t="inlineStr"/>
-      <c r="N98" s="39" t="inlineStr"/>
-    </row>
-    <row r="99" ht="30" customHeight="1">
+      <c r="L98" s="39" t="inlineStr">
+        <is>
+          <t>Looking for NFC orange juice</t>
+        </is>
+      </c>
+      <c r="N98" s="39" t="inlineStr">
+        <is>
+          <t>Andros, France; plans to visit Egypt in March, asks to visit on the 11th; Tel 0033620730939</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="46" customHeight="1">
       <c r="A99" s="39" t="n">
         <v>95</v>
       </c>
@@ -4551,10 +5203,18 @@
         </is>
       </c>
       <c r="J99" s="39" t="inlineStr"/>
-      <c r="L99" s="39" t="inlineStr"/>
-      <c r="N99" s="39" t="inlineStr"/>
-    </row>
-    <row r="100" ht="30" customHeight="1">
+      <c r="L99" s="39" t="inlineStr">
+        <is>
+          <t>Concentrated fruit juices and purees: peach, cherry, apricot, apple, etc.; requests product specifications and indicative price</t>
+        </is>
+      </c>
+      <c r="N99" s="39" t="inlineStr">
+        <is>
+          <t>PROGRESS (Frutonanny), baby food producer, Moscow, Russia; Tel +79264121460</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="46" customHeight="1">
       <c r="A100" s="39" t="n">
         <v>96</v>
       </c>
@@ -4590,11 +5250,23 @@
           <t>Sweet potato varieties / EU export &amp; chips line</t>
         </is>
       </c>
-      <c r="J100" s="39" t="inlineStr"/>
-      <c r="L100" s="39" t="inlineStr"/>
-      <c r="N100" s="39" t="inlineStr"/>
-    </row>
-    <row r="101" ht="30" customHeight="1">
+      <c r="J100" s="39" t="inlineStr">
+        <is>
+          <t>Reference: Peru exports ~80,000-100,000 t/yr and Chile ~15,000-25,000 t/yr sweet potatoes to EU</t>
+        </is>
+      </c>
+      <c r="L100" s="39" t="inlineStr">
+        <is>
+          <t>Sweet potato varieties (Japanese Satsumaimo/Murasaki, purple-flesh Okinawan, white-flesh processing types) for IQF/chips; partnership to cultivate in Egypt and export to EU</t>
+        </is>
+      </c>
+      <c r="N100" s="39" t="inlineStr">
+        <is>
+          <t>Destination EU (Germany, Spain, France, Netherlands); proposes technical call/pilot phase; Uniya Chile spa; phone +56 9 3414 3633</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="46" customHeight="1">
       <c r="A101" s="39" t="n">
         <v>97</v>
       </c>
@@ -4634,7 +5306,7 @@
       <c r="L101" s="39" t="inlineStr"/>
       <c r="N101" s="39" t="inlineStr"/>
     </row>
-    <row r="102" ht="30" customHeight="1">
+    <row r="102" ht="46" customHeight="1">
       <c r="A102" s="39" t="n">
         <v>98</v>
       </c>
@@ -4674,7 +5346,7 @@
       <c r="L102" s="39" t="inlineStr"/>
       <c r="N102" s="39" t="inlineStr"/>
     </row>
-    <row r="103" ht="30" customHeight="1">
+    <row r="103" ht="46" customHeight="1">
       <c r="A103" s="39" t="n">
         <v>99</v>
       </c>
@@ -4710,11 +5382,23 @@
           <t>Import inquiry</t>
         </is>
       </c>
-      <c r="J103" s="39" t="inlineStr"/>
-      <c r="L103" s="39" t="inlineStr"/>
-      <c r="N103" s="39" t="inlineStr"/>
-    </row>
-    <row r="104" ht="30" customHeight="1">
+      <c r="J103" s="39" t="inlineStr">
+        <is>
+          <t>1x 20ft FCL or 1x 40ft FCL</t>
+        </is>
+      </c>
+      <c r="L103" s="39" t="inlineStr">
+        <is>
+          <t>NFC Orange Juice; packing 200 L drums or 1000 L IBC tanks; requests FOB prices, product photos, spec sheet (broker takes 5% commission on FOB)</t>
+        </is>
+      </c>
+      <c r="N103" s="39" t="inlineStr">
+        <is>
+          <t>FOB for Brazil market; needs port of loading, container load 20/40ft, ETD, payment terms, price validity; HR Broker, Maceio, Brazil; Tel 9373399905</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="46" customHeight="1">
       <c r="A104" s="39" t="n">
         <v>100</v>
       </c>
@@ -4747,10 +5431,18 @@
         </is>
       </c>
       <c r="J104" s="39" t="inlineStr"/>
-      <c r="L104" s="39" t="inlineStr"/>
-      <c r="N104" s="39" t="inlineStr"/>
-    </row>
-    <row r="105" ht="30" customHeight="1">
+      <c r="L104" s="39" t="inlineStr">
+        <is>
+          <t>Rehydrated prunes, with pit and pitted, for industrial fruit processing (purees, fillings, jams) - supplier offer, not buyer request</t>
+        </is>
+      </c>
+      <c r="N104" s="39" t="inlineStr">
+        <is>
+          <t>Originia Foods / SAMCA Group, Spain; requests intro call; contact +34 976160188, +34 690092156, Ana Arnal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="46" customHeight="1">
       <c r="A105" s="39" t="n">
         <v>101</v>
       </c>
@@ -4786,11 +5478,23 @@
           <t>Supply fresh/IQF strawberries (300 tons, FDA)</t>
         </is>
       </c>
-      <c r="J105" s="39" t="inlineStr"/>
-      <c r="L105" s="39" t="inlineStr"/>
-      <c r="N105" s="39" t="inlineStr"/>
-    </row>
-    <row r="106" ht="30" customHeight="1">
+      <c r="J105" s="39" t="inlineStr">
+        <is>
+          <t>300 tons</t>
+        </is>
+      </c>
+      <c r="L105" s="39" t="inlineStr">
+        <is>
+          <t>Strawberries ready for freezing; FDA-tested and dried (freeze-dried) strawberries</t>
+        </is>
+      </c>
+      <c r="N105" s="39" t="inlineStr">
+        <is>
+          <t>Arabic inquiry (Allian for Agricultural Supplies); asks delivery timing and contracting method; contact 01007075225</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="46" customHeight="1">
       <c r="A106" s="39" t="n">
         <v>102</v>
       </c>
@@ -4822,11 +5526,23 @@
           <t>Supply fresh strawberries</t>
         </is>
       </c>
-      <c r="J106" s="39" t="inlineStr"/>
-      <c r="L106" s="39" t="inlineStr"/>
-      <c r="N106" s="39" t="inlineStr"/>
-    </row>
-    <row r="107" ht="30" customHeight="1">
+      <c r="J106" s="39" t="inlineStr">
+        <is>
+          <t>Required quantities (unspecified)</t>
+        </is>
+      </c>
+      <c r="L106" s="39" t="inlineStr">
+        <is>
+          <t>Direct supply of fruits (general); no specific product/specs given</t>
+        </is>
+      </c>
+      <c r="N106" s="39" t="inlineStr">
+        <is>
+          <t>Generic collaboration/supply proposal; wants to discuss technical and commercial details; contact 01013579935 (Ahmed Ali)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="46" customHeight="1">
       <c r="A107" s="39" t="n">
         <v>103</v>
       </c>
@@ -4859,10 +5575,18 @@
         </is>
       </c>
       <c r="J107" s="39" t="inlineStr"/>
-      <c r="L107" s="39" t="inlineStr"/>
-      <c r="N107" s="39" t="inlineStr"/>
-    </row>
-    <row r="108" ht="30" customHeight="1">
+      <c r="L107" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried products (full range requested); requests pricing and MOQ, packaging info</t>
+        </is>
+      </c>
+      <c r="N107" s="39" t="inlineStr">
+        <is>
+          <t>Export to Morocco; requests export conditions, quality certifications, catalogues/specs/samples; Morocco SAULE; contact +212662680881 (Leila Khedji, CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="46" customHeight="1">
       <c r="A108" s="39" t="n">
         <v>104</v>
       </c>
@@ -4898,7 +5622,7 @@
       <c r="L108" s="39" t="inlineStr"/>
       <c r="N108" s="39" t="inlineStr"/>
     </row>
-    <row r="109" ht="30" customHeight="1">
+    <row r="109" ht="46" customHeight="1">
       <c r="A109" s="39" t="n">
         <v>105</v>
       </c>
@@ -4931,10 +5655,18 @@
         </is>
       </c>
       <c r="J109" s="39" t="inlineStr"/>
-      <c r="L109" s="39" t="inlineStr"/>
-      <c r="N109" s="39" t="inlineStr"/>
-    </row>
-    <row r="110" ht="30" customHeight="1">
+      <c r="L109" s="39" t="inlineStr">
+        <is>
+          <t>Seeks organic fruit seeds for vegetable oil production: organic Strawberry, Raspberry, Black currant, Blueberry seeds (not standard fruit products)</t>
+        </is>
+      </c>
+      <c r="N109" s="39" t="inlineStr">
+        <is>
+          <t>Oleador GmbH, Hannover, Germany; reply to MAFI Gulfood 2026 outreach; Tel +49 511 676559-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="46" customHeight="1">
       <c r="A110" s="39" t="n">
         <v>106</v>
       </c>
@@ -4962,11 +5694,23 @@
           <t>FD strawberries (granules) 7 tons - export to China</t>
         </is>
       </c>
-      <c r="J110" s="39" t="inlineStr"/>
-      <c r="L110" s="39" t="inlineStr"/>
-      <c r="N110" s="39" t="inlineStr"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
+      <c r="J110" s="39" t="inlineStr">
+        <is>
+          <t>7 tons</t>
+        </is>
+      </c>
+      <c r="L110" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries (granules); Grade: premium food grade</t>
+        </is>
+      </c>
+      <c r="N110" s="39" t="inlineStr">
+        <is>
+          <t>Export to China; requests availability, price quotation and available certifications; Garden Guru; contact 01066650873 (Dr Nesrine Hammady)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="46" customHeight="1">
       <c r="A111" s="39" t="n">
         <v>107</v>
       </c>
@@ -5006,7 +5750,7 @@
       <c r="L111" s="39" t="inlineStr"/>
       <c r="N111" s="39" t="inlineStr"/>
     </row>
-    <row r="112" ht="30" customHeight="1">
+    <row r="112" ht="46" customHeight="1">
       <c r="A112" s="39" t="n">
         <v>108</v>
       </c>
@@ -5046,7 +5790,7 @@
       <c r="L112" s="39" t="inlineStr"/>
       <c r="N112" s="39" t="inlineStr"/>
     </row>
-    <row r="113" ht="30" customHeight="1">
+    <row r="113" ht="46" customHeight="1">
       <c r="A113" s="39" t="n">
         <v>109</v>
       </c>
@@ -5082,7 +5826,7 @@
       <c r="L113" s="39" t="inlineStr"/>
       <c r="N113" s="39" t="inlineStr"/>
     </row>
-    <row r="114" ht="30" customHeight="1">
+    <row r="114" ht="46" customHeight="1">
       <c r="A114" s="39" t="n">
         <v>110</v>
       </c>
@@ -5120,9 +5864,13 @@
       </c>
       <c r="J114" s="39" t="inlineStr"/>
       <c r="L114" s="39" t="inlineStr"/>
-      <c r="N114" s="39" t="inlineStr"/>
-    </row>
-    <row r="115" ht="30" customHeight="1">
+      <c r="N114" s="39" t="inlineStr">
+        <is>
+          <t>General intro via website contact form; wants to discuss business opportunities for REWE Germany; REWE Far East Ltd, Istanbul Turkey; Tel +905423193883</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="46" customHeight="1">
       <c r="A115" s="39" t="n">
         <v>111</v>
       </c>
@@ -5160,9 +5908,13 @@
       </c>
       <c r="J115" s="39" t="inlineStr"/>
       <c r="L115" s="39" t="inlineStr"/>
-      <c r="N115" s="39" t="inlineStr"/>
-    </row>
-    <row r="116" ht="30" customHeight="1">
+      <c r="N115" s="39" t="inlineStr">
+        <is>
+          <t>Not a buyer - Ovorider is Smurfit WestRock agent in ME pitching Bag-in-Box liquid packaging (juices/sauces); requests meeting at Gulfood; Dubai UAE; Tel +962790389890</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="46" customHeight="1">
       <c r="A116" s="39" t="n">
         <v>112</v>
       </c>
@@ -5194,11 +5946,23 @@
           <t>Representation &amp; sales for Brazil</t>
         </is>
       </c>
-      <c r="J116" s="39" t="inlineStr"/>
-      <c r="L116" s="39" t="inlineStr"/>
-      <c r="N116" s="39" t="inlineStr"/>
-    </row>
-    <row r="117" ht="30" customHeight="1">
+      <c r="J116" s="39" t="inlineStr">
+        <is>
+          <t>Has supplied 10,000+ tons strawberries; multiple containers; wants exclusive Brazil representation</t>
+        </is>
+      </c>
+      <c r="L116" s="39" t="inlineStr">
+        <is>
+          <t>IQF strawberries, freeze-dried strawberries, purees and concentrates line</t>
+        </is>
+      </c>
+      <c r="N116" s="39" t="inlineStr">
+        <is>
+          <t>Importer/distributor Frutas do Mundo Ltda, Brazil; Ricardo Pascal; seeks new products/exclusive rep for Brazil; WhatsApp +5551981187269, +5548998491012</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="46" customHeight="1">
       <c r="A117" s="39" t="n">
         <v>113</v>
       </c>
@@ -5234,11 +5998,23 @@
           <t>Processing company - sourcing inquiry</t>
         </is>
       </c>
-      <c r="J117" s="39" t="inlineStr"/>
-      <c r="L117" s="39" t="inlineStr"/>
-      <c r="N117" s="39" t="inlineStr"/>
-    </row>
-    <row r="118" ht="30" customHeight="1">
+      <c r="J117" s="39" t="inlineStr">
+        <is>
+          <t>Asking MOQ; volume/long-term contract discounts requested</t>
+        </is>
+      </c>
+      <c r="L117" s="39" t="inlineStr">
+        <is>
+          <t>NFC (Not-From-Concentrate) orange juice; asks Brix/acidity, pasteurization, packaging (aseptic bag-in-box, PET), shelf life; price per MT in USD</t>
+        </is>
+      </c>
+      <c r="N117" s="39" t="inlineStr">
+        <is>
+          <t>Incoterms FOB/CIF requested; certs ISO/HACCP/organic/Fair Trade; wants samples, facility location, lead time; MJC co, St Petersburg Russia; Tel +79817146772</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="46" customHeight="1">
       <c r="A118" s="39" t="n">
         <v>114</v>
       </c>
@@ -5275,10 +6051,18 @@
         </is>
       </c>
       <c r="J118" s="39" t="inlineStr"/>
-      <c r="L118" s="39" t="inlineStr"/>
-      <c r="N118" s="39" t="inlineStr"/>
-    </row>
-    <row r="119" ht="30" customHeight="1">
+      <c r="L118" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries</t>
+        </is>
+      </c>
+      <c r="N118" s="39" t="inlineStr">
+        <is>
+          <t>Maya Holling, Badger Ingredients/Ingredient Logistics (US); Office +1 480-404-9539, Mobile +1 480-639-8982</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="46" customHeight="1">
       <c r="A119" s="39" t="n">
         <v>115</v>
       </c>
@@ -5306,11 +6090,23 @@
           <t>Whole FD strawberries (Turkish client)</t>
         </is>
       </c>
-      <c r="J119" s="39" t="inlineStr"/>
-      <c r="L119" s="39" t="inlineStr"/>
-      <c r="N119" s="39" t="inlineStr"/>
-    </row>
-    <row r="120" ht="30" customHeight="1">
+      <c r="J119" s="39" t="inlineStr">
+        <is>
+          <t>Quantities to be agreed at meeting</t>
+        </is>
+      </c>
+      <c r="L119" s="39" t="inlineStr">
+        <is>
+          <t>Whole freeze-dried strawberries</t>
+        </is>
+      </c>
+      <c r="N119" s="39" t="inlineStr">
+        <is>
+          <t>City Run Group, export services, Sadat City; sourcing for a Turkish client visiting Egypt 27th-29th; requests meeting to agree quantities/prices; Mahran Yousof CFO +201114449383</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="46" customHeight="1">
       <c r="A120" s="39" t="n">
         <v>116</v>
       </c>
@@ -5342,11 +6138,23 @@
           <t>FD fruit private label/OEM export to US</t>
         </is>
       </c>
-      <c r="J120" s="39" t="inlineStr"/>
-      <c r="L120" s="39" t="inlineStr"/>
-      <c r="N120" s="39" t="inlineStr"/>
-    </row>
-    <row r="121" ht="30" customHeight="1">
+      <c r="J120" s="39" t="inlineStr">
+        <is>
+          <t>Asking MOQ for private label freeze-dried products</t>
+        </is>
+      </c>
+      <c r="L120" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried fruit snacks - strawberry, mango, mixed fruits; private label/OEM; requests price list (bulk and private label)</t>
+        </is>
+      </c>
+      <c r="N120" s="39" t="inlineStr">
+        <is>
+          <t>Export to US/Amazon FBA; FDA-compliant labeling, UPC/FNSKU barcoding, export docs/customs, ship to US forwarder/FBA; asks lead time &amp; production availability; US startup managed from UAE; Tel +971562021745</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="46" customHeight="1">
       <c r="A121" s="39" t="n">
         <v>117</v>
       </c>
@@ -5382,7 +6190,7 @@
       <c r="L121" s="39" t="inlineStr"/>
       <c r="N121" s="39" t="inlineStr"/>
     </row>
-    <row r="122" ht="30" customHeight="1">
+    <row r="122" ht="46" customHeight="1">
       <c r="A122" s="39" t="n">
         <v>118</v>
       </c>
@@ -5414,7 +6222,7 @@
       <c r="L122" s="39" t="inlineStr"/>
       <c r="N122" s="39" t="inlineStr"/>
     </row>
-    <row r="123" ht="30" customHeight="1">
+    <row r="123" ht="46" customHeight="1">
       <c r="A123" s="39" t="n">
         <v>119</v>
       </c>
@@ -5447,10 +6255,18 @@
         </is>
       </c>
       <c r="J123" s="39" t="inlineStr"/>
-      <c r="L123" s="39" t="inlineStr"/>
-      <c r="N123" s="39" t="inlineStr"/>
-    </row>
-    <row r="124" ht="30" customHeight="1">
+      <c r="L123" s="39" t="inlineStr">
+        <is>
+          <t>Requests explanation of products and prices plus packaging</t>
+        </is>
+      </c>
+      <c r="N123" s="39" t="inlineStr">
+        <is>
+          <t>Mohamad Khalil, Lagos, Nigeria; general product/price inquiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="46" customHeight="1">
       <c r="A124" s="39" t="n">
         <v>120</v>
       </c>
@@ -5482,11 +6298,23 @@
           <t>FD strawberries 50 MT export to China (CIF Shanghai)</t>
         </is>
       </c>
-      <c r="J124" s="39" t="inlineStr"/>
-      <c r="L124" s="39" t="inlineStr"/>
-      <c r="N124" s="39" t="inlineStr"/>
-    </row>
-    <row r="125" ht="30" customHeight="1">
+      <c r="J124" s="39" t="inlineStr">
+        <is>
+          <t>50 metric tons for export to China</t>
+        </is>
+      </c>
+      <c r="L124" s="39" t="inlineStr">
+        <is>
+          <t>1) FD strawberries whole, premium food grade, moisture &lt;=5% (target &lt;=3%), 10kg carton w/ 4x2.5kg inner bags; 2) FD strawberry powder 100% (no sugar/carriers), moisture &lt;=4%; FDA/USDA compliant</t>
+        </is>
+      </c>
+      <c r="N124" s="39" t="inlineStr">
+        <is>
+          <t>CIF Shanghai; certs HACCP/ISO/BRC/Organic, COA, heavy metals &amp; pesticide testing; asks MOQ/container plan, lead time, payment terms, samples (partner in China till 8 Jan); Garden Guru, Cairo; Taha Azouz +201114200008</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="46" customHeight="1">
       <c r="A125" s="39" t="n">
         <v>121</v>
       </c>
@@ -5522,7 +6350,7 @@
       <c r="L125" s="39" t="inlineStr"/>
       <c r="N125" s="39" t="inlineStr"/>
     </row>
-    <row r="126" ht="30" customHeight="1">
+    <row r="126" ht="46" customHeight="1">
       <c r="A126" s="39" t="n">
         <v>122</v>
       </c>
@@ -5555,10 +6383,18 @@
         </is>
       </c>
       <c r="J126" s="39" t="inlineStr"/>
-      <c r="L126" s="39" t="inlineStr"/>
-      <c r="N126" s="39" t="inlineStr"/>
-    </row>
-    <row r="127" ht="30" customHeight="1">
+      <c r="L126" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried strawberries, whole, 15-25 mm, preferably round form (not prolongated); quality (taste/appearance); requests quote and product specs</t>
+        </is>
+      </c>
+      <c r="N126" s="39" t="inlineStr">
+        <is>
+          <t>FCA price and CFR Hamburg requested; must comply with EU legislation (pesticides, heavy metals contaminants); Fruzbi Ukraine LLC for EU partner; wants meeting at FI Europe 2025; Anatolii Kondratenko +380931352755, dir Max +380673103857</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="46" customHeight="1">
       <c r="A127" s="39" t="n">
         <v>123</v>
       </c>
@@ -5596,9 +6432,13 @@
       </c>
       <c r="J127" s="39" t="inlineStr"/>
       <c r="L127" s="39" t="inlineStr"/>
-      <c r="N127" s="39" t="inlineStr"/>
-    </row>
-    <row r="128" ht="30" customHeight="1">
+      <c r="N127" s="39" t="inlineStr">
+        <is>
+          <t>Not a buyer - Egyptian supplier (Anwar Moussa, Nubaria/Beheira) offering to supply fresh/frozen produce &amp; citrus to MAFI's Sadat City concentrate factory; Tel 01014147590, 01555087590; MAFI replied will cooperate once plant starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="46" customHeight="1">
       <c r="A128" s="39" t="n">
         <v>124</v>
       </c>
@@ -5630,11 +6470,23 @@
           <t>FD strawberries sliced 10,000 kg (offer request)</t>
         </is>
       </c>
-      <c r="J128" s="39" t="inlineStr"/>
-      <c r="L128" s="39" t="inlineStr"/>
-      <c r="N128" s="39" t="inlineStr"/>
-    </row>
-    <row r="129" ht="30" customHeight="1">
+      <c r="J128" s="39" t="inlineStr">
+        <is>
+          <t>10,000 kg</t>
+        </is>
+      </c>
+      <c r="L128" s="39" t="inlineStr">
+        <is>
+          <t>Conventional FD strawberries, sliced; residual moisture max 5%, powder content max 5%, DGHM micro standards, no irradiated/GMO raw materials, metal-detector/X-ray foreign-body control; organic option queried</t>
+        </is>
+      </c>
+      <c r="N128" s="39" t="inlineStr">
+        <is>
+          <t>Requests MOQ &amp; volume-based price tiers; will only buy with intact certification chain - asks for IFS / BRC / FSSC 22000</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="46" customHeight="1">
       <c r="A129" s="39" t="n">
         <v>125</v>
       </c>
@@ -5666,11 +6518,23 @@
           <t>Fruit waste/seeds after puree production (2026-28)</t>
         </is>
       </c>
-      <c r="J129" s="39" t="inlineStr"/>
-      <c r="L129" s="39" t="inlineStr"/>
-      <c r="N129" s="39" t="inlineStr"/>
-    </row>
-    <row r="130" ht="30" customHeight="1">
+      <c r="J129" s="39" t="inlineStr">
+        <is>
+          <t>Single pallets up to FTL refrigerated (40 pallets = 160 drums); ~10 MT strawberry seed waste per 100 MT puree</t>
+        </is>
+      </c>
+      <c r="L129" s="39" t="inlineStr">
+        <is>
+          <t>Frozen fruit waste/seeds after puree/concentrate production - strawberry (high seed content), blackcurrant, passion fruit, kiwi, fig, prickly pear, all organic; packed in used drums/box pallets</t>
+        </is>
+      </c>
+      <c r="N129" s="39" t="inlineStr">
+        <is>
+          <t>Long-term cooperation 2026/27/28; more seeds = higher price; wants Teams meeting; sent sample photos; GreenField Sp z o.o., Warsaw Poland; Pawel Gucajtis +48 502 170 343</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="46" customHeight="1">
       <c r="A130" s="39" t="n">
         <v>126</v>
       </c>
@@ -5702,11 +6566,23 @@
           <t>Orange Juice Concentrate (demand 200MT/month; wants to be Chinese representative)</t>
         </is>
       </c>
-      <c r="J130" s="39" t="inlineStr"/>
-      <c r="L130" s="39" t="inlineStr"/>
-      <c r="N130" s="39" t="inlineStr"/>
-    </row>
-    <row r="131" ht="30" customHeight="1">
+      <c r="J130" s="39" t="inlineStr">
+        <is>
+          <t>Can sell 200 MT per month; wants to be Chinese representative</t>
+        </is>
+      </c>
+      <c r="L130" s="39" t="inlineStr">
+        <is>
+          <t>Orange Juice Concentrate; asks if blended or pure concentrate; requests COA</t>
+        </is>
+      </c>
+      <c r="N130" s="39" t="inlineStr">
+        <is>
+          <t>China importer Far Way Agro (Shaanxi); imports citrus from Egypt &amp; OJC from S.Africa/Brazil/Spain; asks current OJC stock (Egyptian oranges start Dec); Darren Yang +86 132 8929 9418</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="46" customHeight="1">
       <c r="A131" s="39" t="n">
         <v>127</v>
       </c>
@@ -5743,10 +6619,18 @@
         </is>
       </c>
       <c r="J131" s="39" t="inlineStr"/>
-      <c r="L131" s="39" t="inlineStr"/>
-      <c r="N131" s="39" t="inlineStr"/>
-    </row>
-    <row r="132" ht="30" customHeight="1">
+      <c r="L131" s="39" t="inlineStr">
+        <is>
+          <t>Freeze-dried (FD) strawberries; requests specifications and samples</t>
+        </is>
+      </c>
+      <c r="N131" s="39" t="inlineStr">
+        <is>
+          <t>Trawosa AG, St Gallen Switzerland; Michael Lang, Product Manager; already has many customers for FD strawberry products; open to cooperation, asked when production starts (MAFI: Q1/Q2 2026); Tel +41 78 882 04 77</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="46" customHeight="1">
       <c r="A132" s="39" t="n">
         <v>128</v>
       </c>
@@ -5786,7 +6670,7 @@
       <c r="L132" s="39" t="inlineStr"/>
       <c r="N132" s="39" t="inlineStr"/>
     </row>
-    <row r="133" ht="30" customHeight="1">
+    <row r="133" ht="46" customHeight="1">
       <c r="A133" s="39" t="n">
         <v>129</v>
       </c>
@@ -5830,7 +6714,7 @@
       <c r="L133" s="39" t="inlineStr"/>
       <c r="N133" s="39" t="inlineStr"/>
     </row>
-    <row r="134" ht="30" customHeight="1">
+    <row r="134" ht="46" customHeight="1">
       <c r="A134" s="39" t="n">
         <v>130</v>
       </c>
@@ -5870,11 +6754,23 @@
           <t>IQF mango 20x20 chunks (zebdya variety), 1x24t container</t>
         </is>
       </c>
-      <c r="J134" s="39" t="inlineStr"/>
-      <c r="L134" s="39" t="inlineStr"/>
-      <c r="N134" s="39" t="inlineStr"/>
-    </row>
-    <row r="135" ht="30" customHeight="1">
+      <c r="J134" s="39" t="inlineStr">
+        <is>
+          <t>One container - 24 tons</t>
+        </is>
+      </c>
+      <c r="L134" s="39" t="inlineStr">
+        <is>
+          <t>IQF mango 20x20 chunks, only Zebdya variety; asks price and lead time</t>
+        </is>
+      </c>
+      <c r="N134" s="39" t="inlineStr">
+        <is>
+          <t>Fresh Apple Turkey; Furkan Col, Manager; also requested online meeting; MAFI noted IQF production but no mango, start Q2 2026; Mobile +9053...</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="46" customHeight="1">
       <c r="A135" s="39" t="n">
         <v>131</v>
       </c>
@@ -5915,8 +6811,16 @@
         </is>
       </c>
       <c r="J135" s="39" t="inlineStr"/>
-      <c r="L135" s="39" t="inlineStr"/>
-      <c r="N135" s="39" t="inlineStr"/>
+      <c r="L135" s="39" t="inlineStr">
+        <is>
+          <t>Strawberry IQF; asks if MAFI can offer</t>
+        </is>
+      </c>
+      <c r="N135" s="39" t="inlineStr">
+        <is>
+          <t>Hellenic Juice Industry C. Dedes ASPIS S.A., Argos-Korinthos Greece; Mario Chronis, General Manager; T +302751028004, M +306951010008</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="410">
